--- a/Files/Madden26/IE/Season2/FreeAgency/Input/ContractOffer.xlsx
+++ b/Files/Madden26/IE/Season2/FreeAgency/Input/ContractOffer.xlsx
@@ -414,10 +414,10 @@
     </row>
     <row r="2">
       <c r="A2" t="str">
-        <v>00101110001110100000000000000001</v>
+        <v>00000000000000000000000000111010</v>
       </c>
       <c r="B2" t="str">
-        <v>00100000111111000000000111100100</v>
+        <v>00000000000000000000000000000000</v>
       </c>
       <c r="C2" t="str">
         <v>00000000000000000000000000000000</v>
@@ -426,7 +426,7 @@
         <v>00000000000000000000000000000000</v>
       </c>
       <c r="E2" t="str">
-        <v>00100001011110100000000000000000</v>
+        <v>00000000000000000000000000000000</v>
       </c>
       <c r="F2" t="b">
         <v>0</v>
@@ -449,10 +449,10 @@
     </row>
     <row r="3">
       <c r="A3" t="str">
-        <v>00101110001110100000000000000001</v>
+        <v>00000000000000000000000010101111</v>
       </c>
       <c r="B3" t="str">
-        <v>00100000111111000000100101000010</v>
+        <v>00000000000000000000000000000000</v>
       </c>
       <c r="C3" t="str">
         <v>00000000000000000000000000000000</v>
@@ -461,7 +461,7 @@
         <v>00000000000000000000000000000000</v>
       </c>
       <c r="E3" t="str">
-        <v>00100001011110100000000000000001</v>
+        <v>00000000000000000000000000000000</v>
       </c>
       <c r="F3" t="b">
         <v>0</v>
@@ -470,7 +470,7 @@
         <v>0</v>
       </c>
       <c r="H3" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I3">
         <v>0</v>
@@ -484,10 +484,10 @@
     </row>
     <row r="4">
       <c r="A4" t="str">
-        <v>00101110001110100000000000000001</v>
+        <v>00000000000000000000000001110100</v>
       </c>
       <c r="B4" t="str">
-        <v>00100000111111000000000011011010</v>
+        <v>00000000000000000000000000000000</v>
       </c>
       <c r="C4" t="str">
         <v>00000000000000000000000000000000</v>
@@ -496,7 +496,7 @@
         <v>00000000000000000000000000000000</v>
       </c>
       <c r="E4" t="str">
-        <v>00100001011110100000000000000010</v>
+        <v>00000000000000000000000000000000</v>
       </c>
       <c r="F4" t="b">
         <v>0</v>
@@ -519,10 +519,10 @@
     </row>
     <row r="5">
       <c r="A5" t="str">
-        <v>00101110001110100000000000000001</v>
+        <v>00000000000000000000000001010000</v>
       </c>
       <c r="B5" t="str">
-        <v>00100000111111000000100011001001</v>
+        <v>00000000000000000000000000000000</v>
       </c>
       <c r="C5" t="str">
         <v>00000000000000000000000000000000</v>
@@ -531,7 +531,7 @@
         <v>00000000000000000000000000000000</v>
       </c>
       <c r="E5" t="str">
-        <v>00100001011110100000000000000011</v>
+        <v>00000000000000000000000000000000</v>
       </c>
       <c r="F5" t="b">
         <v>0</v>
@@ -554,10 +554,10 @@
     </row>
     <row r="6">
       <c r="A6" t="str">
-        <v>00101110001110100000000000000001</v>
+        <v>00000000000000000000000011001001</v>
       </c>
       <c r="B6" t="str">
-        <v>00100000111111000000000111010111</v>
+        <v>00000000000000000000000000000000</v>
       </c>
       <c r="C6" t="str">
         <v>00000000000000000000000000000000</v>
@@ -566,7 +566,7 @@
         <v>00000000000000000000000000000000</v>
       </c>
       <c r="E6" t="str">
-        <v>00100001011110100000000000000100</v>
+        <v>00000000000000000000000000000000</v>
       </c>
       <c r="F6" t="b">
         <v>0</v>
@@ -589,10 +589,10 @@
     </row>
     <row r="7">
       <c r="A7" t="str">
-        <v>00101110001110100000000000000001</v>
+        <v>00000000000000000000000010111011</v>
       </c>
       <c r="B7" t="str">
-        <v>00100000111111000000100111100100</v>
+        <v>00000000000000000000000000000000</v>
       </c>
       <c r="C7" t="str">
         <v>00000000000000000000000000000000</v>
@@ -601,7 +601,7 @@
         <v>00000000000000000000000000000000</v>
       </c>
       <c r="E7" t="str">
-        <v>00100001011110100000000000000101</v>
+        <v>00000000000000000000000000000000</v>
       </c>
       <c r="F7" t="b">
         <v>0</v>
@@ -610,7 +610,7 @@
         <v>0</v>
       </c>
       <c r="H7" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I7">
         <v>0</v>
@@ -624,10 +624,10 @@
     </row>
     <row r="8">
       <c r="A8" t="str">
-        <v>00101110001110100000000000000001</v>
+        <v>00000000000000000000000010001000</v>
       </c>
       <c r="B8" t="str">
-        <v>00100000111111000000011101000100</v>
+        <v>00000000000000000000000000000000</v>
       </c>
       <c r="C8" t="str">
         <v>00000000000000000000000000000000</v>
@@ -636,7 +636,7 @@
         <v>00000000000000000000000000000000</v>
       </c>
       <c r="E8" t="str">
-        <v>00100001011110100000000000000110</v>
+        <v>00000000000000000000000000000000</v>
       </c>
       <c r="F8" t="b">
         <v>0</v>
@@ -659,10 +659,10 @@
     </row>
     <row r="9">
       <c r="A9" t="str">
-        <v>00101110001110100000000000000010</v>
+        <v>00000000000000000000000000000011</v>
       </c>
       <c r="B9" t="str">
-        <v>00100000111111000000010011111111</v>
+        <v>00000000000000000000000000000000</v>
       </c>
       <c r="C9" t="str">
         <v>00000000000000000000000000000000</v>
@@ -671,7 +671,7 @@
         <v>00000000000000000000000000000000</v>
       </c>
       <c r="E9" t="str">
-        <v>00100001011110100000000000000111</v>
+        <v>00000000000000000000000000000000</v>
       </c>
       <c r="F9" t="b">
         <v>0</v>
@@ -694,10 +694,10 @@
     </row>
     <row r="10">
       <c r="A10" t="str">
-        <v>00101110001110100000000000000001</v>
+        <v>00000000000000000000000001101010</v>
       </c>
       <c r="B10" t="str">
-        <v>00100000111111000000000110100100</v>
+        <v>00000000000000000000000000000000</v>
       </c>
       <c r="C10" t="str">
         <v>00000000000000000000000000000000</v>
@@ -706,7 +706,7 @@
         <v>00000000000000000000000000000000</v>
       </c>
       <c r="E10" t="str">
-        <v>00100001011110100000000000001000</v>
+        <v>00000000000000000000000000000000</v>
       </c>
       <c r="F10" t="b">
         <v>0</v>
@@ -729,10 +729,10 @@
     </row>
     <row r="11">
       <c r="A11" t="str">
-        <v>00101110001110100000000000000001</v>
+        <v>00000000000000000000000001001100</v>
       </c>
       <c r="B11" t="str">
-        <v>00100000111111000000000100011011</v>
+        <v>00000000000000000000000000000000</v>
       </c>
       <c r="C11" t="str">
         <v>00000000000000000000000000000000</v>
@@ -741,7 +741,7 @@
         <v>00000000000000000000000000000000</v>
       </c>
       <c r="E11" t="str">
-        <v>00100001011110100000000000001001</v>
+        <v>00000000000000000000000000000000</v>
       </c>
       <c r="F11" t="b">
         <v>0</v>
@@ -764,10 +764,10 @@
     </row>
     <row r="12">
       <c r="A12" t="str">
-        <v>00101110001110100000000000000010</v>
+        <v>00000000000000000000000000101001</v>
       </c>
       <c r="B12" t="str">
-        <v>00100000111111000000001111101001</v>
+        <v>00000000000000000000000000000000</v>
       </c>
       <c r="C12" t="str">
         <v>00000000000000000000000000000000</v>
@@ -776,7 +776,7 @@
         <v>00000000000000000000000000000000</v>
       </c>
       <c r="E12" t="str">
-        <v>00100001011110100000000000001010</v>
+        <v>00000000000000000000000000000000</v>
       </c>
       <c r="F12" t="b">
         <v>0</v>
@@ -799,10 +799,10 @@
     </row>
     <row r="13">
       <c r="A13" t="str">
-        <v>00101110001110100000000000000010</v>
+        <v>00000000000000000000000000111011</v>
       </c>
       <c r="B13" t="str">
-        <v>00100000111111000000011110110111</v>
+        <v>00000000000000000000000000000000</v>
       </c>
       <c r="C13" t="str">
         <v>00000000000000000000000000000000</v>
@@ -811,7 +811,7 @@
         <v>00000000000000000000000000000000</v>
       </c>
       <c r="E13" t="str">
-        <v>00100001011110100000000000001011</v>
+        <v>00000000000000000000000000000000</v>
       </c>
       <c r="F13" t="b">
         <v>0</v>
@@ -820,7 +820,7 @@
         <v>0</v>
       </c>
       <c r="H13" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I13">
         <v>0</v>
@@ -834,10 +834,10 @@
     </row>
     <row r="14">
       <c r="A14" t="str">
-        <v>00101110001110100000000000000010</v>
+        <v>00000000000000000000000000011110</v>
       </c>
       <c r="B14" t="str">
-        <v>00100000111111000000001011001011</v>
+        <v>00000000000000000000000000000000</v>
       </c>
       <c r="C14" t="str">
         <v>00000000000000000000000000000000</v>
@@ -846,7 +846,7 @@
         <v>00000000000000000000000000000000</v>
       </c>
       <c r="E14" t="str">
-        <v>00100001011110100000000000001100</v>
+        <v>00000000000000000000000000000000</v>
       </c>
       <c r="F14" t="b">
         <v>0</v>
@@ -855,7 +855,7 @@
         <v>0</v>
       </c>
       <c r="H14" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I14">
         <v>0</v>
@@ -869,10 +869,10 @@
     </row>
     <row r="15">
       <c r="A15" t="str">
-        <v>00101110001110100000000000000011</v>
+        <v>00000000000000000000000000011111</v>
       </c>
       <c r="B15" t="str">
-        <v>00100000111111000000101000001110</v>
+        <v>00000000000000000000000000000000</v>
       </c>
       <c r="C15" t="str">
         <v>00000000000000000000000000000000</v>
@@ -881,7 +881,7 @@
         <v>00000000000000000000000000000000</v>
       </c>
       <c r="E15" t="str">
-        <v>00100001011110100000000000001101</v>
+        <v>00000000000000000000000000000000</v>
       </c>
       <c r="F15" t="b">
         <v>0</v>
@@ -904,10 +904,10 @@
     </row>
     <row r="16">
       <c r="A16" t="str">
-        <v>00101110001110100000000000000011</v>
+        <v>00000000000000000000000001010010</v>
       </c>
       <c r="B16" t="str">
-        <v>00100000111111000000101010000100</v>
+        <v>00000000000000000000000000000000</v>
       </c>
       <c r="C16" t="str">
         <v>00000000000000000000000000000000</v>
@@ -916,7 +916,7 @@
         <v>00000000000000000000000000000000</v>
       </c>
       <c r="E16" t="str">
-        <v>00100001011110100000000000001110</v>
+        <v>00000000000000000000000000000000</v>
       </c>
       <c r="F16" t="b">
         <v>0</v>
@@ -939,10 +939,10 @@
     </row>
     <row r="17">
       <c r="A17" t="str">
-        <v>00101110001110100000000000000011</v>
+        <v>00000000000000000000000000011000</v>
       </c>
       <c r="B17" t="str">
-        <v>00100000111111000000101001010111</v>
+        <v>00000000000000000000000000000000</v>
       </c>
       <c r="C17" t="str">
         <v>00000000000000000000000000000000</v>
@@ -951,7 +951,7 @@
         <v>00000000000000000000000000000000</v>
       </c>
       <c r="E17" t="str">
-        <v>00100001011110100000000000001111</v>
+        <v>00000000000000000000000000000000</v>
       </c>
       <c r="F17" t="b">
         <v>0</v>
@@ -960,7 +960,7 @@
         <v>0</v>
       </c>
       <c r="H17" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I17">
         <v>0</v>
@@ -974,10 +974,10 @@
     </row>
     <row r="18">
       <c r="A18" t="str">
-        <v>00101110001110100000000000000011</v>
+        <v>00000000000000000000000001110001</v>
       </c>
       <c r="B18" t="str">
-        <v>00100000111111000000100110011110</v>
+        <v>00000000000000000000000000000000</v>
       </c>
       <c r="C18" t="str">
         <v>00000000000000000000000000000000</v>
@@ -986,7 +986,7 @@
         <v>00000000000000000000000000000000</v>
       </c>
       <c r="E18" t="str">
-        <v>00100001011110100000000000010000</v>
+        <v>00000000000000000000000000000000</v>
       </c>
       <c r="F18" t="b">
         <v>0</v>
@@ -1009,10 +1009,10 @@
     </row>
     <row r="19">
       <c r="A19" t="str">
-        <v>00101110001110100000000000000011</v>
+        <v>00000000000000000000000011011000</v>
       </c>
       <c r="B19" t="str">
-        <v>00100000111111000000100011001110</v>
+        <v>00000000000000000000000000000000</v>
       </c>
       <c r="C19" t="str">
         <v>00000000000000000000000000000000</v>
@@ -1021,7 +1021,7 @@
         <v>00000000000000000000000000000000</v>
       </c>
       <c r="E19" t="str">
-        <v>00100001011110100000000000010001</v>
+        <v>00000000000000000000000000000000</v>
       </c>
       <c r="F19" t="b">
         <v>0</v>
@@ -1030,7 +1030,7 @@
         <v>0</v>
       </c>
       <c r="H19" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I19">
         <v>0</v>
@@ -1044,10 +1044,10 @@
     </row>
     <row r="20">
       <c r="A20" t="str">
-        <v>00101110001110100000000000000011</v>
+        <v>00000000000000000000000000101010</v>
       </c>
       <c r="B20" t="str">
-        <v>00100000111111000000101111011010</v>
+        <v>00000000000000000000000000000000</v>
       </c>
       <c r="C20" t="str">
         <v>00000000000000000000000000000000</v>
@@ -1056,7 +1056,7 @@
         <v>00000000000000000000000000000000</v>
       </c>
       <c r="E20" t="str">
-        <v>00100001011110100000000000010010</v>
+        <v>00000000000000000000000000000000</v>
       </c>
       <c r="F20" t="b">
         <v>0</v>
@@ -1079,7 +1079,7 @@
     </row>
     <row r="21">
       <c r="A21" t="str">
-        <v>00000000000000000000000011010111</v>
+        <v>00000000000000000000000001001000</v>
       </c>
       <c r="B21" t="str">
         <v>00000000000000000000000000000000</v>
@@ -1100,7 +1100,7 @@
         <v>0</v>
       </c>
       <c r="H21" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I21">
         <v>0</v>
@@ -1114,10 +1114,10 @@
     </row>
     <row r="22">
       <c r="A22" t="str">
-        <v>00101110001110100000000000000100</v>
+        <v>00000000000000000000000001001110</v>
       </c>
       <c r="B22" t="str">
-        <v>00100000111111000000100010001111</v>
+        <v>00000000000000000000000000000000</v>
       </c>
       <c r="C22" t="str">
         <v>00000000000000000000000000000000</v>
@@ -1126,7 +1126,7 @@
         <v>00000000000000000000000000000000</v>
       </c>
       <c r="E22" t="str">
-        <v>00100001011110100000000000010100</v>
+        <v>00000000000000000000000000000000</v>
       </c>
       <c r="F22" t="b">
         <v>0</v>
@@ -1149,10 +1149,10 @@
     </row>
     <row r="23">
       <c r="A23" t="str">
-        <v>00101110001110100000000000000100</v>
+        <v>00000000000000000000000001010100</v>
       </c>
       <c r="B23" t="str">
-        <v>00100000111111000000011011101110</v>
+        <v>00000000000000000000000000000000</v>
       </c>
       <c r="C23" t="str">
         <v>00000000000000000000000000000000</v>
@@ -1161,7 +1161,7 @@
         <v>00000000000000000000000000000000</v>
       </c>
       <c r="E23" t="str">
-        <v>00100001011110100000000000010101</v>
+        <v>00000000000000000000000000000000</v>
       </c>
       <c r="F23" t="b">
         <v>0</v>
@@ -1184,10 +1184,10 @@
     </row>
     <row r="24">
       <c r="A24" t="str">
-        <v>00101110001110100000000000000100</v>
+        <v>00000000000000000000000001001101</v>
       </c>
       <c r="B24" t="str">
-        <v>00100000111111000000000001100011</v>
+        <v>00000000000000000000000000000000</v>
       </c>
       <c r="C24" t="str">
         <v>00000000000000000000000000000000</v>
@@ -1196,7 +1196,7 @@
         <v>00000000000000000000000000000000</v>
       </c>
       <c r="E24" t="str">
-        <v>00100001011110100000000000010110</v>
+        <v>00000000000000000000000000000000</v>
       </c>
       <c r="F24" t="b">
         <v>0</v>
@@ -1219,10 +1219,10 @@
     </row>
     <row r="25">
       <c r="A25" t="str">
-        <v>00101110001110100000000000000100</v>
+        <v>00000000000000000000000000101101</v>
       </c>
       <c r="B25" t="str">
-        <v>00100000111111000000001101000110</v>
+        <v>00000000000000000000000000000000</v>
       </c>
       <c r="C25" t="str">
         <v>00000000000000000000000000000000</v>
@@ -1231,7 +1231,7 @@
         <v>00000000000000000000000000000000</v>
       </c>
       <c r="E25" t="str">
-        <v>00100001011110100000000000010111</v>
+        <v>00000000000000000000000000000000</v>
       </c>
       <c r="F25" t="b">
         <v>0</v>
@@ -1254,10 +1254,10 @@
     </row>
     <row r="26">
       <c r="A26" t="str">
-        <v>00101110001110100000000000000100</v>
+        <v>00000000000000000000000100001010</v>
       </c>
       <c r="B26" t="str">
-        <v>00100000111111000000011010100000</v>
+        <v>00000000000000000000000000000000</v>
       </c>
       <c r="C26" t="str">
         <v>00000000000000000000000000000000</v>
@@ -1266,7 +1266,7 @@
         <v>00000000000000000000000000000000</v>
       </c>
       <c r="E26" t="str">
-        <v>00100001011110100000000000011000</v>
+        <v>00000000000000000000000000000000</v>
       </c>
       <c r="F26" t="b">
         <v>0</v>
@@ -1275,7 +1275,7 @@
         <v>0</v>
       </c>
       <c r="H26" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I26">
         <v>0</v>
@@ -1289,10 +1289,10 @@
     </row>
     <row r="27">
       <c r="A27" t="str">
-        <v>00101110001110100000000000000100</v>
+        <v>00000000000000000000000000111110</v>
       </c>
       <c r="B27" t="str">
-        <v>00100000111111000000011010111110</v>
+        <v>00000000000000000000000000000000</v>
       </c>
       <c r="C27" t="str">
         <v>00000000000000000000000000000000</v>
@@ -1301,7 +1301,7 @@
         <v>00000000000000000000000000000000</v>
       </c>
       <c r="E27" t="str">
-        <v>00100001011110100000000000011001</v>
+        <v>00000000000000000000000000000000</v>
       </c>
       <c r="F27" t="b">
         <v>0</v>
@@ -1324,10 +1324,10 @@
     </row>
     <row r="28">
       <c r="A28" t="str">
-        <v>00101110001110100000000000000001</v>
+        <v>00000000000000000000000001110111</v>
       </c>
       <c r="B28" t="str">
-        <v>00100000111111000000011110010110</v>
+        <v>00000000000000000000000000000000</v>
       </c>
       <c r="C28" t="str">
         <v>00000000000000000000000000000000</v>
@@ -1336,7 +1336,7 @@
         <v>00000000000000000000000000000000</v>
       </c>
       <c r="E28" t="str">
-        <v>00100001011110100000000000011010</v>
+        <v>00000000000000000000000000000000</v>
       </c>
       <c r="F28" t="b">
         <v>0</v>
@@ -1359,10 +1359,10 @@
     </row>
     <row r="29">
       <c r="A29" t="str">
-        <v>00101110001110100000000000000001</v>
+        <v>00000000000000000000000000001001</v>
       </c>
       <c r="B29" t="str">
-        <v>00100000111111000000000100100001</v>
+        <v>00000000000000000000000000000000</v>
       </c>
       <c r="C29" t="str">
         <v>00000000000000000000000000000000</v>
@@ -1371,7 +1371,7 @@
         <v>00000000000000000000000000000000</v>
       </c>
       <c r="E29" t="str">
-        <v>00100001011110100000000000011011</v>
+        <v>00000000000000000000000000000000</v>
       </c>
       <c r="F29" t="b">
         <v>0</v>
@@ -1394,10 +1394,10 @@
     </row>
     <row r="30">
       <c r="A30" t="str">
-        <v>00101110001110100000000000000101</v>
+        <v>00000000000000000000000001101011</v>
       </c>
       <c r="B30" t="str">
-        <v>00100000111111000000001011110000</v>
+        <v>00000000000000000000000000000000</v>
       </c>
       <c r="C30" t="str">
         <v>00000000000000000000000000000000</v>
@@ -1406,7 +1406,7 @@
         <v>00000000000000000000000000000000</v>
       </c>
       <c r="E30" t="str">
-        <v>00100001011110100000000000011100</v>
+        <v>00000000000000000000000000000000</v>
       </c>
       <c r="F30" t="b">
         <v>0</v>
@@ -1429,10 +1429,10 @@
     </row>
     <row r="31">
       <c r="A31" t="str">
-        <v>00101110001110100000000000000101</v>
+        <v>00000000000000000000000000001000</v>
       </c>
       <c r="B31" t="str">
-        <v>00100000111111000000000000101011</v>
+        <v>00000000000000000000000000000000</v>
       </c>
       <c r="C31" t="str">
         <v>00000000000000000000000000000000</v>
@@ -1441,7 +1441,7 @@
         <v>00000000000000000000000000000000</v>
       </c>
       <c r="E31" t="str">
-        <v>00100001011110100000000000011101</v>
+        <v>00000000000000000000000000000000</v>
       </c>
       <c r="F31" t="b">
         <v>0</v>
@@ -1464,10 +1464,10 @@
     </row>
     <row r="32">
       <c r="A32" t="str">
-        <v>00101110001110100000000000000001</v>
+        <v>00000000000000000000000010000001</v>
       </c>
       <c r="B32" t="str">
-        <v>00100000111111000000011111001101</v>
+        <v>00000000000000000000000000000000</v>
       </c>
       <c r="C32" t="str">
         <v>00000000000000000000000000000000</v>
@@ -1476,7 +1476,7 @@
         <v>00000000000000000000000000000000</v>
       </c>
       <c r="E32" t="str">
-        <v>00100001011110100000000000011110</v>
+        <v>00000000000000000000000000000000</v>
       </c>
       <c r="F32" t="b">
         <v>0</v>
@@ -1485,7 +1485,7 @@
         <v>0</v>
       </c>
       <c r="H32" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I32">
         <v>0</v>
@@ -1499,10 +1499,10 @@
     </row>
     <row r="33">
       <c r="A33" t="str">
-        <v>00101110001110100000000000000101</v>
+        <v>00000000000000000000000001111100</v>
       </c>
       <c r="B33" t="str">
-        <v>00100000111111000000101011110100</v>
+        <v>00000000000000000000000000000000</v>
       </c>
       <c r="C33" t="str">
         <v>00000000000000000000000000000000</v>
@@ -1511,7 +1511,7 @@
         <v>00000000000000000000000000000000</v>
       </c>
       <c r="E33" t="str">
-        <v>00100001011110100000000000011111</v>
+        <v>00000000000000000000000000000000</v>
       </c>
       <c r="F33" t="b">
         <v>0</v>
@@ -1534,10 +1534,10 @@
     </row>
     <row r="34">
       <c r="A34" t="str">
-        <v>00101110001110100000000000000101</v>
+        <v>00000000000000000000000000101011</v>
       </c>
       <c r="B34" t="str">
-        <v>00100000111111000000010101010011</v>
+        <v>00000000000000000000000000000000</v>
       </c>
       <c r="C34" t="str">
         <v>00000000000000000000000000000000</v>
@@ -1546,7 +1546,7 @@
         <v>00000000000000000000000000000000</v>
       </c>
       <c r="E34" t="str">
-        <v>00100001011110100000000000100000</v>
+        <v>00000000000000000000000000000000</v>
       </c>
       <c r="F34" t="b">
         <v>0</v>
@@ -1569,10 +1569,10 @@
     </row>
     <row r="35">
       <c r="A35" t="str">
-        <v>00101110001110100000000000000101</v>
+        <v>00000000000000000000000001111111</v>
       </c>
       <c r="B35" t="str">
-        <v>00100000111111000000100001001110</v>
+        <v>00000000000000000000000000000000</v>
       </c>
       <c r="C35" t="str">
         <v>00000000000000000000000000000000</v>
@@ -1581,7 +1581,7 @@
         <v>00000000000000000000000000000000</v>
       </c>
       <c r="E35" t="str">
-        <v>00100001011110100000000000100001</v>
+        <v>00000000000000000000000000000000</v>
       </c>
       <c r="F35" t="b">
         <v>0</v>
@@ -1604,10 +1604,10 @@
     </row>
     <row r="36">
       <c r="A36" t="str">
-        <v>00101110001110100000000000000101</v>
+        <v>00000000000000000000000000110010</v>
       </c>
       <c r="B36" t="str">
-        <v>00100000111111000000101111000000</v>
+        <v>00000000000000000000000000000000</v>
       </c>
       <c r="C36" t="str">
         <v>00000000000000000000000000000000</v>
@@ -1616,7 +1616,7 @@
         <v>00000000000000000000000000000000</v>
       </c>
       <c r="E36" t="str">
-        <v>00100001011110100000000000100010</v>
+        <v>00000000000000000000000000000000</v>
       </c>
       <c r="F36" t="b">
         <v>0</v>
@@ -1639,10 +1639,10 @@
     </row>
     <row r="37">
       <c r="A37" t="str">
-        <v>00101110001110100000000000000101</v>
+        <v>00000000000000000000000001000111</v>
       </c>
       <c r="B37" t="str">
-        <v>00100000111111000000011011011111</v>
+        <v>00000000000000000000000000000000</v>
       </c>
       <c r="C37" t="str">
         <v>00000000000000000000000000000000</v>
@@ -1651,7 +1651,7 @@
         <v>00000000000000000000000000000000</v>
       </c>
       <c r="E37" t="str">
-        <v>00100001011110100000000000100011</v>
+        <v>00000000000000000000000000000000</v>
       </c>
       <c r="F37" t="b">
         <v>0</v>
@@ -1674,7 +1674,7 @@
     </row>
     <row r="38">
       <c r="A38" t="str">
-        <v>00000000000000000000000011010100</v>
+        <v>00000000000000000000000001100011</v>
       </c>
       <c r="B38" t="str">
         <v>00000000000000000000000000000000</v>
@@ -1695,7 +1695,7 @@
         <v>0</v>
       </c>
       <c r="H38" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I38">
         <v>0</v>
@@ -1709,10 +1709,10 @@
     </row>
     <row r="39">
       <c r="A39" t="str">
-        <v>00101110001110100000000000000110</v>
+        <v>00000000000000000000000000010101</v>
       </c>
       <c r="B39" t="str">
-        <v>00100000111111000000011111010011</v>
+        <v>00000000000000000000000000000000</v>
       </c>
       <c r="C39" t="str">
         <v>00000000000000000000000000000000</v>
@@ -1721,7 +1721,7 @@
         <v>00000000000000000000000000000000</v>
       </c>
       <c r="E39" t="str">
-        <v>00100001011110100000000000100101</v>
+        <v>00000000000000000000000000000000</v>
       </c>
       <c r="F39" t="b">
         <v>0</v>
@@ -1744,10 +1744,10 @@
     </row>
     <row r="40">
       <c r="A40" t="str">
-        <v>00101110001110100000000000000110</v>
+        <v>00000000000000000000000011101010</v>
       </c>
       <c r="B40" t="str">
-        <v>00100000111111000000000101011010</v>
+        <v>00000000000000000000000000000000</v>
       </c>
       <c r="C40" t="str">
         <v>00000000000000000000000000000000</v>
@@ -1756,7 +1756,7 @@
         <v>00000000000000000000000000000000</v>
       </c>
       <c r="E40" t="str">
-        <v>00100001011110100000000000100110</v>
+        <v>00000000000000000000000000000000</v>
       </c>
       <c r="F40" t="b">
         <v>0</v>
@@ -1779,10 +1779,10 @@
     </row>
     <row r="41">
       <c r="A41" t="str">
-        <v>00101110001110100000000000000110</v>
+        <v>00000000000000000000000011100001</v>
       </c>
       <c r="B41" t="str">
-        <v>00100000111111000000010010111100</v>
+        <v>00000000000000000000000000000000</v>
       </c>
       <c r="C41" t="str">
         <v>00000000000000000000000000000000</v>
@@ -1791,7 +1791,7 @@
         <v>00000000000000000000000000000000</v>
       </c>
       <c r="E41" t="str">
-        <v>00100001011110100000000000100111</v>
+        <v>00000000000000000000000000000000</v>
       </c>
       <c r="F41" t="b">
         <v>0</v>
@@ -1814,10 +1814,10 @@
     </row>
     <row r="42">
       <c r="A42" t="str">
-        <v>00101110001110100000000000000110</v>
+        <v>00000000000000000000000001010101</v>
       </c>
       <c r="B42" t="str">
-        <v>00100000111111000000011101100000</v>
+        <v>00000000000000000000000000000000</v>
       </c>
       <c r="C42" t="str">
         <v>00000000000000000000000000000000</v>
@@ -1826,7 +1826,7 @@
         <v>00000000000000000000000000000000</v>
       </c>
       <c r="E42" t="str">
-        <v>00100001011110100000000000101000</v>
+        <v>00000000000000000000000000000000</v>
       </c>
       <c r="F42" t="b">
         <v>0</v>
@@ -1849,10 +1849,10 @@
     </row>
     <row r="43">
       <c r="A43" t="str">
-        <v>00101110001110100000000000000110</v>
+        <v>00000000000000000000000000011011</v>
       </c>
       <c r="B43" t="str">
-        <v>00100000111111000000100000010011</v>
+        <v>00000000000000000000000000000000</v>
       </c>
       <c r="C43" t="str">
         <v>00000000000000000000000000000000</v>
@@ -1861,7 +1861,7 @@
         <v>00000000000000000000000000000000</v>
       </c>
       <c r="E43" t="str">
-        <v>00100001011110100000000000101001</v>
+        <v>00000000000000000000000000000000</v>
       </c>
       <c r="F43" t="b">
         <v>0</v>
@@ -1884,10 +1884,10 @@
     </row>
     <row r="44">
       <c r="A44" t="str">
-        <v>00101110001110100000000000000110</v>
+        <v>00000000000000000000000001011011</v>
       </c>
       <c r="B44" t="str">
-        <v>00100000111111000000011000010110</v>
+        <v>00000000000000000000000000000000</v>
       </c>
       <c r="C44" t="str">
         <v>00000000000000000000000000000000</v>
@@ -1896,7 +1896,7 @@
         <v>00000000000000000000000000000000</v>
       </c>
       <c r="E44" t="str">
-        <v>00100001011110100000000000101010</v>
+        <v>00000000000000000000000000000000</v>
       </c>
       <c r="F44" t="b">
         <v>0</v>
@@ -1919,10 +1919,10 @@
     </row>
     <row r="45">
       <c r="A45" t="str">
-        <v>00101110001110100000000000000111</v>
+        <v>00000000000000000000000001001010</v>
       </c>
       <c r="B45" t="str">
-        <v>00100000111111000000101000011110</v>
+        <v>00000000000000000000000000000000</v>
       </c>
       <c r="C45" t="str">
         <v>00000000000000000000000000000000</v>
@@ -1931,7 +1931,7 @@
         <v>00000000000000000000000000000000</v>
       </c>
       <c r="E45" t="str">
-        <v>00100001011110100000000000101011</v>
+        <v>00000000000000000000000000000000</v>
       </c>
       <c r="F45" t="b">
         <v>0</v>
@@ -1954,10 +1954,10 @@
     </row>
     <row r="46">
       <c r="A46" t="str">
-        <v>00101110001110100000000000000111</v>
+        <v>00000000000000000000000011101011</v>
       </c>
       <c r="B46" t="str">
-        <v>00100000111111000000100001011101</v>
+        <v>00000000000000000000000000000000</v>
       </c>
       <c r="C46" t="str">
         <v>00000000000000000000000000000000</v>
@@ -1966,7 +1966,7 @@
         <v>00000000000000000000000000000000</v>
       </c>
       <c r="E46" t="str">
-        <v>00100001011110100000000000101100</v>
+        <v>00000000000000000000000000000000</v>
       </c>
       <c r="F46" t="b">
         <v>0</v>
@@ -1975,7 +1975,7 @@
         <v>0</v>
       </c>
       <c r="H46" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I46">
         <v>0</v>
@@ -1989,10 +1989,10 @@
     </row>
     <row r="47">
       <c r="A47" t="str">
-        <v>00101110001110100000000000000111</v>
+        <v>00000000000000000000000000010100</v>
       </c>
       <c r="B47" t="str">
-        <v>00100000111111000000100101001001</v>
+        <v>00000000000000000000000000000000</v>
       </c>
       <c r="C47" t="str">
         <v>00000000000000000000000000000000</v>
@@ -2001,7 +2001,7 @@
         <v>00000000000000000000000000000000</v>
       </c>
       <c r="E47" t="str">
-        <v>00100001011110100000000000101101</v>
+        <v>00000000000000000000000000000000</v>
       </c>
       <c r="F47" t="b">
         <v>0</v>
@@ -2024,10 +2024,10 @@
     </row>
     <row r="48">
       <c r="A48" t="str">
-        <v>00101110001110100000000000000001</v>
+        <v>00000000000000000000000010001110</v>
       </c>
       <c r="B48" t="str">
-        <v>00100000111111000000001110110111</v>
+        <v>00000000000000000000000000000000</v>
       </c>
       <c r="C48" t="str">
         <v>00000000000000000000000000000000</v>
@@ -2036,7 +2036,7 @@
         <v>00000000000000000000000000000000</v>
       </c>
       <c r="E48" t="str">
-        <v>00100001011110100000000000101110</v>
+        <v>00000000000000000000000000000000</v>
       </c>
       <c r="F48" t="b">
         <v>0</v>
@@ -2059,10 +2059,10 @@
     </row>
     <row r="49">
       <c r="A49" t="str">
-        <v>00101110001110100000000000000111</v>
+        <v>00000000000000000000000011110011</v>
       </c>
       <c r="B49" t="str">
-        <v>00100000111111000000001101111100</v>
+        <v>00000000000000000000000000000000</v>
       </c>
       <c r="C49" t="str">
         <v>00000000000000000000000000000000</v>
@@ -2071,7 +2071,7 @@
         <v>00000000000000000000000000000000</v>
       </c>
       <c r="E49" t="str">
-        <v>00100001011110100000000000101111</v>
+        <v>00000000000000000000000000000000</v>
       </c>
       <c r="F49" t="b">
         <v>0</v>
@@ -2094,10 +2094,10 @@
     </row>
     <row r="50">
       <c r="A50" t="str">
-        <v>00101110001110100000000000000111</v>
+        <v>00000000000000000000000010000101</v>
       </c>
       <c r="B50" t="str">
-        <v>00100000111111000000101001100101</v>
+        <v>00000000000000000000000000000000</v>
       </c>
       <c r="C50" t="str">
         <v>00000000000000000000000000000000</v>
@@ -2106,7 +2106,7 @@
         <v>00000000000000000000000000000000</v>
       </c>
       <c r="E50" t="str">
-        <v>00100001011110100000000000110000</v>
+        <v>00000000000000000000000000000000</v>
       </c>
       <c r="F50" t="b">
         <v>0</v>
@@ -2115,7 +2115,7 @@
         <v>0</v>
       </c>
       <c r="H50" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I50">
         <v>0</v>
@@ -2129,7 +2129,7 @@
     </row>
     <row r="51">
       <c r="A51" t="str">
-        <v>00000000000000000000000100011010</v>
+        <v>00000000000000000000000001111000</v>
       </c>
       <c r="B51" t="str">
         <v>00000000000000000000000000000000</v>
@@ -2150,7 +2150,7 @@
         <v>0</v>
       </c>
       <c r="H51" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I51">
         <v>0</v>
@@ -2164,7 +2164,7 @@
     </row>
     <row r="52">
       <c r="A52" t="str">
-        <v>00000000000000000000000100011100</v>
+        <v>00000000000000000000000001010111</v>
       </c>
       <c r="B52" t="str">
         <v>00000000000000000000000000000000</v>
@@ -2185,7 +2185,7 @@
         <v>0</v>
       </c>
       <c r="H52" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I52">
         <v>0</v>
@@ -2199,10 +2199,10 @@
     </row>
     <row r="53">
       <c r="A53" t="str">
-        <v>00101110001110100000000000000111</v>
+        <v>00000000000000000000000001111011</v>
       </c>
       <c r="B53" t="str">
-        <v>00100000111111000000010110001101</v>
+        <v>00000000000000000000000000000000</v>
       </c>
       <c r="C53" t="str">
         <v>00000000000000000000000000000000</v>
@@ -2211,7 +2211,7 @@
         <v>00000000000000000000000000000000</v>
       </c>
       <c r="E53" t="str">
-        <v>00100001011110100000000000110011</v>
+        <v>00000000000000000000000000000000</v>
       </c>
       <c r="F53" t="b">
         <v>0</v>
@@ -2234,10 +2234,10 @@
     </row>
     <row r="54">
       <c r="A54" t="str">
-        <v>00101110001110100000000000000010</v>
+        <v>00000000000000000000000000001110</v>
       </c>
       <c r="B54" t="str">
-        <v>00100000111111000000011001110111</v>
+        <v>00000000000000000000000000000000</v>
       </c>
       <c r="C54" t="str">
         <v>00000000000000000000000000000000</v>
@@ -2246,7 +2246,7 @@
         <v>00000000000000000000000000000000</v>
       </c>
       <c r="E54" t="str">
-        <v>00100001011110100000000000110100</v>
+        <v>00000000000000000000000000000000</v>
       </c>
       <c r="F54" t="b">
         <v>0</v>
@@ -2269,7 +2269,7 @@
     </row>
     <row r="55">
       <c r="A55" t="str">
-        <v>00000000000000000000000000010011</v>
+        <v>00000000000000000000000001111001</v>
       </c>
       <c r="B55" t="str">
         <v>00000000000000000000000000000000</v>
@@ -2290,7 +2290,7 @@
         <v>0</v>
       </c>
       <c r="H55" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I55">
         <v>0</v>
@@ -2304,10 +2304,10 @@
     </row>
     <row r="56">
       <c r="A56" t="str">
-        <v>00101110001110100000000000001010</v>
+        <v>00000000000000000000000000100110</v>
       </c>
       <c r="B56" t="str">
-        <v>00100000111111000000001010101001</v>
+        <v>00000000000000000000000000000000</v>
       </c>
       <c r="C56" t="str">
         <v>00000000000000000000000000000000</v>
@@ -2316,7 +2316,7 @@
         <v>00000000000000000000000000000000</v>
       </c>
       <c r="E56" t="str">
-        <v>00100001011110100000000000110110</v>
+        <v>00000000000000000000000000000000</v>
       </c>
       <c r="F56" t="b">
         <v>0</v>
@@ -2360,7 +2360,7 @@
         <v>0</v>
       </c>
       <c r="H57" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I57">
         <v>0</v>
@@ -2374,10 +2374,10 @@
     </row>
     <row r="58">
       <c r="A58" t="str">
-        <v>00101110001110100000000000001010</v>
+        <v>00000000000000000000000011010110</v>
       </c>
       <c r="B58" t="str">
-        <v>00100000111111000000001001111001</v>
+        <v>00000000000000000000000000000000</v>
       </c>
       <c r="C58" t="str">
         <v>00000000000000000000000000000000</v>
@@ -2386,7 +2386,7 @@
         <v>00000000000000000000000000000000</v>
       </c>
       <c r="E58" t="str">
-        <v>00100001011110100000000000111000</v>
+        <v>00000000000000000000000000000000</v>
       </c>
       <c r="F58" t="b">
         <v>0</v>
@@ -2409,10 +2409,10 @@
     </row>
     <row r="59">
       <c r="A59" t="str">
-        <v>00101110001110100000000000001011</v>
+        <v>00000000000000000000000000110000</v>
       </c>
       <c r="B59" t="str">
-        <v>00100000111111000000010111000001</v>
+        <v>00000000000000000000000000000000</v>
       </c>
       <c r="C59" t="str">
         <v>00000000000000000000000000000000</v>
@@ -2421,7 +2421,7 @@
         <v>00000000000000000000000000000000</v>
       </c>
       <c r="E59" t="str">
-        <v>00100001011110100000000000111001</v>
+        <v>00000000000000000000000000000000</v>
       </c>
       <c r="F59" t="b">
         <v>0</v>
@@ -2430,7 +2430,7 @@
         <v>0</v>
       </c>
       <c r="H59" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I59">
         <v>0</v>
@@ -2444,10 +2444,10 @@
     </row>
     <row r="60">
       <c r="A60" t="str">
-        <v>00101110001110100000000000001011</v>
+        <v>00000000000000000000000000100000</v>
       </c>
       <c r="B60" t="str">
-        <v>00100000111111000000011101100111</v>
+        <v>00000000000000000000000000000000</v>
       </c>
       <c r="C60" t="str">
         <v>00000000000000000000000000000000</v>
@@ -2456,7 +2456,7 @@
         <v>00000000000000000000000000000000</v>
       </c>
       <c r="E60" t="str">
-        <v>00100001011110100000000000111010</v>
+        <v>00000000000000000000000000000000</v>
       </c>
       <c r="F60" t="b">
         <v>0</v>
@@ -2479,10 +2479,10 @@
     </row>
     <row r="61">
       <c r="A61" t="str">
-        <v>00101110001110100000000000001011</v>
+        <v>00000000000000000000000000101100</v>
       </c>
       <c r="B61" t="str">
-        <v>00100000111111000000100000100110</v>
+        <v>00000000000000000000000000000000</v>
       </c>
       <c r="C61" t="str">
         <v>00000000000000000000000000000000</v>
@@ -2491,7 +2491,7 @@
         <v>00000000000000000000000000000000</v>
       </c>
       <c r="E61" t="str">
-        <v>00100001011110100000000000111011</v>
+        <v>00000000000000000000000000000000</v>
       </c>
       <c r="F61" t="b">
         <v>0</v>
@@ -2500,7 +2500,7 @@
         <v>0</v>
       </c>
       <c r="H61" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I61">
         <v>0</v>
@@ -2514,10 +2514,10 @@
     </row>
     <row r="62">
       <c r="A62" t="str">
-        <v>00101110001110100000000000001011</v>
+        <v>00000000000000000000000001000000</v>
       </c>
       <c r="B62" t="str">
-        <v>00100000111111000000100111111110</v>
+        <v>00000000000000000000000000000000</v>
       </c>
       <c r="C62" t="str">
         <v>00000000000000000000000000000000</v>
@@ -2526,7 +2526,7 @@
         <v>00000000000000000000000000000000</v>
       </c>
       <c r="E62" t="str">
-        <v>00100001011110100000000000111100</v>
+        <v>00000000000000000000000000000000</v>
       </c>
       <c r="F62" t="b">
         <v>0</v>
@@ -2549,10 +2549,10 @@
     </row>
     <row r="63">
       <c r="A63" t="str">
-        <v>00101110001110100000000000000010</v>
+        <v>00000000000000000000000011001111</v>
       </c>
       <c r="B63" t="str">
-        <v>00100000111111000000011001000100</v>
+        <v>00000000000000000000000000000000</v>
       </c>
       <c r="C63" t="str">
         <v>00000000000000000000000000000000</v>
@@ -2561,7 +2561,7 @@
         <v>00000000000000000000000000000000</v>
       </c>
       <c r="E63" t="str">
-        <v>00100001011110100000000000111101</v>
+        <v>00000000000000000000000000000000</v>
       </c>
       <c r="F63" t="b">
         <v>0</v>
@@ -2584,10 +2584,10 @@
     </row>
     <row r="64">
       <c r="A64" t="str">
-        <v>00101110001110100000000000001100</v>
+        <v>00000000000000000000000000111100</v>
       </c>
       <c r="B64" t="str">
-        <v>00100000111111000000000100000001</v>
+        <v>00000000000000000000000000000000</v>
       </c>
       <c r="C64" t="str">
         <v>00000000000000000000000000000000</v>
@@ -2596,7 +2596,7 @@
         <v>00000000000000000000000000000000</v>
       </c>
       <c r="E64" t="str">
-        <v>00100001011110100000000000111110</v>
+        <v>00000000000000000000000000000000</v>
       </c>
       <c r="F64" t="b">
         <v>0</v>
@@ -2619,10 +2619,10 @@
     </row>
     <row r="65">
       <c r="A65" t="str">
-        <v>00101110001110100000000000001100</v>
+        <v>00000000000000000000000001011101</v>
       </c>
       <c r="B65" t="str">
-        <v>00100000111111000000011100011001</v>
+        <v>00000000000000000000000000000000</v>
       </c>
       <c r="C65" t="str">
         <v>00000000000000000000000000000000</v>
@@ -2631,7 +2631,7 @@
         <v>00000000000000000000000000000000</v>
       </c>
       <c r="E65" t="str">
-        <v>00100001011110100000000000111111</v>
+        <v>00000000000000000000000000000000</v>
       </c>
       <c r="F65" t="b">
         <v>0</v>
@@ -2654,10 +2654,10 @@
     </row>
     <row r="66">
       <c r="A66" t="str">
-        <v>00101110001110100000000000000010</v>
+        <v>00000000000000000000000001101111</v>
       </c>
       <c r="B66" t="str">
-        <v>00100000111111000000000000101100</v>
+        <v>00000000000000000000000000000000</v>
       </c>
       <c r="C66" t="str">
         <v>00000000000000000000000000000000</v>
@@ -2666,7 +2666,7 @@
         <v>00000000000000000000000000000000</v>
       </c>
       <c r="E66" t="str">
-        <v>00100001011110100000000001000000</v>
+        <v>00000000000000000000000000000000</v>
       </c>
       <c r="F66" t="b">
         <v>0</v>
@@ -2689,10 +2689,10 @@
     </row>
     <row r="67">
       <c r="A67" t="str">
-        <v>00101110001110100000000000000010</v>
+        <v>00000000000000000000000011100110</v>
       </c>
       <c r="B67" t="str">
-        <v>00100000111111000000001110000011</v>
+        <v>00000000000000000000000000000000</v>
       </c>
       <c r="C67" t="str">
         <v>00000000000000000000000000000000</v>
@@ -2701,7 +2701,7 @@
         <v>00000000000000000000000000000000</v>
       </c>
       <c r="E67" t="str">
-        <v>00100001011110100000000001000001</v>
+        <v>00000000000000000000000000000000</v>
       </c>
       <c r="F67" t="b">
         <v>0</v>
@@ -2710,7 +2710,7 @@
         <v>0</v>
       </c>
       <c r="H67" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I67">
         <v>0</v>
@@ -2724,10 +2724,10 @@
     </row>
     <row r="68">
       <c r="A68" t="str">
-        <v>00101110001110100000000000001111</v>
+        <v>00000000000000000000000000011010</v>
       </c>
       <c r="B68" t="str">
-        <v>00100000111111000000000001111111</v>
+        <v>00000000000000000000000000000000</v>
       </c>
       <c r="C68" t="str">
         <v>00000000000000000000000000000000</v>
@@ -2736,7 +2736,7 @@
         <v>00000000000000000000000000000000</v>
       </c>
       <c r="E68" t="str">
-        <v>00100001011110100000000001000010</v>
+        <v>00000000000000000000000000000000</v>
       </c>
       <c r="F68" t="b">
         <v>0</v>
@@ -2759,10 +2759,10 @@
     </row>
     <row r="69">
       <c r="A69" t="str">
-        <v>00101110001110100000000000000010</v>
+        <v>00000000000000000000000011010010</v>
       </c>
       <c r="B69" t="str">
-        <v>00100000111111000000101100111000</v>
+        <v>00000000000000000000000000000000</v>
       </c>
       <c r="C69" t="str">
         <v>00000000000000000000000000000000</v>
@@ -2771,7 +2771,7 @@
         <v>00000000000000000000000000000000</v>
       </c>
       <c r="E69" t="str">
-        <v>00100001011110100000000001000011</v>
+        <v>00000000000000000000000000000000</v>
       </c>
       <c r="F69" t="b">
         <v>0</v>
@@ -2794,10 +2794,10 @@
     </row>
     <row r="70">
       <c r="A70" t="str">
-        <v>00101110001110100000000000001111</v>
+        <v>00000000000000000000000000111111</v>
       </c>
       <c r="B70" t="str">
-        <v>00100000111111000000101000010111</v>
+        <v>00000000000000000000000000000000</v>
       </c>
       <c r="C70" t="str">
         <v>00000000000000000000000000000000</v>
@@ -2806,7 +2806,7 @@
         <v>00000000000000000000000000000000</v>
       </c>
       <c r="E70" t="str">
-        <v>00100001011110100000000001000100</v>
+        <v>00000000000000000000000000000000</v>
       </c>
       <c r="F70" t="b">
         <v>0</v>
@@ -2829,10 +2829,10 @@
     </row>
     <row r="71">
       <c r="A71" t="str">
-        <v>00101110001110100000000000000010</v>
+        <v>00000000000000000000000000001100</v>
       </c>
       <c r="B71" t="str">
-        <v>00100000111111000000010010011010</v>
+        <v>00000000000000000000000000000000</v>
       </c>
       <c r="C71" t="str">
         <v>00000000000000000000000000000000</v>
@@ -2841,7 +2841,7 @@
         <v>00000000000000000000000000000000</v>
       </c>
       <c r="E71" t="str">
-        <v>00100001011110100000000001000101</v>
+        <v>00000000000000000000000000000000</v>
       </c>
       <c r="F71" t="b">
         <v>0</v>
@@ -2850,7 +2850,7 @@
         <v>0</v>
       </c>
       <c r="H71" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I71">
         <v>0</v>
@@ -2864,10 +2864,10 @@
     </row>
     <row r="72">
       <c r="A72" t="str">
-        <v>00101110001110100000000000001111</v>
+        <v>00000000000000000000000000000000</v>
       </c>
       <c r="B72" t="str">
-        <v>00100000111111000000000101101100</v>
+        <v>00000000000000000000000000000000</v>
       </c>
       <c r="C72" t="str">
         <v>00000000000000000000000000000000</v>
@@ -2876,7 +2876,7 @@
         <v>00000000000000000000000000000000</v>
       </c>
       <c r="E72" t="str">
-        <v>00100001011110100000000001000110</v>
+        <v>00000000000000000000000000000000</v>
       </c>
       <c r="F72" t="b">
         <v>0</v>
@@ -2899,10 +2899,10 @@
     </row>
     <row r="73">
       <c r="A73" t="str">
-        <v>00101110001110100000000000001111</v>
+        <v>00000000000000000000000001110011</v>
       </c>
       <c r="B73" t="str">
-        <v>00100000111111000000100010000010</v>
+        <v>00000000000000000000000000000000</v>
       </c>
       <c r="C73" t="str">
         <v>00000000000000000000000000000000</v>
@@ -2911,7 +2911,7 @@
         <v>00000000000000000000000000000000</v>
       </c>
       <c r="E73" t="str">
-        <v>00100001011110100000000001000111</v>
+        <v>00000000000000000000000000000000</v>
       </c>
       <c r="F73" t="b">
         <v>0</v>
@@ -2934,10 +2934,10 @@
     </row>
     <row r="74">
       <c r="A74" t="str">
-        <v>00101110001110100000000000010001</v>
+        <v>00000000000000000000000011101101</v>
       </c>
       <c r="B74" t="str">
-        <v>00100000111111000000101100110010</v>
+        <v>00000000000000000000000000000000</v>
       </c>
       <c r="C74" t="str">
         <v>00000000000000000000000000000000</v>
@@ -2946,7 +2946,7 @@
         <v>00000000000000000000000000000000</v>
       </c>
       <c r="E74" t="str">
-        <v>00100001011110100000000001001000</v>
+        <v>00000000000000000000000000000000</v>
       </c>
       <c r="F74" t="b">
         <v>0</v>
@@ -2969,10 +2969,10 @@
     </row>
     <row r="75">
       <c r="A75" t="str">
-        <v>00101110001110100000000000010001</v>
+        <v>00000000000000000000000001110000</v>
       </c>
       <c r="B75" t="str">
-        <v>00100000111111000000011111100110</v>
+        <v>00000000000000000000000000000000</v>
       </c>
       <c r="C75" t="str">
         <v>00000000000000000000000000000000</v>
@@ -2981,7 +2981,7 @@
         <v>00000000000000000000000000000000</v>
       </c>
       <c r="E75" t="str">
-        <v>00100001011110100000000001001001</v>
+        <v>00000000000000000000000000000000</v>
       </c>
       <c r="F75" t="b">
         <v>0</v>
@@ -3004,10 +3004,10 @@
     </row>
     <row r="76">
       <c r="A76" t="str">
-        <v>00101110001110100000000000010001</v>
+        <v>00000000000000000000000001001011</v>
       </c>
       <c r="B76" t="str">
-        <v>00100000111111000000010101000001</v>
+        <v>00000000000000000000000000000000</v>
       </c>
       <c r="C76" t="str">
         <v>00000000000000000000000000000000</v>
@@ -3016,7 +3016,7 @@
         <v>00000000000000000000000000000000</v>
       </c>
       <c r="E76" t="str">
-        <v>00100001011110100000000001001010</v>
+        <v>00000000000000000000000000000000</v>
       </c>
       <c r="F76" t="b">
         <v>0</v>
@@ -3039,10 +3039,10 @@
     </row>
     <row r="77">
       <c r="A77" t="str">
-        <v>00101110001110100000000000000011</v>
+        <v>00000000000000000000000000010110</v>
       </c>
       <c r="B77" t="str">
-        <v>00100000111111000000011010110101</v>
+        <v>00000000000000000000000000000000</v>
       </c>
       <c r="C77" t="str">
         <v>00000000000000000000000000000000</v>
@@ -3051,7 +3051,7 @@
         <v>00000000000000000000000000000000</v>
       </c>
       <c r="E77" t="str">
-        <v>00100001011110100000000001001011</v>
+        <v>00000000000000000000000000000000</v>
       </c>
       <c r="F77" t="b">
         <v>0</v>
@@ -3074,10 +3074,10 @@
     </row>
     <row r="78">
       <c r="A78" t="str">
-        <v>00101110001110100000000000000000</v>
+        <v>00000000000000000000000000100010</v>
       </c>
       <c r="B78" t="str">
-        <v>00100000111111000000001111101111</v>
+        <v>00000000000000000000000000000000</v>
       </c>
       <c r="C78" t="str">
         <v>00000000000000000000000000000000</v>
@@ -3086,7 +3086,7 @@
         <v>00000000000000000000000000000000</v>
       </c>
       <c r="E78" t="str">
-        <v>00100001011110100000000001001100</v>
+        <v>00000000000000000000000000000000</v>
       </c>
       <c r="F78" t="b">
         <v>0</v>
@@ -3109,10 +3109,10 @@
     </row>
     <row r="79">
       <c r="A79" t="str">
-        <v>00101110001110100000000000010011</v>
+        <v>00000000000000000000000001111101</v>
       </c>
       <c r="B79" t="str">
-        <v>00100000111111000000100101111010</v>
+        <v>00000000000000000000000000000000</v>
       </c>
       <c r="C79" t="str">
         <v>00000000000000000000000000000000</v>
@@ -3121,7 +3121,7 @@
         <v>00000000000000000000000000000000</v>
       </c>
       <c r="E79" t="str">
-        <v>00100001011110100000000001001101</v>
+        <v>00000000000000000000000000000000</v>
       </c>
       <c r="F79" t="b">
         <v>0</v>
@@ -3144,10 +3144,10 @@
     </row>
     <row r="80">
       <c r="A80" t="str">
-        <v>00101110001110100000000000010011</v>
+        <v>00000000000000000000000010000010</v>
       </c>
       <c r="B80" t="str">
-        <v>00100000111111000000011011100000</v>
+        <v>00000000000000000000000000000000</v>
       </c>
       <c r="C80" t="str">
         <v>00000000000000000000000000000000</v>
@@ -3156,7 +3156,7 @@
         <v>00000000000000000000000000000000</v>
       </c>
       <c r="E80" t="str">
-        <v>00100001011110100000000001001110</v>
+        <v>00000000000000000000000000000000</v>
       </c>
       <c r="F80" t="b">
         <v>0</v>
@@ -3179,10 +3179,10 @@
     </row>
     <row r="81">
       <c r="A81" t="str">
-        <v>00101110001110100000000000010011</v>
+        <v>00000000000000000000000000110100</v>
       </c>
       <c r="B81" t="str">
-        <v>00100000111111000000011101011001</v>
+        <v>00000000000000000000000000000000</v>
       </c>
       <c r="C81" t="str">
         <v>00000000000000000000000000000000</v>
@@ -3191,7 +3191,7 @@
         <v>00000000000000000000000000000000</v>
       </c>
       <c r="E81" t="str">
-        <v>00100001011110100000000001001111</v>
+        <v>00000000000000000000000000000000</v>
       </c>
       <c r="F81" t="b">
         <v>0</v>
@@ -3214,10 +3214,10 @@
     </row>
     <row r="82">
       <c r="A82" t="str">
-        <v>00101110001110100000000000010101</v>
+        <v>00000000000000000000000000000110</v>
       </c>
       <c r="B82" t="str">
-        <v>00100000111111000000010100000101</v>
+        <v>00000000000000000000000000000000</v>
       </c>
       <c r="C82" t="str">
         <v>00000000000000000000000000000000</v>
@@ -3226,7 +3226,7 @@
         <v>00000000000000000000000000000000</v>
       </c>
       <c r="E82" t="str">
-        <v>00100001011110100000000001010000</v>
+        <v>00000000000000000000000000000000</v>
       </c>
       <c r="F82" t="b">
         <v>0</v>
@@ -3249,10 +3249,10 @@
     </row>
     <row r="83">
       <c r="A83" t="str">
-        <v>00101110001110100000000000000011</v>
+        <v>00000000000000000000000011110101</v>
       </c>
       <c r="B83" t="str">
-        <v>00100000111111000000100001001100</v>
+        <v>00000000000000000000000000000000</v>
       </c>
       <c r="C83" t="str">
         <v>00000000000000000000000000000000</v>
@@ -3261,7 +3261,7 @@
         <v>00000000000000000000000000000000</v>
       </c>
       <c r="E83" t="str">
-        <v>00100001011110100000000001010001</v>
+        <v>00000000000000000000000000000000</v>
       </c>
       <c r="F83" t="b">
         <v>0</v>
@@ -3284,10 +3284,10 @@
     </row>
     <row r="84">
       <c r="A84" t="str">
-        <v>00101110001110100000000000010101</v>
+        <v>00000000000000000000000001010011</v>
       </c>
       <c r="B84" t="str">
-        <v>00100000111111000000000101110100</v>
+        <v>00000000000000000000000000000000</v>
       </c>
       <c r="C84" t="str">
         <v>00000000000000000000000000000000</v>
@@ -3296,7 +3296,7 @@
         <v>00000000000000000000000000000000</v>
       </c>
       <c r="E84" t="str">
-        <v>00100001011110100000000001010010</v>
+        <v>00000000000000000000000000000000</v>
       </c>
       <c r="F84" t="b">
         <v>0</v>
@@ -3319,10 +3319,10 @@
     </row>
     <row r="85">
       <c r="A85" t="str">
-        <v>00101110001110100000000000000011</v>
+        <v>00000000000000000000000000101000</v>
       </c>
       <c r="B85" t="str">
-        <v>00100000111111000000011011110111</v>
+        <v>00000000000000000000000000000000</v>
       </c>
       <c r="C85" t="str">
         <v>00000000000000000000000000000000</v>
@@ -3331,7 +3331,7 @@
         <v>00000000000000000000000000000000</v>
       </c>
       <c r="E85" t="str">
-        <v>00100001011110100000000001010011</v>
+        <v>00000000000000000000000000000000</v>
       </c>
       <c r="F85" t="b">
         <v>0</v>
@@ -3354,10 +3354,10 @@
     </row>
     <row r="86">
       <c r="A86" t="str">
-        <v>00101110001110100000000000010110</v>
+        <v>00000000000000000000000011011010</v>
       </c>
       <c r="B86" t="str">
-        <v>00100000111111000000001100110101</v>
+        <v>00000000000000000000000000000000</v>
       </c>
       <c r="C86" t="str">
         <v>00000000000000000000000000000000</v>
@@ -3366,7 +3366,7 @@
         <v>00000000000000000000000000000000</v>
       </c>
       <c r="E86" t="str">
-        <v>00100001011110100000000001010100</v>
+        <v>00000000000000000000000000000000</v>
       </c>
       <c r="F86" t="b">
         <v>0</v>
@@ -3389,10 +3389,10 @@
     </row>
     <row r="87">
       <c r="A87" t="str">
-        <v>00101110001110100000000000010110</v>
+        <v>00000000000000000000000001010110</v>
       </c>
       <c r="B87" t="str">
-        <v>00100000111111000000011000001100</v>
+        <v>00000000000000000000000000000000</v>
       </c>
       <c r="C87" t="str">
         <v>00000000000000000000000000000000</v>
@@ -3401,7 +3401,7 @@
         <v>00000000000000000000000000000000</v>
       </c>
       <c r="E87" t="str">
-        <v>00100001011110100000000001010101</v>
+        <v>00000000000000000000000000000000</v>
       </c>
       <c r="F87" t="b">
         <v>0</v>
@@ -3424,10 +3424,10 @@
     </row>
     <row r="88">
       <c r="A88" t="str">
-        <v>00101110001110100000000000000101</v>
+        <v>00000000000000000000000001110101</v>
       </c>
       <c r="B88" t="str">
-        <v>00100000111111000000101001011101</v>
+        <v>00000000000000000000000000000000</v>
       </c>
       <c r="C88" t="str">
         <v>00000000000000000000000000000000</v>
@@ -3436,7 +3436,7 @@
         <v>00000000000000000000000000000000</v>
       </c>
       <c r="E88" t="str">
-        <v>00100001011110100000000001010110</v>
+        <v>00000000000000000000000000000000</v>
       </c>
       <c r="F88" t="b">
         <v>0</v>
@@ -3459,7 +3459,7 @@
     </row>
     <row r="89">
       <c r="A89" t="str">
-        <v>00000000000000000000000000110101</v>
+        <v>00000000000000000000000001001001</v>
       </c>
       <c r="B89" t="str">
         <v>00000000000000000000000000000000</v>
@@ -3480,7 +3480,7 @@
         <v>0</v>
       </c>
       <c r="H89" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I89">
         <v>0</v>
@@ -3494,10 +3494,10 @@
     </row>
     <row r="90">
       <c r="A90" t="str">
-        <v>00101110001110100000000000000101</v>
+        <v>00000000000000000000000011110010</v>
       </c>
       <c r="B90" t="str">
-        <v>00100000111111000000010000111000</v>
+        <v>00000000000000000000000000000000</v>
       </c>
       <c r="C90" t="str">
         <v>00000000000000000000000000000000</v>
@@ -3506,7 +3506,7 @@
         <v>00000000000000000000000000000000</v>
       </c>
       <c r="E90" t="str">
-        <v>00100001011110100000000001011000</v>
+        <v>00000000000000000000000000000000</v>
       </c>
       <c r="F90" t="b">
         <v>0</v>
@@ -3529,10 +3529,10 @@
     </row>
     <row r="91">
       <c r="A91" t="str">
-        <v>00101110001110100000000000010110</v>
+        <v>00000000000000000000000001110110</v>
       </c>
       <c r="B91" t="str">
-        <v>00100000111111000000000011011001</v>
+        <v>00000000000000000000000000000000</v>
       </c>
       <c r="C91" t="str">
         <v>00000000000000000000000000000000</v>
@@ -3541,7 +3541,7 @@
         <v>00000000000000000000000000000000</v>
       </c>
       <c r="E91" t="str">
-        <v>00100001011110100000000001011001</v>
+        <v>00000000000000000000000000000000</v>
       </c>
       <c r="F91" t="b">
         <v>0</v>
@@ -3564,10 +3564,10 @@
     </row>
     <row r="92">
       <c r="A92" t="str">
-        <v>00101110001110100000000000000101</v>
+        <v>00000000000000000000000011010011</v>
       </c>
       <c r="B92" t="str">
-        <v>00100000111111000000000001101001</v>
+        <v>00000000000000000000000000000000</v>
       </c>
       <c r="C92" t="str">
         <v>00000000000000000000000000000000</v>
@@ -3576,7 +3576,7 @@
         <v>00000000000000000000000000000000</v>
       </c>
       <c r="E92" t="str">
-        <v>00100001011110100000000001011010</v>
+        <v>00000000000000000000000000000000</v>
       </c>
       <c r="F92" t="b">
         <v>0</v>
@@ -3585,7 +3585,7 @@
         <v>0</v>
       </c>
       <c r="H92" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I92">
         <v>0</v>
@@ -3599,10 +3599,10 @@
     </row>
     <row r="93">
       <c r="A93" t="str">
-        <v>00101110001110100000000000010110</v>
+        <v>00000000000000000000000000110110</v>
       </c>
       <c r="B93" t="str">
-        <v>00100000111111000000010010100000</v>
+        <v>00000000000000000000000000000000</v>
       </c>
       <c r="C93" t="str">
         <v>00000000000000000000000000000000</v>
@@ -3611,7 +3611,7 @@
         <v>00000000000000000000000000000000</v>
       </c>
       <c r="E93" t="str">
-        <v>00100001011110100000000001011011</v>
+        <v>00000000000000000000000000000000</v>
       </c>
       <c r="F93" t="b">
         <v>0</v>
@@ -3634,10 +3634,10 @@
     </row>
     <row r="94">
       <c r="A94" t="str">
-        <v>00101110001110100000000000010110</v>
+        <v>00000000000000000000000001100110</v>
       </c>
       <c r="B94" t="str">
-        <v>00100000111111000000001110001100</v>
+        <v>00000000000000000000000000000000</v>
       </c>
       <c r="C94" t="str">
         <v>00000000000000000000000000000000</v>
@@ -3646,7 +3646,7 @@
         <v>00000000000000000000000000000000</v>
       </c>
       <c r="E94" t="str">
-        <v>00100001011110100000000001011100</v>
+        <v>00000000000000000000000000000000</v>
       </c>
       <c r="F94" t="b">
         <v>0</v>
@@ -3669,10 +3669,10 @@
     </row>
     <row r="95">
       <c r="A95" t="str">
-        <v>00101110001110100000000000010110</v>
+        <v>00000000000000000000000000010011</v>
       </c>
       <c r="B95" t="str">
-        <v>00100000111111000000000000010010</v>
+        <v>00000000000000000000000000000000</v>
       </c>
       <c r="C95" t="str">
         <v>00000000000000000000000000000000</v>
@@ -3681,7 +3681,7 @@
         <v>00000000000000000000000000000000</v>
       </c>
       <c r="E95" t="str">
-        <v>00100001011110100000000001011101</v>
+        <v>00000000000000000000000000000000</v>
       </c>
       <c r="F95" t="b">
         <v>0</v>
@@ -3704,10 +3704,10 @@
     </row>
     <row r="96">
       <c r="A96" t="str">
-        <v>00101110001110100000000000000101</v>
+        <v>00000000000000000000000000011100</v>
       </c>
       <c r="B96" t="str">
-        <v>00100000111111000000101010001110</v>
+        <v>00000000000000000000000000000000</v>
       </c>
       <c r="C96" t="str">
         <v>00000000000000000000000000000000</v>
@@ -3716,7 +3716,7 @@
         <v>00000000000000000000000000000000</v>
       </c>
       <c r="E96" t="str">
-        <v>00100001011110100000000001011110</v>
+        <v>00000000000000000000000000000000</v>
       </c>
       <c r="F96" t="b">
         <v>0</v>
@@ -3739,10 +3739,10 @@
     </row>
     <row r="97">
       <c r="A97" t="str">
-        <v>00101110001110100000000000000101</v>
+        <v>00000000000000000000000000110101</v>
       </c>
       <c r="B97" t="str">
-        <v>00100000111111000000100001111110</v>
+        <v>00000000000000000000000000000000</v>
       </c>
       <c r="C97" t="str">
         <v>00000000000000000000000000000000</v>
@@ -3751,7 +3751,7 @@
         <v>00000000000000000000000000000000</v>
       </c>
       <c r="E97" t="str">
-        <v>00100001011110100000000001011111</v>
+        <v>00000000000000000000000000000000</v>
       </c>
       <c r="F97" t="b">
         <v>0</v>
@@ -3774,10 +3774,10 @@
     </row>
     <row r="98">
       <c r="A98" t="str">
-        <v>00101110001110100000000000010111</v>
+        <v>00000000000000000000000011110100</v>
       </c>
       <c r="B98" t="str">
-        <v>00100000111111000000010110110100</v>
+        <v>00000000000000000000000000000000</v>
       </c>
       <c r="C98" t="str">
         <v>00000000000000000000000000000000</v>
@@ -3786,7 +3786,7 @@
         <v>00000000000000000000000000000000</v>
       </c>
       <c r="E98" t="str">
-        <v>00100001011110100000000001100000</v>
+        <v>00000000000000000000000000000000</v>
       </c>
       <c r="F98" t="b">
         <v>0</v>
@@ -3809,10 +3809,10 @@
     </row>
     <row r="99">
       <c r="A99" t="str">
-        <v>00101110001110100000000000010111</v>
+        <v>00000000000000000000000001101001</v>
       </c>
       <c r="B99" t="str">
-        <v>00100000111111000000100101001100</v>
+        <v>00000000000000000000000000000000</v>
       </c>
       <c r="C99" t="str">
         <v>00000000000000000000000000000000</v>
@@ -3821,7 +3821,7 @@
         <v>00000000000000000000000000000000</v>
       </c>
       <c r="E99" t="str">
-        <v>00100001011110100000000001100001</v>
+        <v>00000000000000000000000000000000</v>
       </c>
       <c r="F99" t="b">
         <v>0</v>
@@ -3844,10 +3844,10 @@
     </row>
     <row r="100">
       <c r="A100" t="str">
-        <v>00101110001110100000000000000101</v>
+        <v>00000000000000000000000010000111</v>
       </c>
       <c r="B100" t="str">
-        <v>00100000111111000000010110110000</v>
+        <v>00000000000000000000000000000000</v>
       </c>
       <c r="C100" t="str">
         <v>00000000000000000000000000000000</v>
@@ -3856,7 +3856,7 @@
         <v>00000000000000000000000000000000</v>
       </c>
       <c r="E100" t="str">
-        <v>00100001011110100000000001100010</v>
+        <v>00000000000000000000000000000000</v>
       </c>
       <c r="F100" t="b">
         <v>0</v>
@@ -3865,7 +3865,7 @@
         <v>0</v>
       </c>
       <c r="H100" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I100">
         <v>0</v>
@@ -3879,10 +3879,10 @@
     </row>
     <row r="101">
       <c r="A101" t="str">
-        <v>00101110001110100000000000011001</v>
+        <v>00000000000000000000000000101110</v>
       </c>
       <c r="B101" t="str">
-        <v>00100000111111000000000000010000</v>
+        <v>00000000000000000000000000000000</v>
       </c>
       <c r="C101" t="str">
         <v>00000000000000000000000000000000</v>
@@ -3891,7 +3891,7 @@
         <v>00000000000000000000000000000000</v>
       </c>
       <c r="E101" t="str">
-        <v>00100001011110100000000001100011</v>
+        <v>00000000000000000000000000000000</v>
       </c>
       <c r="F101" t="b">
         <v>0</v>
@@ -3914,10 +3914,10 @@
     </row>
     <row r="102">
       <c r="A102" t="str">
-        <v>00101110001110100000000000011010</v>
+        <v>00000000000000000000000010111110</v>
       </c>
       <c r="B102" t="str">
-        <v>00100000111111000000000111101100</v>
+        <v>00000000000000000000000000000000</v>
       </c>
       <c r="C102" t="str">
         <v>00000000000000000000000000000000</v>
@@ -3926,7 +3926,7 @@
         <v>00000000000000000000000000000000</v>
       </c>
       <c r="E102" t="str">
-        <v>00100001011110100000000001100100</v>
+        <v>00000000000000000000000000000000</v>
       </c>
       <c r="F102" t="b">
         <v>0</v>
@@ -3949,10 +3949,10 @@
     </row>
     <row r="103">
       <c r="A103" t="str">
-        <v>00101110001110100000000000011010</v>
+        <v>00000000000000000000000010010011</v>
       </c>
       <c r="B103" t="str">
-        <v>00100000111111000000101100001101</v>
+        <v>00000000000000000000000000000000</v>
       </c>
       <c r="C103" t="str">
         <v>00000000000000000000000000000000</v>
@@ -3961,7 +3961,7 @@
         <v>00000000000000000000000000000000</v>
       </c>
       <c r="E103" t="str">
-        <v>00100001011110100000000001100101</v>
+        <v>00000000000000000000000000000000</v>
       </c>
       <c r="F103" t="b">
         <v>0</v>
@@ -3984,10 +3984,10 @@
     </row>
     <row r="104">
       <c r="A104" t="str">
-        <v>00101110001110100000000000011010</v>
+        <v>00000000000000000000000010001011</v>
       </c>
       <c r="B104" t="str">
-        <v>00100000111111000000100101110110</v>
+        <v>00000000000000000000000000000000</v>
       </c>
       <c r="C104" t="str">
         <v>00000000000000000000000000000000</v>
@@ -3996,7 +3996,7 @@
         <v>00000000000000000000000000000000</v>
       </c>
       <c r="E104" t="str">
-        <v>00100001011110100000000001100110</v>
+        <v>00000000000000000000000000000000</v>
       </c>
       <c r="F104" t="b">
         <v>0</v>
@@ -4019,10 +4019,10 @@
     </row>
     <row r="105">
       <c r="A105" t="str">
-        <v>00101110001110100000000000011010</v>
+        <v>00000000000000000000000000001010</v>
       </c>
       <c r="B105" t="str">
-        <v>00100000111111000000000010110111</v>
+        <v>00000000000000000000000000000000</v>
       </c>
       <c r="C105" t="str">
         <v>00000000000000000000000000000000</v>
@@ -4031,7 +4031,7 @@
         <v>00000000000000000000000000000000</v>
       </c>
       <c r="E105" t="str">
-        <v>00100001011110100000000001100111</v>
+        <v>00000000000000000000000000000000</v>
       </c>
       <c r="F105" t="b">
         <v>0</v>
@@ -4054,10 +4054,10 @@
     </row>
     <row r="106">
       <c r="A106" t="str">
-        <v>00101110001110100000000000011010</v>
+        <v>00000000000000000000000000001011</v>
       </c>
       <c r="B106" t="str">
-        <v>00100000111111000000011000110101</v>
+        <v>00000000000000000000000000000000</v>
       </c>
       <c r="C106" t="str">
         <v>00000000000000000000000000000000</v>
@@ -4066,7 +4066,7 @@
         <v>00000000000000000000000000000000</v>
       </c>
       <c r="E106" t="str">
-        <v>00100001011110100000000001101000</v>
+        <v>00000000000000000000000000000000</v>
       </c>
       <c r="F106" t="b">
         <v>0</v>
@@ -4075,7 +4075,7 @@
         <v>0</v>
       </c>
       <c r="H106" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I106">
         <v>0</v>
@@ -4089,10 +4089,10 @@
     </row>
     <row r="107">
       <c r="A107" t="str">
-        <v>00101110001110100000000000011010</v>
+        <v>00000000000000000000000001010001</v>
       </c>
       <c r="B107" t="str">
-        <v>00100000111111000000011001000011</v>
+        <v>00000000000000000000000000000000</v>
       </c>
       <c r="C107" t="str">
         <v>00000000000000000000000000000000</v>
@@ -4101,7 +4101,7 @@
         <v>00000000000000000000000000000000</v>
       </c>
       <c r="E107" t="str">
-        <v>00100001011110100000000001101001</v>
+        <v>00000000000000000000000000000000</v>
       </c>
       <c r="F107" t="b">
         <v>0</v>
@@ -4124,10 +4124,10 @@
     </row>
     <row r="108">
       <c r="A108" t="str">
-        <v>00101110001110100000000000000101</v>
+        <v>00000000000000000000000001100111</v>
       </c>
       <c r="B108" t="str">
-        <v>00100000111111000000001110101100</v>
+        <v>00000000000000000000000000000000</v>
       </c>
       <c r="C108" t="str">
         <v>00000000000000000000000000000000</v>
@@ -4136,7 +4136,7 @@
         <v>00000000000000000000000000000000</v>
       </c>
       <c r="E108" t="str">
-        <v>00100001011110100000000001101010</v>
+        <v>00000000000000000000000000000000</v>
       </c>
       <c r="F108" t="b">
         <v>0</v>
@@ -4159,10 +4159,10 @@
     </row>
     <row r="109">
       <c r="A109" t="str">
-        <v>00101110001110100000000000000101</v>
+        <v>00000000000000000000000011000011</v>
       </c>
       <c r="B109" t="str">
-        <v>00100000111111000000011111101110</v>
+        <v>00000000000000000000000000000000</v>
       </c>
       <c r="C109" t="str">
         <v>00000000000000000000000000000000</v>
@@ -4171,7 +4171,7 @@
         <v>00000000000000000000000000000000</v>
       </c>
       <c r="E109" t="str">
-        <v>00100001011110100000000001101011</v>
+        <v>00000000000000000000000000000000</v>
       </c>
       <c r="F109" t="b">
         <v>0</v>
@@ -4194,10 +4194,10 @@
     </row>
     <row r="110">
       <c r="A110" t="str">
-        <v>00101110001110100000000000011010</v>
+        <v>00000000000000000000000001101110</v>
       </c>
       <c r="B110" t="str">
-        <v>00100000111111000000010111001101</v>
+        <v>00000000000000000000000000000000</v>
       </c>
       <c r="C110" t="str">
         <v>00000000000000000000000000000000</v>
@@ -4206,7 +4206,7 @@
         <v>00000000000000000000000000000000</v>
       </c>
       <c r="E110" t="str">
-        <v>00100001011110100000000001101100</v>
+        <v>00000000000000000000000000000000</v>
       </c>
       <c r="F110" t="b">
         <v>0</v>
@@ -4229,7 +4229,7 @@
     </row>
     <row r="111">
       <c r="A111" t="str">
-        <v>00000000000000000000000011100001</v>
+        <v>00000000000000000000000001101000</v>
       </c>
       <c r="B111" t="str">
         <v>00000000000000000000000000000000</v>
@@ -4264,10 +4264,10 @@
     </row>
     <row r="112">
       <c r="A112" t="str">
-        <v>00101110001110100000000000011011</v>
+        <v>00000000000000000000000011101000</v>
       </c>
       <c r="B112" t="str">
-        <v>00100000111111000000100111101010</v>
+        <v>00000000000000000000000000000000</v>
       </c>
       <c r="C112" t="str">
         <v>00000000000000000000000000000000</v>
@@ -4276,7 +4276,7 @@
         <v>00000000000000000000000000000000</v>
       </c>
       <c r="E112" t="str">
-        <v>00100001011110100000000001101110</v>
+        <v>00000000000000000000000000000000</v>
       </c>
       <c r="F112" t="b">
         <v>0</v>
@@ -4299,10 +4299,10 @@
     </row>
     <row r="113">
       <c r="A113" t="str">
-        <v>00101110001110100000000000011011</v>
+        <v>00000000000000000000000001000010</v>
       </c>
       <c r="B113" t="str">
-        <v>00100000111111000000101001111000</v>
+        <v>00000000000000000000000000000000</v>
       </c>
       <c r="C113" t="str">
         <v>00000000000000000000000000000000</v>
@@ -4311,7 +4311,7 @@
         <v>00000000000000000000000000000000</v>
       </c>
       <c r="E113" t="str">
-        <v>00100001011110100000000001101111</v>
+        <v>00000000000000000000000000000000</v>
       </c>
       <c r="F113" t="b">
         <v>0</v>
@@ -4334,10 +4334,10 @@
     </row>
     <row r="114">
       <c r="A114" t="str">
-        <v>00101110001110100000000000011011</v>
+        <v>00000000000000000000000010000000</v>
       </c>
       <c r="B114" t="str">
-        <v>00100000111111000000100110101001</v>
+        <v>00000000000000000000000000000000</v>
       </c>
       <c r="C114" t="str">
         <v>00000000000000000000000000000000</v>
@@ -4346,7 +4346,7 @@
         <v>00000000000000000000000000000000</v>
       </c>
       <c r="E114" t="str">
-        <v>00100001011110100000000001110000</v>
+        <v>00000000000000000000000000000000</v>
       </c>
       <c r="F114" t="b">
         <v>0</v>
@@ -4369,10 +4369,10 @@
     </row>
     <row r="115">
       <c r="A115" t="str">
-        <v>00101110001110100000000000011100</v>
+        <v>00000000000000000000000011101111</v>
       </c>
       <c r="B115" t="str">
-        <v>00100000111111000000101011000110</v>
+        <v>00000000000000000000000000000000</v>
       </c>
       <c r="C115" t="str">
         <v>00000000000000000000000000000000</v>
@@ -4381,7 +4381,7 @@
         <v>00000000000000000000000000000000</v>
       </c>
       <c r="E115" t="str">
-        <v>00100001011110100000000001110001</v>
+        <v>00000000000000000000000000000000</v>
       </c>
       <c r="F115" t="b">
         <v>0</v>
@@ -4404,10 +4404,10 @@
     </row>
     <row r="116">
       <c r="A116" t="str">
-        <v>00101110001110100000000000011100</v>
+        <v>00000000000000000000000001111110</v>
       </c>
       <c r="B116" t="str">
-        <v>00100000111111000000100010110101</v>
+        <v>00000000000000000000000000000000</v>
       </c>
       <c r="C116" t="str">
         <v>00000000000000000000000000000000</v>
@@ -4416,7 +4416,7 @@
         <v>00000000000000000000000000000000</v>
       </c>
       <c r="E116" t="str">
-        <v>00100001011110100000000001110010</v>
+        <v>00000000000000000000000000000000</v>
       </c>
       <c r="F116" t="b">
         <v>0</v>
@@ -4439,10 +4439,10 @@
     </row>
     <row r="117">
       <c r="A117" t="str">
-        <v>00101110001110100000000000011100</v>
+        <v>00000000000000000000000011101100</v>
       </c>
       <c r="B117" t="str">
-        <v>00100000111111000000100010000101</v>
+        <v>00000000000000000000000000000000</v>
       </c>
       <c r="C117" t="str">
         <v>00000000000000000000000000000000</v>
@@ -4451,7 +4451,7 @@
         <v>00000000000000000000000000000000</v>
       </c>
       <c r="E117" t="str">
-        <v>00100001011110100000000001110011</v>
+        <v>00000000000000000000000000000000</v>
       </c>
       <c r="F117" t="b">
         <v>0</v>
@@ -4474,10 +4474,10 @@
     </row>
     <row r="118">
       <c r="A118" t="str">
-        <v>00101110001110100000000000011100</v>
+        <v>00000000000000000000000001000011</v>
       </c>
       <c r="B118" t="str">
-        <v>00100000111111000000010100010110</v>
+        <v>00000000000000000000000000000000</v>
       </c>
       <c r="C118" t="str">
         <v>00000000000000000000000000000000</v>
@@ -4486,7 +4486,7 @@
         <v>00000000000000000000000000000000</v>
       </c>
       <c r="E118" t="str">
-        <v>00100001011110100000000001110100</v>
+        <v>00000000000000000000000000000000</v>
       </c>
       <c r="F118" t="b">
         <v>0</v>
@@ -4509,10 +4509,10 @@
     </row>
     <row r="119">
       <c r="A119" t="str">
-        <v>00101110001110100000000000011100</v>
+        <v>00000000000000000000000010001001</v>
       </c>
       <c r="B119" t="str">
-        <v>00100000111111000000010001001100</v>
+        <v>00000000000000000000000000000000</v>
       </c>
       <c r="C119" t="str">
         <v>00000000000000000000000000000000</v>
@@ -4521,7 +4521,7 @@
         <v>00000000000000000000000000000000</v>
       </c>
       <c r="E119" t="str">
-        <v>00100001011110100000000001110101</v>
+        <v>00000000000000000000000000000000</v>
       </c>
       <c r="F119" t="b">
         <v>0</v>
@@ -4544,10 +4544,10 @@
     </row>
     <row r="120">
       <c r="A120" t="str">
-        <v>00101110001110100000000000011101</v>
+        <v>00000000000000000000000000000100</v>
       </c>
       <c r="B120" t="str">
-        <v>00100000111111000000000110000111</v>
+        <v>00000000000000000000000000000000</v>
       </c>
       <c r="C120" t="str">
         <v>00000000000000000000000000000000</v>
@@ -4556,7 +4556,7 @@
         <v>00000000000000000000000000000000</v>
       </c>
       <c r="E120" t="str">
-        <v>00100001011110100000000001110110</v>
+        <v>00000000000000000000000000000000</v>
       </c>
       <c r="F120" t="b">
         <v>0</v>
@@ -4579,7 +4579,7 @@
     </row>
     <row r="121">
       <c r="A121" t="str">
-        <v>00000000000000000000000010101111</v>
+        <v>00000000000000000000000011011001</v>
       </c>
       <c r="B121" t="str">
         <v>00000000000000000000000000000000</v>
@@ -4600,7 +4600,7 @@
         <v>0</v>
       </c>
       <c r="H121" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I121">
         <v>0</v>
@@ -4614,10 +4614,10 @@
     </row>
     <row r="122">
       <c r="A122" t="str">
-        <v>00101110001110100000000000011101</v>
+        <v>00000000000000000000000000100101</v>
       </c>
       <c r="B122" t="str">
-        <v>00100000111111000000010111010100</v>
+        <v>00000000000000000000000000000000</v>
       </c>
       <c r="C122" t="str">
         <v>00000000000000000000000000000000</v>
@@ -4626,7 +4626,7 @@
         <v>00000000000000000000000000000000</v>
       </c>
       <c r="E122" t="str">
-        <v>00100001011110100000000001111000</v>
+        <v>00000000000000000000000000000000</v>
       </c>
       <c r="F122" t="b">
         <v>0</v>
@@ -4649,10 +4649,10 @@
     </row>
     <row r="123">
       <c r="A123" t="str">
-        <v>00101110001110100000000000011101</v>
+        <v>00000000000000000000000000110011</v>
       </c>
       <c r="B123" t="str">
-        <v>00100000111111000000000101011000</v>
+        <v>00000000000000000000000000000000</v>
       </c>
       <c r="C123" t="str">
         <v>00000000000000000000000000000000</v>
@@ -4661,7 +4661,7 @@
         <v>00000000000000000000000000000000</v>
       </c>
       <c r="E123" t="str">
-        <v>00100001011110100000000001111001</v>
+        <v>00000000000000000000000000000000</v>
       </c>
       <c r="F123" t="b">
         <v>0</v>
@@ -4684,10 +4684,10 @@
     </row>
     <row r="124">
       <c r="A124" t="str">
-        <v>00101110001110100000000000011101</v>
+        <v>00000000000000000000000010001101</v>
       </c>
       <c r="B124" t="str">
-        <v>00100000111111000000101100110011</v>
+        <v>00000000000000000000000000000000</v>
       </c>
       <c r="C124" t="str">
         <v>00000000000000000000000000000000</v>
@@ -4696,7 +4696,7 @@
         <v>00000000000000000000000000000000</v>
       </c>
       <c r="E124" t="str">
-        <v>00100001011110100000000001111010</v>
+        <v>00000000000000000000000000000000</v>
       </c>
       <c r="F124" t="b">
         <v>0</v>
@@ -4719,10 +4719,10 @@
     </row>
     <row r="125">
       <c r="A125" t="str">
-        <v>00101110001110100000000000011101</v>
+        <v>00000000000000000000000000110001</v>
       </c>
       <c r="B125" t="str">
-        <v>00100000111111000000001010011111</v>
+        <v>00000000000000000000000000000000</v>
       </c>
       <c r="C125" t="str">
         <v>00000000000000000000000000000000</v>
@@ -4731,7 +4731,7 @@
         <v>00000000000000000000000000000000</v>
       </c>
       <c r="E125" t="str">
-        <v>00100001011110100000000001111011</v>
+        <v>00000000000000000000000000000000</v>
       </c>
       <c r="F125" t="b">
         <v>0</v>
@@ -4754,10 +4754,10 @@
     </row>
     <row r="126">
       <c r="A126" t="str">
-        <v>00101110001110100000000000011101</v>
+        <v>00000000000000000000000000000111</v>
       </c>
       <c r="B126" t="str">
-        <v>00100000111111000000010111100110</v>
+        <v>00000000000000000000000000000000</v>
       </c>
       <c r="C126" t="str">
         <v>00000000000000000000000000000000</v>
@@ -4766,7 +4766,7 @@
         <v>00000000000000000000000000000000</v>
       </c>
       <c r="E126" t="str">
-        <v>00100001011110100000000001111100</v>
+        <v>00000000000000000000000000000000</v>
       </c>
       <c r="F126" t="b">
         <v>0</v>
@@ -4789,10 +4789,10 @@
     </row>
     <row r="127">
       <c r="A127" t="str">
-        <v>00101110001110100000000000011101</v>
+        <v>00000000000000000000000001001111</v>
       </c>
       <c r="B127" t="str">
-        <v>00100000111111000000010100110100</v>
+        <v>00000000000000000000000000000000</v>
       </c>
       <c r="C127" t="str">
         <v>00000000000000000000000000000000</v>
@@ -4801,7 +4801,7 @@
         <v>00000000000000000000000000000000</v>
       </c>
       <c r="E127" t="str">
-        <v>00100001011110100000000001111101</v>
+        <v>00000000000000000000000000000000</v>
       </c>
       <c r="F127" t="b">
         <v>0</v>
@@ -4824,10 +4824,10 @@
     </row>
     <row r="128">
       <c r="A128" t="str">
-        <v>00101110001110100000000000011101</v>
+        <v>00000000000000000000000001101100</v>
       </c>
       <c r="B128" t="str">
-        <v>00100000111111000000100100001001</v>
+        <v>00000000000000000000000000000000</v>
       </c>
       <c r="C128" t="str">
         <v>00000000000000000000000000000000</v>
@@ -4836,7 +4836,7 @@
         <v>00000000000000000000000000000000</v>
       </c>
       <c r="E128" t="str">
-        <v>00100001011110100000000001111110</v>
+        <v>00000000000000000000000000000000</v>
       </c>
       <c r="F128" t="b">
         <v>0</v>
@@ -4859,10 +4859,10 @@
     </row>
     <row r="129">
       <c r="A129" t="str">
-        <v>00101110001110100000000000000110</v>
+        <v>00000000000000000000000001110010</v>
       </c>
       <c r="B129" t="str">
-        <v>00100000111111000000010010110001</v>
+        <v>00000000000000000000000000000000</v>
       </c>
       <c r="C129" t="str">
         <v>00000000000000000000000000000000</v>
@@ -4871,7 +4871,7 @@
         <v>00000000000000000000000000000000</v>
       </c>
       <c r="E129" t="str">
-        <v>00100001011110100000000001111111</v>
+        <v>00000000000000000000000000000000</v>
       </c>
       <c r="F129" t="b">
         <v>0</v>
@@ -4894,10 +4894,10 @@
     </row>
     <row r="130">
       <c r="A130" t="str">
-        <v>00101110001110100000000000011110</v>
+        <v>00000000000000000000000000110111</v>
       </c>
       <c r="B130" t="str">
-        <v>00100000111111000000001010101010</v>
+        <v>00000000000000000000000000000000</v>
       </c>
       <c r="C130" t="str">
         <v>00000000000000000000000000000000</v>
@@ -4906,7 +4906,7 @@
         <v>00000000000000000000000000000000</v>
       </c>
       <c r="E130" t="str">
-        <v>00100001011110100000000010000000</v>
+        <v>00000000000000000000000000000000</v>
       </c>
       <c r="F130" t="b">
         <v>0</v>
@@ -4929,10 +4929,10 @@
     </row>
     <row r="131">
       <c r="A131" t="str">
-        <v>00101110001110100000000000011110</v>
+        <v>00000000000000000000000010010010</v>
       </c>
       <c r="B131" t="str">
-        <v>00100000111111000000011011110011</v>
+        <v>00000000000000000000000000000000</v>
       </c>
       <c r="C131" t="str">
         <v>00000000000000000000000000000000</v>
@@ -4941,7 +4941,7 @@
         <v>00000000000000000000000000000000</v>
       </c>
       <c r="E131" t="str">
-        <v>00100001011110100000000010000001</v>
+        <v>00000000000000000000000000000000</v>
       </c>
       <c r="F131" t="b">
         <v>0</v>
@@ -4950,7 +4950,7 @@
         <v>0</v>
       </c>
       <c r="H131" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I131">
         <v>0</v>
@@ -4964,10 +4964,10 @@
     </row>
     <row r="132">
       <c r="A132" t="str">
-        <v>00101110001110100000000000000110</v>
+        <v>00000000000000000000000001100101</v>
       </c>
       <c r="B132" t="str">
-        <v>00100000111111000000011100010101</v>
+        <v>00000000000000000000000000000000</v>
       </c>
       <c r="C132" t="str">
         <v>00000000000000000000000000000000</v>
@@ -4976,7 +4976,7 @@
         <v>00000000000000000000000000000000</v>
       </c>
       <c r="E132" t="str">
-        <v>00100001011110100000000010000010</v>
+        <v>00000000000000000000000000000000</v>
       </c>
       <c r="F132" t="b">
         <v>0</v>
@@ -4999,10 +4999,10 @@
     </row>
     <row r="133">
       <c r="A133" t="str">
-        <v>00101110001110100000000000000110</v>
+        <v>00000000000000000000000001011111</v>
       </c>
       <c r="B133" t="str">
-        <v>00100000111111000000000001001110</v>
+        <v>00000000000000000000000000000000</v>
       </c>
       <c r="C133" t="str">
         <v>00000000000000000000000000000000</v>
@@ -5011,7 +5011,7 @@
         <v>00000000000000000000000000000000</v>
       </c>
       <c r="E133" t="str">
-        <v>00100001011110100000000010000011</v>
+        <v>00000000000000000000000000000000</v>
       </c>
       <c r="F133" t="b">
         <v>0</v>
@@ -5034,10 +5034,10 @@
     </row>
     <row r="134">
       <c r="A134" t="str">
-        <v>00101110001110100000000000000110</v>
+        <v>00000000000000000000000011110110</v>
       </c>
       <c r="B134" t="str">
-        <v>00100000111111000000100110000110</v>
+        <v>00000000000000000000000000000000</v>
       </c>
       <c r="C134" t="str">
         <v>00000000000000000000000000000000</v>
@@ -5046,7 +5046,7 @@
         <v>00000000000000000000000000000000</v>
       </c>
       <c r="E134" t="str">
-        <v>00100001011110100000000010000100</v>
+        <v>00000000000000000000000000000000</v>
       </c>
       <c r="F134" t="b">
         <v>0</v>
@@ -5069,10 +5069,10 @@
     </row>
     <row r="135">
       <c r="A135" t="str">
-        <v>00101110001110100000000000011110</v>
+        <v>00000000000000000000000010000110</v>
       </c>
       <c r="B135" t="str">
-        <v>00100000111111000000100101101111</v>
+        <v>00000000000000000000000000000000</v>
       </c>
       <c r="C135" t="str">
         <v>00000000000000000000000000000000</v>
@@ -5081,7 +5081,7 @@
         <v>00000000000000000000000000000000</v>
       </c>
       <c r="E135" t="str">
-        <v>00100001011110100000000010000101</v>
+        <v>00000000000000000000000000000000</v>
       </c>
       <c r="F135" t="b">
         <v>0</v>
@@ -5090,7 +5090,7 @@
         <v>0</v>
       </c>
       <c r="H135" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I135">
         <v>0</v>
@@ -5104,10 +5104,10 @@
     </row>
     <row r="136">
       <c r="A136" t="str">
-        <v>00101110001110100000000000000110</v>
+        <v>00000000000000000000000010001100</v>
       </c>
       <c r="B136" t="str">
-        <v>00100000111111000000010101100000</v>
+        <v>00000000000000000000000000000000</v>
       </c>
       <c r="C136" t="str">
         <v>00000000000000000000000000000000</v>
@@ -5116,7 +5116,7 @@
         <v>00000000000000000000000000000000</v>
       </c>
       <c r="E136" t="str">
-        <v>00100001011110100000000010000110</v>
+        <v>00000000000000000000000000000000</v>
       </c>
       <c r="F136" t="b">
         <v>0</v>
@@ -5125,7 +5125,7 @@
         <v>0</v>
       </c>
       <c r="H136" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I136">
         <v>0</v>
@@ -5139,10 +5139,10 @@
     </row>
     <row r="137">
       <c r="A137" t="str">
-        <v>00101110001110100000000000000110</v>
+        <v>00000000000000000000000010010111</v>
       </c>
       <c r="B137" t="str">
-        <v>00100000111111000000101001011010</v>
+        <v>00000000000000000000000000000000</v>
       </c>
       <c r="C137" t="str">
         <v>00000000000000000000000000000000</v>
@@ -5151,7 +5151,7 @@
         <v>00000000000000000000000000000000</v>
       </c>
       <c r="E137" t="str">
-        <v>00100001011110100000000010000111</v>
+        <v>00000000000000000000000000000000</v>
       </c>
       <c r="F137" t="b">
         <v>0</v>
@@ -5160,7 +5160,7 @@
         <v>0</v>
       </c>
       <c r="H137" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I137">
         <v>0</v>
@@ -5174,10 +5174,10 @@
     </row>
     <row r="138">
       <c r="A138" t="str">
-        <v>00101110001110100000000000100000</v>
+        <v>00000000000000000000000000010111</v>
       </c>
       <c r="B138" t="str">
-        <v>00100000111111000000100111011111</v>
+        <v>00000000000000000000000000000000</v>
       </c>
       <c r="C138" t="str">
         <v>00000000000000000000000000000000</v>
@@ -5186,7 +5186,7 @@
         <v>00000000000000000000000000000000</v>
       </c>
       <c r="E138" t="str">
-        <v>00100001011110100000000010001000</v>
+        <v>00000000000000000000000000000000</v>
       </c>
       <c r="F138" t="b">
         <v>0</v>
@@ -5209,10 +5209,10 @@
     </row>
     <row r="139">
       <c r="A139" t="str">
-        <v>00101110001110100000000000100000</v>
+        <v>00000000000000000000000010010001</v>
       </c>
       <c r="B139" t="str">
-        <v>00100000111111000000000011010010</v>
+        <v>00000000000000000000000000000000</v>
       </c>
       <c r="C139" t="str">
         <v>00000000000000000000000000000000</v>
@@ -5221,7 +5221,7 @@
         <v>00000000000000000000000000000000</v>
       </c>
       <c r="E139" t="str">
-        <v>00100001011110100000000010001001</v>
+        <v>00000000000000000000000000000000</v>
       </c>
       <c r="F139" t="b">
         <v>0</v>
@@ -5244,10 +5244,10 @@
     </row>
     <row r="140">
       <c r="A140" t="str">
-        <v>00101110001110100000000000100000</v>
+        <v>00000000000000000000000000100011</v>
       </c>
       <c r="B140" t="str">
-        <v>00100000111111000000010110001010</v>
+        <v>00000000000000000000000000000000</v>
       </c>
       <c r="C140" t="str">
         <v>00000000000000000000000000000000</v>
@@ -5256,7 +5256,7 @@
         <v>00000000000000000000000000000000</v>
       </c>
       <c r="E140" t="str">
-        <v>00100001011110100000000010001010</v>
+        <v>00000000000000000000000000000000</v>
       </c>
       <c r="F140" t="b">
         <v>0</v>
@@ -5279,10 +5279,10 @@
     </row>
     <row r="141">
       <c r="A141" t="str">
-        <v>00101110001110100000000000100000</v>
+        <v>00000000000000000000000010000011</v>
       </c>
       <c r="B141" t="str">
-        <v>00100000111111000000011101111011</v>
+        <v>00000000000000000000000000000000</v>
       </c>
       <c r="C141" t="str">
         <v>00000000000000000000000000000000</v>
@@ -5291,7 +5291,7 @@
         <v>00000000000000000000000000000000</v>
       </c>
       <c r="E141" t="str">
-        <v>00100001011110100000000010001011</v>
+        <v>00000000000000000000000000000000</v>
       </c>
       <c r="F141" t="b">
         <v>0</v>
@@ -5314,10 +5314,10 @@
     </row>
     <row r="142">
       <c r="A142" t="str">
-        <v>00101110001110100000000000100000</v>
+        <v>00000000000000000000000010010100</v>
       </c>
       <c r="B142" t="str">
-        <v>00100000111111000000011010110010</v>
+        <v>00000000000000000000000000000000</v>
       </c>
       <c r="C142" t="str">
         <v>00000000000000000000000000000000</v>
@@ -5326,7 +5326,7 @@
         <v>00000000000000000000000000000000</v>
       </c>
       <c r="E142" t="str">
-        <v>00100001011110100000000010001100</v>
+        <v>00000000000000000000000000000000</v>
       </c>
       <c r="F142" t="b">
         <v>0</v>
@@ -5335,7 +5335,7 @@
         <v>0</v>
       </c>
       <c r="H142" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I142">
         <v>0</v>
@@ -5349,10 +5349,10 @@
     </row>
     <row r="143">
       <c r="A143" t="str">
-        <v>00101110001110100000000000100000</v>
+        <v>00000000000000000000000001011100</v>
       </c>
       <c r="B143" t="str">
-        <v>00100000111111000000011000111110</v>
+        <v>00000000000000000000000000000000</v>
       </c>
       <c r="C143" t="str">
         <v>00000000000000000000000000000000</v>
@@ -5361,7 +5361,7 @@
         <v>00000000000000000000000000000000</v>
       </c>
       <c r="E143" t="str">
-        <v>00100001011110100000000010001101</v>
+        <v>00000000000000000000000000000000</v>
       </c>
       <c r="F143" t="b">
         <v>0</v>
@@ -5384,10 +5384,10 @@
     </row>
     <row r="144">
       <c r="A144" t="str">
-        <v>00101110001110100000000000100000</v>
+        <v>00000000000000000000000000010010</v>
       </c>
       <c r="B144" t="str">
-        <v>00100000111111000000000000000111</v>
+        <v>00000000000000000000000000000000</v>
       </c>
       <c r="C144" t="str">
         <v>00000000000000000000000000000000</v>
@@ -5396,7 +5396,7 @@
         <v>00000000000000000000000000000000</v>
       </c>
       <c r="E144" t="str">
-        <v>00100001011110100000000010001110</v>
+        <v>00000000000000000000000000000000</v>
       </c>
       <c r="F144" t="b">
         <v>0</v>
@@ -5419,10 +5419,10 @@
     </row>
     <row r="145">
       <c r="A145" t="str">
-        <v>00101110001110100000000000100000</v>
+        <v>00000000000000000000000000010000</v>
       </c>
       <c r="B145" t="str">
-        <v>00100000111111000000011100001010</v>
+        <v>00000000000000000000000000000000</v>
       </c>
       <c r="C145" t="str">
         <v>00000000000000000000000000000000</v>
@@ -5431,7 +5431,7 @@
         <v>00000000000000000000000000000000</v>
       </c>
       <c r="E145" t="str">
-        <v>00100001011110100000000010001111</v>
+        <v>00000000000000000000000000000000</v>
       </c>
       <c r="F145" t="b">
         <v>0</v>
@@ -5454,10 +5454,10 @@
     </row>
     <row r="146">
       <c r="A146" t="str">
-        <v>00101110001110100000000000100001</v>
+        <v>00000000000000000000000000111101</v>
       </c>
       <c r="B146" t="str">
-        <v>00100000111111000000100100000010</v>
+        <v>00000000000000000000000000000000</v>
       </c>
       <c r="C146" t="str">
         <v>00000000000000000000000000000000</v>
@@ -5466,7 +5466,7 @@
         <v>00000000000000000000000000000000</v>
       </c>
       <c r="E146" t="str">
-        <v>00100001011110100000000010010000</v>
+        <v>00000000000000000000000000000000</v>
       </c>
       <c r="F146" t="b">
         <v>0</v>
@@ -5489,10 +5489,10 @@
     </row>
     <row r="147">
       <c r="A147" t="str">
-        <v>00101110001110100000000000100001</v>
+        <v>00000000000000000000000001111010</v>
       </c>
       <c r="B147" t="str">
-        <v>00100000111111000000010111001110</v>
+        <v>00000000000000000000000000000000</v>
       </c>
       <c r="C147" t="str">
         <v>00000000000000000000000000000000</v>
@@ -5501,7 +5501,7 @@
         <v>00000000000000000000000000000000</v>
       </c>
       <c r="E147" t="str">
-        <v>00100001011110100000000010010001</v>
+        <v>00000000000000000000000000000000</v>
       </c>
       <c r="F147" t="b">
         <v>0</v>
@@ -5524,10 +5524,10 @@
     </row>
     <row r="148">
       <c r="A148" t="str">
-        <v>00101110001110100000000000100001</v>
+        <v>00000000000000000000000011000000</v>
       </c>
       <c r="B148" t="str">
-        <v>00100000111111000000001101011111</v>
+        <v>00000000000000000000000000000000</v>
       </c>
       <c r="C148" t="str">
         <v>00000000000000000000000000000000</v>
@@ -5536,7 +5536,7 @@
         <v>00000000000000000000000000000000</v>
       </c>
       <c r="E148" t="str">
-        <v>00100001011110100000000010010010</v>
+        <v>00000000000000000000000000000000</v>
       </c>
       <c r="F148" t="b">
         <v>0</v>
@@ -5545,7 +5545,7 @@
         <v>0</v>
       </c>
       <c r="H148" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I148">
         <v>0</v>
@@ -5559,10 +5559,10 @@
     </row>
     <row r="149">
       <c r="A149" t="str">
-        <v>00101110001110100000000000100001</v>
+        <v>00000000000000000000000011011100</v>
       </c>
       <c r="B149" t="str">
-        <v>00100000111111000000001011001101</v>
+        <v>00000000000000000000000000000000</v>
       </c>
       <c r="C149" t="str">
         <v>00000000000000000000000000000000</v>
@@ -5571,7 +5571,7 @@
         <v>00000000000000000000000000000000</v>
       </c>
       <c r="E149" t="str">
-        <v>00100001011110100000000010010011</v>
+        <v>00000000000000000000000000000000</v>
       </c>
       <c r="F149" t="b">
         <v>0</v>
@@ -5594,10 +5594,10 @@
     </row>
     <row r="150">
       <c r="A150" t="str">
-        <v>00101110001110100000000000100001</v>
+        <v>00000000000000000000000010101000</v>
       </c>
       <c r="B150" t="str">
-        <v>00100000111111000000001011000011</v>
+        <v>00000000000000000000000000000000</v>
       </c>
       <c r="C150" t="str">
         <v>00000000000000000000000000000000</v>
@@ -5606,7 +5606,7 @@
         <v>00000000000000000000000000000000</v>
       </c>
       <c r="E150" t="str">
-        <v>00100001011110100000000010010100</v>
+        <v>00000000000000000000000000000000</v>
       </c>
       <c r="F150" t="b">
         <v>0</v>
@@ -5615,7 +5615,7 @@
         <v>0</v>
       </c>
       <c r="H150" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I150">
         <v>0</v>
@@ -5629,10 +5629,10 @@
     </row>
     <row r="151">
       <c r="A151" t="str">
-        <v>00101110001110100000000000100001</v>
+        <v>00000000000000000000000001100010</v>
       </c>
       <c r="B151" t="str">
-        <v>00100000111111000000001011111101</v>
+        <v>00000000000000000000000000000000</v>
       </c>
       <c r="C151" t="str">
         <v>00000000000000000000000000000000</v>
@@ -5641,7 +5641,7 @@
         <v>00000000000000000000000000000000</v>
       </c>
       <c r="E151" t="str">
-        <v>00100001011110100000000010010101</v>
+        <v>00000000000000000000000000000000</v>
       </c>
       <c r="F151" t="b">
         <v>0</v>
@@ -5650,7 +5650,7 @@
         <v>0</v>
       </c>
       <c r="H151" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I151">
         <v>0</v>
@@ -5664,10 +5664,10 @@
     </row>
     <row r="152">
       <c r="A152" t="str">
-        <v>00101110001110100000000000100001</v>
+        <v>00000000000000000000000011010001</v>
       </c>
       <c r="B152" t="str">
-        <v>00100000111111000000101110101111</v>
+        <v>00000000000000000000000000000000</v>
       </c>
       <c r="C152" t="str">
         <v>00000000000000000000000000000000</v>
@@ -5676,7 +5676,7 @@
         <v>00000000000000000000000000000000</v>
       </c>
       <c r="E152" t="str">
-        <v>00100001011110100000000010010110</v>
+        <v>00000000000000000000000000000000</v>
       </c>
       <c r="F152" t="b">
         <v>0</v>
@@ -5699,10 +5699,10 @@
     </row>
     <row r="153">
       <c r="A153" t="str">
-        <v>00101110001110100000000000100001</v>
+        <v>00000000000000000000000010101010</v>
       </c>
       <c r="B153" t="str">
-        <v>00100000111111000000101101110001</v>
+        <v>00000000000000000000000000000000</v>
       </c>
       <c r="C153" t="str">
         <v>00000000000000000000000000000000</v>
@@ -5711,7 +5711,7 @@
         <v>00000000000000000000000000000000</v>
       </c>
       <c r="E153" t="str">
-        <v>00100001011110100000000010010111</v>
+        <v>00000000000000000000000000000000</v>
       </c>
       <c r="F153" t="b">
         <v>0</v>
@@ -5720,7 +5720,7 @@
         <v>0</v>
       </c>
       <c r="H153" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I153">
         <v>0</v>
@@ -5734,10 +5734,10 @@
     </row>
     <row r="154">
       <c r="A154" t="str">
-        <v>00101110001110100000000000100001</v>
+        <v>00000000000000000000000011001101</v>
       </c>
       <c r="B154" t="str">
-        <v>00100000111111000000000011010011</v>
+        <v>00000000000000000000000000000000</v>
       </c>
       <c r="C154" t="str">
         <v>00000000000000000000000000000000</v>
@@ -5746,7 +5746,7 @@
         <v>00000000000000000000000000000000</v>
       </c>
       <c r="E154" t="str">
-        <v>00100001011110100000000010011000</v>
+        <v>00000000000000000000000000000000</v>
       </c>
       <c r="F154" t="b">
         <v>0</v>
@@ -5769,10 +5769,10 @@
     </row>
     <row r="155">
       <c r="A155" t="str">
-        <v>00101110001110100000000000000111</v>
+        <v>00000000000000000000000011000101</v>
       </c>
       <c r="B155" t="str">
-        <v>00100000111111000000000100101101</v>
+        <v>00000000000000000000000000000000</v>
       </c>
       <c r="C155" t="str">
         <v>00000000000000000000000000000000</v>
@@ -5781,7 +5781,7 @@
         <v>00000000000000000000000000000000</v>
       </c>
       <c r="E155" t="str">
-        <v>00100001011110100000000010011001</v>
+        <v>00000000000000000000000000000000</v>
       </c>
       <c r="F155" t="b">
         <v>0</v>
@@ -5790,7 +5790,7 @@
         <v>0</v>
       </c>
       <c r="H155" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I155">
         <v>0</v>
@@ -5804,10 +5804,10 @@
     </row>
     <row r="156">
       <c r="A156" t="str">
-        <v>00101110001110100000000000100011</v>
+        <v>00000000000000000000000011011110</v>
       </c>
       <c r="B156" t="str">
-        <v>00100000111111000000010110000101</v>
+        <v>00000000000000000000000000000000</v>
       </c>
       <c r="C156" t="str">
         <v>00000000000000000000000000000000</v>
@@ -5816,7 +5816,7 @@
         <v>00000000000000000000000000000000</v>
       </c>
       <c r="E156" t="str">
-        <v>00100001011110100000000010011010</v>
+        <v>00000000000000000000000000000000</v>
       </c>
       <c r="F156" t="b">
         <v>0</v>
@@ -5839,10 +5839,10 @@
     </row>
     <row r="157">
       <c r="A157" t="str">
-        <v>00101110001110100000000000100100</v>
+        <v>00000000000000000000000010011010</v>
       </c>
       <c r="B157" t="str">
-        <v>00100000111111000000000010100100</v>
+        <v>00000000000000000000000000000000</v>
       </c>
       <c r="C157" t="str">
         <v>00000000000000000000000000000000</v>
@@ -5851,7 +5851,7 @@
         <v>00000000000000000000000000000000</v>
       </c>
       <c r="E157" t="str">
-        <v>00100001011110100000000010011011</v>
+        <v>00000000000000000000000000000000</v>
       </c>
       <c r="F157" t="b">
         <v>0</v>
@@ -5874,10 +5874,10 @@
     </row>
     <row r="158">
       <c r="A158" t="str">
-        <v>00101110001110100000000000100100</v>
+        <v>00000000000000000000000010011011</v>
       </c>
       <c r="B158" t="str">
-        <v>00100000111111000000011111100001</v>
+        <v>00000000000000000000000000000000</v>
       </c>
       <c r="C158" t="str">
         <v>00000000000000000000000000000000</v>
@@ -5886,7 +5886,7 @@
         <v>00000000000000000000000000000000</v>
       </c>
       <c r="E158" t="str">
-        <v>00100001011110100000000010011100</v>
+        <v>00000000000000000000000000000000</v>
       </c>
       <c r="F158" t="b">
         <v>0</v>
@@ -5909,10 +5909,10 @@
     </row>
     <row r="159">
       <c r="A159" t="str">
-        <v>00101110001110100000000000100100</v>
+        <v>00000000000000000000000000001111</v>
       </c>
       <c r="B159" t="str">
-        <v>00100000111111000000011100111011</v>
+        <v>00000000000000000000000000000000</v>
       </c>
       <c r="C159" t="str">
         <v>00000000000000000000000000000000</v>
@@ -5921,7 +5921,7 @@
         <v>00000000000000000000000000000000</v>
       </c>
       <c r="E159" t="str">
-        <v>00100001011110100000000010011101</v>
+        <v>00000000000000000000000000000000</v>
       </c>
       <c r="F159" t="b">
         <v>0</v>
@@ -5930,7 +5930,7 @@
         <v>0</v>
       </c>
       <c r="H159" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I159">
         <v>0</v>
@@ -5944,10 +5944,10 @@
     </row>
     <row r="160">
       <c r="A160" t="str">
-        <v>00101110001110100000000000100100</v>
+        <v>00000000000000000000000010111010</v>
       </c>
       <c r="B160" t="str">
-        <v>00100000111111000000011001011100</v>
+        <v>00000000000000000000000000000000</v>
       </c>
       <c r="C160" t="str">
         <v>00000000000000000000000000000000</v>
@@ -5956,7 +5956,7 @@
         <v>00000000000000000000000000000000</v>
       </c>
       <c r="E160" t="str">
-        <v>00100001011110100000000010011110</v>
+        <v>00000000000000000000000000000000</v>
       </c>
       <c r="F160" t="b">
         <v>0</v>
@@ -5965,7 +5965,7 @@
         <v>0</v>
       </c>
       <c r="H160" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I160">
         <v>0</v>
@@ -5979,10 +5979,10 @@
     </row>
     <row r="161">
       <c r="A161" t="str">
-        <v>00101110001110100000000000100100</v>
+        <v>00000000000000000000000011000001</v>
       </c>
       <c r="B161" t="str">
-        <v>00100000111111000000010101111101</v>
+        <v>00000000000000000000000000000000</v>
       </c>
       <c r="C161" t="str">
         <v>00000000000000000000000000000000</v>
@@ -5991,7 +5991,7 @@
         <v>00000000000000000000000000000000</v>
       </c>
       <c r="E161" t="str">
-        <v>00100001011110100000000010011111</v>
+        <v>00000000000000000000000000000000</v>
       </c>
       <c r="F161" t="b">
         <v>0</v>
@@ -6014,7 +6014,7 @@
     </row>
     <row r="162">
       <c r="A162" t="str">
-        <v>00000000000000000000000010110001</v>
+        <v>00000000000000000000000001011010</v>
       </c>
       <c r="B162" t="str">
         <v>00000000000000000000000000000000</v>
@@ -6049,10 +6049,10 @@
     </row>
     <row r="163">
       <c r="A163" t="str">
-        <v>00101110001110100000000000100010</v>
+        <v>00000000000000000000000010111111</v>
       </c>
       <c r="B163" t="str">
-        <v>00100000111111000000100110011011</v>
+        <v>00000000000000000000000000000000</v>
       </c>
       <c r="C163" t="str">
         <v>00000000000000000000000000000000</v>
@@ -6061,7 +6061,7 @@
         <v>00000000000000000000000000000000</v>
       </c>
       <c r="E163" t="str">
-        <v>00100001011110100000000010100001</v>
+        <v>00000000000000000000000000000000</v>
       </c>
       <c r="F163" t="b">
         <v>0</v>
@@ -6084,10 +6084,10 @@
     </row>
     <row r="164">
       <c r="A164" t="str">
-        <v>00101110001110100000000000000111</v>
+        <v>00000000000000000000000010100001</v>
       </c>
       <c r="B164" t="str">
-        <v>00100000111111000000001111111101</v>
+        <v>00000000000000000000000000000000</v>
       </c>
       <c r="C164" t="str">
         <v>00000000000000000000000000000000</v>
@@ -6096,7 +6096,7 @@
         <v>00000000000000000000000000000000</v>
       </c>
       <c r="E164" t="str">
-        <v>00100001011110100000000010100010</v>
+        <v>00000000000000000000000000000000</v>
       </c>
       <c r="F164" t="b">
         <v>0</v>
@@ -6119,10 +6119,10 @@
     </row>
     <row r="165">
       <c r="A165" t="str">
-        <v>00101110001110100000000000000111</v>
+        <v>00000000000000000000000011000111</v>
       </c>
       <c r="B165" t="str">
-        <v>00100000111111000000000100010101</v>
+        <v>00000000000000000000000000000000</v>
       </c>
       <c r="C165" t="str">
         <v>00000000000000000000000000000000</v>
@@ -6131,7 +6131,7 @@
         <v>00000000000000000000000000000000</v>
       </c>
       <c r="E165" t="str">
-        <v>00100001011110100000000010100011</v>
+        <v>00000000000000000000000000000000</v>
       </c>
       <c r="F165" t="b">
         <v>0</v>
@@ -6140,7 +6140,7 @@
         <v>0</v>
       </c>
       <c r="H165" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I165">
         <v>0</v>
@@ -6154,10 +6154,10 @@
     </row>
     <row r="166">
       <c r="A166" t="str">
-        <v>00101110001110100000000000000111</v>
+        <v>00000000000000000000000011100011</v>
       </c>
       <c r="B166" t="str">
-        <v>00100000111111000000000111111001</v>
+        <v>00000000000000000000000000000000</v>
       </c>
       <c r="C166" t="str">
         <v>00000000000000000000000000000000</v>
@@ -6166,7 +6166,7 @@
         <v>00000000000000000000000000000000</v>
       </c>
       <c r="E166" t="str">
-        <v>00100001011110100000000010100100</v>
+        <v>00000000000000000000000000000000</v>
       </c>
       <c r="F166" t="b">
         <v>0</v>
@@ -6189,7 +6189,7 @@
     </row>
     <row r="167">
       <c r="A167" t="str">
-        <v>00000000000000000000000000110001</v>
+        <v>00000000000000000000000010100111</v>
       </c>
       <c r="B167" t="str">
         <v>00000000000000000000000000000000</v>
@@ -6224,10 +6224,10 @@
     </row>
     <row r="168">
       <c r="A168" t="str">
-        <v>00101110001110100000000000000111</v>
+        <v>00000000000000000000000011001011</v>
       </c>
       <c r="B168" t="str">
-        <v>00100000111111000000011111011001</v>
+        <v>00000000000000000000000000000000</v>
       </c>
       <c r="C168" t="str">
         <v>00000000000000000000000000000000</v>
@@ -6236,7 +6236,7 @@
         <v>00000000000000000000000000000000</v>
       </c>
       <c r="E168" t="str">
-        <v>00100001011110100000000010100110</v>
+        <v>00000000000000000000000000000000</v>
       </c>
       <c r="F168" t="b">
         <v>0</v>
@@ -6245,7 +6245,7 @@
         <v>0</v>
       </c>
       <c r="H168" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I168">
         <v>0</v>
@@ -6259,10 +6259,10 @@
     </row>
     <row r="169">
       <c r="A169" t="str">
-        <v>00101110001110100000000000000111</v>
+        <v>00000000000000000000000000111001</v>
       </c>
       <c r="B169" t="str">
-        <v>00100000111111000000100000111001</v>
+        <v>00000000000000000000000000000000</v>
       </c>
       <c r="C169" t="str">
         <v>00000000000000000000000000000000</v>
@@ -6271,7 +6271,7 @@
         <v>00000000000000000000000000000000</v>
       </c>
       <c r="E169" t="str">
-        <v>00100001011110100000000010100111</v>
+        <v>00000000000000000000000000000000</v>
       </c>
       <c r="F169" t="b">
         <v>0</v>
@@ -6280,7 +6280,7 @@
         <v>0</v>
       </c>
       <c r="H169" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I169">
         <v>0</v>
@@ -6294,10 +6294,10 @@
     </row>
     <row r="170">
       <c r="A170" t="str">
-        <v>00101110001110100000000000000111</v>
+        <v>00000000000000000000000011010101</v>
       </c>
       <c r="B170" t="str">
-        <v>00100000111111000000100000010101</v>
+        <v>00000000000000000000000000000000</v>
       </c>
       <c r="C170" t="str">
         <v>00000000000000000000000000000000</v>
@@ -6306,7 +6306,7 @@
         <v>00000000000000000000000000000000</v>
       </c>
       <c r="E170" t="str">
-        <v>00100001011110100000000010101000</v>
+        <v>00000000000000000000000000000000</v>
       </c>
       <c r="F170" t="b">
         <v>0</v>
@@ -6315,7 +6315,7 @@
         <v>0</v>
       </c>
       <c r="H170" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I170">
         <v>0</v>
@@ -6329,10 +6329,10 @@
     </row>
     <row r="171">
       <c r="A171" t="str">
-        <v>00101110001110100000000000000111</v>
+        <v>00000000000000000000000010110101</v>
       </c>
       <c r="B171" t="str">
-        <v>00100000111111000000001100110011</v>
+        <v>00000000000000000000000000000000</v>
       </c>
       <c r="C171" t="str">
         <v>00000000000000000000000000000000</v>
@@ -6341,7 +6341,7 @@
         <v>00000000000000000000000000000000</v>
       </c>
       <c r="E171" t="str">
-        <v>00100001011110100000000010101001</v>
+        <v>00000000000000000000000000000000</v>
       </c>
       <c r="F171" t="b">
         <v>0</v>
@@ -6350,7 +6350,7 @@
         <v>0</v>
       </c>
       <c r="H171" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I171">
         <v>0</v>
@@ -6364,10 +6364,10 @@
     </row>
     <row r="172">
       <c r="A172" t="str">
-        <v>00101110001110100000000000001010</v>
+        <v>00000000000000000000000011000100</v>
       </c>
       <c r="B172" t="str">
-        <v>00100000111111000000100000010111</v>
+        <v>00000000000000000000000000000000</v>
       </c>
       <c r="C172" t="str">
         <v>00000000000000000000000000000000</v>
@@ -6376,7 +6376,7 @@
         <v>00000000000000000000000000000000</v>
       </c>
       <c r="E172" t="str">
-        <v>00100001011110100000000010101010</v>
+        <v>00000000000000000000000000000000</v>
       </c>
       <c r="F172" t="b">
         <v>0</v>
@@ -6385,7 +6385,7 @@
         <v>0</v>
       </c>
       <c r="H172" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I172">
         <v>0</v>
@@ -6399,10 +6399,10 @@
     </row>
     <row r="173">
       <c r="A173" t="str">
-        <v>00101110001110100000000000001010</v>
+        <v>00000000000000000000000011100000</v>
       </c>
       <c r="B173" t="str">
-        <v>00100000111111000000100111110001</v>
+        <v>00000000000000000000000000000000</v>
       </c>
       <c r="C173" t="str">
         <v>00000000000000000000000000000000</v>
@@ -6411,7 +6411,7 @@
         <v>00000000000000000000000000000000</v>
       </c>
       <c r="E173" t="str">
-        <v>00100001011110100000000010101011</v>
+        <v>00000000000000000000000000000000</v>
       </c>
       <c r="F173" t="b">
         <v>0</v>
@@ -6434,10 +6434,10 @@
     </row>
     <row r="174">
       <c r="A174" t="str">
-        <v>00101110001110100000000000001010</v>
+        <v>00000000000000000000000010101011</v>
       </c>
       <c r="B174" t="str">
-        <v>00100000111111000000101110111101</v>
+        <v>00000000000000000000000000000000</v>
       </c>
       <c r="C174" t="str">
         <v>00000000000000000000000000000000</v>
@@ -6446,7 +6446,7 @@
         <v>00000000000000000000000000000000</v>
       </c>
       <c r="E174" t="str">
-        <v>00100001011110100000000010101100</v>
+        <v>00000000000000000000000000000000</v>
       </c>
       <c r="F174" t="b">
         <v>0</v>
@@ -6469,10 +6469,10 @@
     </row>
     <row r="175">
       <c r="A175" t="str">
-        <v>00101110001110100000000000001010</v>
+        <v>00000000000000000000000010101100</v>
       </c>
       <c r="B175" t="str">
-        <v>00100000111111000000001110001110</v>
+        <v>00000000000000000000000000000000</v>
       </c>
       <c r="C175" t="str">
         <v>00000000000000000000000000000000</v>
@@ -6481,7 +6481,7 @@
         <v>00000000000000000000000000000000</v>
       </c>
       <c r="E175" t="str">
-        <v>00100001011110100000000010101101</v>
+        <v>00000000000000000000000000000000</v>
       </c>
       <c r="F175" t="b">
         <v>0</v>
@@ -6490,7 +6490,7 @@
         <v>0</v>
       </c>
       <c r="H175" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I175">
         <v>0</v>
@@ -6504,10 +6504,10 @@
     </row>
     <row r="176">
       <c r="A176" t="str">
-        <v>00101110001110100000000000001010</v>
+        <v>00000000000000000000000100001001</v>
       </c>
       <c r="B176" t="str">
-        <v>00100000111111000000000111111011</v>
+        <v>00000000000000000000000000000000</v>
       </c>
       <c r="C176" t="str">
         <v>00000000000000000000000000000000</v>
@@ -6516,7 +6516,7 @@
         <v>00000000000000000000000000000000</v>
       </c>
       <c r="E176" t="str">
-        <v>00100001011110100000000010101110</v>
+        <v>00000000000000000000000000000000</v>
       </c>
       <c r="F176" t="b">
         <v>0</v>
@@ -6525,7 +6525,7 @@
         <v>0</v>
       </c>
       <c r="H176" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I176">
         <v>0</v>
@@ -6539,7 +6539,7 @@
     </row>
     <row r="177">
       <c r="A177" t="str">
-        <v>00000000000000000000000011110010</v>
+        <v>00000000000000000000000010111000</v>
       </c>
       <c r="B177" t="str">
         <v>00000000000000000000000000000000</v>
@@ -6574,7 +6574,7 @@
     </row>
     <row r="178">
       <c r="A178" t="str">
-        <v>00000000000000000000000001101101</v>
+        <v>00000000000000000000000000000101</v>
       </c>
       <c r="B178" t="str">
         <v>00000000000000000000000000000000</v>
@@ -6609,7 +6609,7 @@
     </row>
     <row r="179">
       <c r="A179" t="str">
-        <v>00000000000000000000000100101100</v>
+        <v>00000000000000000000000010011001</v>
       </c>
       <c r="B179" t="str">
         <v>00000000000000000000000000000000</v>
@@ -6644,10 +6644,10 @@
     </row>
     <row r="180">
       <c r="A180" t="str">
-        <v>00101110001110100000000000001010</v>
+        <v>00000000000000000000000010110001</v>
       </c>
       <c r="B180" t="str">
-        <v>00100000111111000000001010100111</v>
+        <v>00000000000000000000000000000000</v>
       </c>
       <c r="C180" t="str">
         <v>00000000000000000000000000000000</v>
@@ -6656,7 +6656,7 @@
         <v>00000000000000000000000000000000</v>
       </c>
       <c r="E180" t="str">
-        <v>00100001011110100000000010110010</v>
+        <v>00000000000000000000000000000000</v>
       </c>
       <c r="F180" t="b">
         <v>0</v>
@@ -6665,7 +6665,7 @@
         <v>0</v>
       </c>
       <c r="H180" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I180">
         <v>0</v>
@@ -6679,10 +6679,10 @@
     </row>
     <row r="181">
       <c r="A181" t="str">
-        <v>00101110001110100000000000001011</v>
+        <v>00000000000000000000000010110010</v>
       </c>
       <c r="B181" t="str">
-        <v>00100000111111000000100100100101</v>
+        <v>00000000000000000000000000000000</v>
       </c>
       <c r="C181" t="str">
         <v>00000000000000000000000000000000</v>
@@ -6691,7 +6691,7 @@
         <v>00000000000000000000000000000000</v>
       </c>
       <c r="E181" t="str">
-        <v>00100001011110100000000010110011</v>
+        <v>00000000000000000000000000000000</v>
       </c>
       <c r="F181" t="b">
         <v>0</v>
@@ -6700,7 +6700,7 @@
         <v>0</v>
       </c>
       <c r="H181" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I181">
         <v>0</v>
@@ -6714,10 +6714,10 @@
     </row>
     <row r="182">
       <c r="A182" t="str">
-        <v>00101110001110100000000000001011</v>
+        <v>00000000000000000000000010110011</v>
       </c>
       <c r="B182" t="str">
-        <v>00100000111111000000000000110000</v>
+        <v>00000000000000000000000000000000</v>
       </c>
       <c r="C182" t="str">
         <v>00000000000000000000000000000000</v>
@@ -6726,7 +6726,7 @@
         <v>00000000000000000000000000000000</v>
       </c>
       <c r="E182" t="str">
-        <v>00100001011110100000000010110100</v>
+        <v>00000000000000000000000000000000</v>
       </c>
       <c r="F182" t="b">
         <v>0</v>
@@ -6735,7 +6735,7 @@
         <v>0</v>
       </c>
       <c r="H182" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I182">
         <v>0</v>
@@ -6749,10 +6749,10 @@
     </row>
     <row r="183">
       <c r="A183" t="str">
-        <v>00101110001110100000000000001011</v>
+        <v>00000000000000000000000010100000</v>
       </c>
       <c r="B183" t="str">
-        <v>00100000111111000000001010010011</v>
+        <v>00000000000000000000000000000000</v>
       </c>
       <c r="C183" t="str">
         <v>00000000000000000000000000000000</v>
@@ -6761,7 +6761,7 @@
         <v>00000000000000000000000000000000</v>
       </c>
       <c r="E183" t="str">
-        <v>00100001011110100000000010110101</v>
+        <v>00000000000000000000000000000000</v>
       </c>
       <c r="F183" t="b">
         <v>0</v>
@@ -6770,7 +6770,7 @@
         <v>0</v>
       </c>
       <c r="H183" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I183">
         <v>0</v>
@@ -6784,10 +6784,10 @@
     </row>
     <row r="184">
       <c r="A184" t="str">
-        <v>00101110001110100000000000001011</v>
+        <v>00000000000000000000000011110000</v>
       </c>
       <c r="B184" t="str">
-        <v>00100000111111000000011111111101</v>
+        <v>00000000000000000000000000000000</v>
       </c>
       <c r="C184" t="str">
         <v>00000000000000000000000000000000</v>
@@ -6796,7 +6796,7 @@
         <v>00000000000000000000000000000000</v>
       </c>
       <c r="E184" t="str">
-        <v>00100001011110100000000010110110</v>
+        <v>00000000000000000000000000000000</v>
       </c>
       <c r="F184" t="b">
         <v>0</v>
@@ -6805,7 +6805,7 @@
         <v>0</v>
       </c>
       <c r="H184" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I184">
         <v>0</v>
@@ -6819,10 +6819,10 @@
     </row>
     <row r="185">
       <c r="A185" t="str">
-        <v>00101110001110100000000000001100</v>
+        <v>00000000000000000000000010110110</v>
       </c>
       <c r="B185" t="str">
-        <v>00100000111111000000100001011110</v>
+        <v>00000000000000000000000000000000</v>
       </c>
       <c r="C185" t="str">
         <v>00000000000000000000000000000000</v>
@@ -6831,7 +6831,7 @@
         <v>00000000000000000000000000000000</v>
       </c>
       <c r="E185" t="str">
-        <v>00100001011110100000000010110111</v>
+        <v>00000000000000000000000000000000</v>
       </c>
       <c r="F185" t="b">
         <v>0</v>
@@ -6840,7 +6840,7 @@
         <v>0</v>
       </c>
       <c r="H185" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I185">
         <v>0</v>
@@ -6854,10 +6854,10 @@
     </row>
     <row r="186">
       <c r="A186" t="str">
-        <v>00101110001110100000000000001100</v>
+        <v>00000000000000000000000010100011</v>
       </c>
       <c r="B186" t="str">
-        <v>00100000111111000000011111101000</v>
+        <v>00000000000000000000000000000000</v>
       </c>
       <c r="C186" t="str">
         <v>00000000000000000000000000000000</v>
@@ -6866,7 +6866,7 @@
         <v>00000000000000000000000000000000</v>
       </c>
       <c r="E186" t="str">
-        <v>00100001011110100000000010111000</v>
+        <v>00000000000000000000000000000000</v>
       </c>
       <c r="F186" t="b">
         <v>0</v>
@@ -6875,7 +6875,7 @@
         <v>0</v>
       </c>
       <c r="H186" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I186">
         <v>0</v>
@@ -6889,10 +6889,10 @@
     </row>
     <row r="187">
       <c r="A187" t="str">
-        <v>00101110001110100000000000001100</v>
+        <v>00000000000000000000000011100100</v>
       </c>
       <c r="B187" t="str">
-        <v>00100000111111000000101101100100</v>
+        <v>00000000000000000000000000000000</v>
       </c>
       <c r="C187" t="str">
         <v>00000000000000000000000000000000</v>
@@ -6901,7 +6901,7 @@
         <v>00000000000000000000000000000000</v>
       </c>
       <c r="E187" t="str">
-        <v>00100001011110100000000010111001</v>
+        <v>00000000000000000000000000000000</v>
       </c>
       <c r="F187" t="b">
         <v>0</v>
@@ -6910,7 +6910,7 @@
         <v>0</v>
       </c>
       <c r="H187" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I187">
         <v>0</v>
@@ -6924,10 +6924,10 @@
     </row>
     <row r="188">
       <c r="A188" t="str">
-        <v>00101110001110100000000000001100</v>
+        <v>00000000000000000000000010111001</v>
       </c>
       <c r="B188" t="str">
-        <v>00100000111111000000011101001101</v>
+        <v>00000000000000000000000000000000</v>
       </c>
       <c r="C188" t="str">
         <v>00000000000000000000000000000000</v>
@@ -6936,7 +6936,7 @@
         <v>00000000000000000000000000000000</v>
       </c>
       <c r="E188" t="str">
-        <v>00100001011110100000000010111010</v>
+        <v>00000000000000000000000000000000</v>
       </c>
       <c r="F188" t="b">
         <v>0</v>
@@ -6945,7 +6945,7 @@
         <v>0</v>
       </c>
       <c r="H188" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I188">
         <v>0</v>
@@ -6959,7 +6959,7 @@
     </row>
     <row r="189">
       <c r="A189" t="str">
-        <v>00000000000000000000000100000001</v>
+        <v>00000000000000000000000010011101</v>
       </c>
       <c r="B189" t="str">
         <v>00000000000000000000000000000000</v>
@@ -6994,10 +6994,10 @@
     </row>
     <row r="190">
       <c r="A190" t="str">
-        <v>00101110001110100000000000001100</v>
+        <v>00000000000000000000000010011110</v>
       </c>
       <c r="B190" t="str">
-        <v>00100000111111000000000110110000</v>
+        <v>00000000000000000000000000000000</v>
       </c>
       <c r="C190" t="str">
         <v>00000000000000000000000000000000</v>
@@ -7006,7 +7006,7 @@
         <v>00000000000000000000000000000000</v>
       </c>
       <c r="E190" t="str">
-        <v>00100001011110100000000010111100</v>
+        <v>00000000000000000000000000000000</v>
       </c>
       <c r="F190" t="b">
         <v>0</v>
@@ -7015,7 +7015,7 @@
         <v>0</v>
       </c>
       <c r="H190" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I190">
         <v>0</v>
@@ -7029,10 +7029,10 @@
     </row>
     <row r="191">
       <c r="A191" t="str">
-        <v>00101110001110100000000000001111</v>
+        <v>00000000000000000000000010110000</v>
       </c>
       <c r="B191" t="str">
-        <v>00100000111111000000100011100010</v>
+        <v>00000000000000000000000000000000</v>
       </c>
       <c r="C191" t="str">
         <v>00000000000000000000000000000000</v>
@@ -7041,7 +7041,7 @@
         <v>00000000000000000000000000000000</v>
       </c>
       <c r="E191" t="str">
-        <v>00100001011110100000000010111101</v>
+        <v>00000000000000000000000000000000</v>
       </c>
       <c r="F191" t="b">
         <v>0</v>
@@ -7050,7 +7050,7 @@
         <v>0</v>
       </c>
       <c r="H191" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I191">
         <v>0</v>
@@ -7064,10 +7064,10 @@
     </row>
     <row r="192">
       <c r="A192" t="str">
-        <v>00101110001110100000000000001111</v>
+        <v>00000000000000000000000011010111</v>
       </c>
       <c r="B192" t="str">
-        <v>00100000111111000000001000010000</v>
+        <v>00000000000000000000000000000000</v>
       </c>
       <c r="C192" t="str">
         <v>00000000000000000000000000000000</v>
@@ -7076,7 +7076,7 @@
         <v>00000000000000000000000000000000</v>
       </c>
       <c r="E192" t="str">
-        <v>00100001011110100000000010111110</v>
+        <v>00000000000000000000000000000000</v>
       </c>
       <c r="F192" t="b">
         <v>0</v>
@@ -7099,7 +7099,7 @@
     </row>
     <row r="193">
       <c r="A193" t="str">
-        <v>00000000000000000000000010111011</v>
+        <v>00000000000000000000000010011111</v>
       </c>
       <c r="B193" t="str">
         <v>00000000000000000000000000000000</v>
@@ -7120,7 +7120,7 @@
         <v>0</v>
       </c>
       <c r="H193" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I193">
         <v>0</v>
@@ -7134,10 +7134,10 @@
     </row>
     <row r="194">
       <c r="A194" t="str">
-        <v>00101110001110100000000000001111</v>
+        <v>00000000000000000000000001101101</v>
       </c>
       <c r="B194" t="str">
-        <v>00100000111111000000000101000000</v>
+        <v>00000000000000000000000000000000</v>
       </c>
       <c r="C194" t="str">
         <v>00000000000000000000000000000000</v>
@@ -7146,7 +7146,7 @@
         <v>00000000000000000000000000000000</v>
       </c>
       <c r="E194" t="str">
-        <v>00100001011110100000000011000000</v>
+        <v>00000000000000000000000000000000</v>
       </c>
       <c r="F194" t="b">
         <v>0</v>
@@ -7155,7 +7155,7 @@
         <v>0</v>
       </c>
       <c r="H194" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I194">
         <v>0</v>
@@ -7169,10 +7169,10 @@
     </row>
     <row r="195">
       <c r="A195" t="str">
-        <v>00101110001110100000000000001111</v>
+        <v>00000000000000000000000011010100</v>
       </c>
       <c r="B195" t="str">
-        <v>00100000111111000000011100101010</v>
+        <v>00000000000000000000000000000000</v>
       </c>
       <c r="C195" t="str">
         <v>00000000000000000000000000000000</v>
@@ -7181,7 +7181,7 @@
         <v>00000000000000000000000000000000</v>
       </c>
       <c r="E195" t="str">
-        <v>00100001011110100000000011000001</v>
+        <v>00000000000000000000000000000000</v>
       </c>
       <c r="F195" t="b">
         <v>0</v>
@@ -7204,10 +7204,10 @@
     </row>
     <row r="196">
       <c r="A196" t="str">
-        <v>00101110001110100000000000001111</v>
+        <v>00000000000000000000000011100111</v>
       </c>
       <c r="B196" t="str">
-        <v>00100000111111000000010011100111</v>
+        <v>00000000000000000000000000000000</v>
       </c>
       <c r="C196" t="str">
         <v>00000000000000000000000000000000</v>
@@ -7216,7 +7216,7 @@
         <v>00000000000000000000000000000000</v>
       </c>
       <c r="E196" t="str">
-        <v>00100001011110100000000011000010</v>
+        <v>00000000000000000000000000000000</v>
       </c>
       <c r="F196" t="b">
         <v>0</v>
@@ -7239,7 +7239,7 @@
     </row>
     <row r="197">
       <c r="A197" t="str">
-        <v>00000000000000000000000011011100</v>
+        <v>00000000000000000000000000111000</v>
       </c>
       <c r="B197" t="str">
         <v>00000000000000000000000000000000</v>
@@ -7260,7 +7260,7 @@
         <v>0</v>
       </c>
       <c r="H197" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I197">
         <v>0</v>
@@ -7274,10 +7274,10 @@
     </row>
     <row r="198">
       <c r="A198" t="str">
-        <v>00101110001110100000000000001111</v>
+        <v>00000000000000000000000000010001</v>
       </c>
       <c r="B198" t="str">
-        <v>00100000111111000000101101110100</v>
+        <v>00000000000000000000000000000000</v>
       </c>
       <c r="C198" t="str">
         <v>00000000000000000000000000000000</v>
@@ -7286,7 +7286,7 @@
         <v>00000000000000000000000000000000</v>
       </c>
       <c r="E198" t="str">
-        <v>00100001011110100000000011000100</v>
+        <v>00000000000000000000000000000000</v>
       </c>
       <c r="F198" t="b">
         <v>0</v>
@@ -7295,7 +7295,7 @@
         <v>0</v>
       </c>
       <c r="H198" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I198">
         <v>0</v>
@@ -7309,10 +7309,10 @@
     </row>
     <row r="199">
       <c r="A199" t="str">
-        <v>00101110001110100000000000001111</v>
+        <v>00000000000000000000000010101110</v>
       </c>
       <c r="B199" t="str">
-        <v>00100000111111000000000111110001</v>
+        <v>00000000000000000000000000000000</v>
       </c>
       <c r="C199" t="str">
         <v>00000000000000000000000000000000</v>
@@ -7321,7 +7321,7 @@
         <v>00000000000000000000000000000000</v>
       </c>
       <c r="E199" t="str">
-        <v>00100001011110100000000011000101</v>
+        <v>00000000000000000000000000000000</v>
       </c>
       <c r="F199" t="b">
         <v>0</v>
@@ -7330,7 +7330,7 @@
         <v>0</v>
       </c>
       <c r="H199" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I199">
         <v>0</v>
@@ -7344,10 +7344,10 @@
     </row>
     <row r="200">
       <c r="A200" t="str">
-        <v>00101110001110100000000000010001</v>
+        <v>00000000000000000000000010100100</v>
       </c>
       <c r="B200" t="str">
-        <v>00100000111111000000100011011110</v>
+        <v>00000000000000000000000000000000</v>
       </c>
       <c r="C200" t="str">
         <v>00000000000000000000000000000000</v>
@@ -7356,7 +7356,7 @@
         <v>00000000000000000000000000000000</v>
       </c>
       <c r="E200" t="str">
-        <v>00100001011110100000000011000110</v>
+        <v>00000000000000000000000000000000</v>
       </c>
       <c r="F200" t="b">
         <v>0</v>
@@ -7379,7 +7379,7 @@
     </row>
     <row r="201">
       <c r="A201" t="str">
-        <v>00000000000000000000000011111111</v>
+        <v>00000000000000000000000010100110</v>
       </c>
       <c r="B201" t="str">
         <v>00000000000000000000000000000000</v>
@@ -7414,7 +7414,7 @@
     </row>
     <row r="202">
       <c r="A202" t="str">
-        <v>00000000000000000000000010100101</v>
+        <v>00000000000000000000000000100001</v>
       </c>
       <c r="B202" t="str">
         <v>00000000000000000000000000000000</v>
@@ -7435,7 +7435,7 @@
         <v>0</v>
       </c>
       <c r="H202" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I202">
         <v>0</v>
@@ -7449,10 +7449,10 @@
     </row>
     <row r="203">
       <c r="A203" t="str">
-        <v>00101110001110100000000000010101</v>
+        <v>00000000000000000000000001100001</v>
       </c>
       <c r="B203" t="str">
-        <v>00100000111111000000011010010110</v>
+        <v>00000000000000000000000000000000</v>
       </c>
       <c r="C203" t="str">
         <v>00000000000000000000000000000000</v>
@@ -7461,7 +7461,7 @@
         <v>00000000000000000000000000000000</v>
       </c>
       <c r="E203" t="str">
-        <v>00100001011110100000000011001001</v>
+        <v>00000000000000000000000000000000</v>
       </c>
       <c r="F203" t="b">
         <v>0</v>
@@ -7484,10 +7484,10 @@
     </row>
     <row r="204">
       <c r="A204" t="str">
-        <v>00101110001110100000000000010101</v>
+        <v>00000000000000000000000011001110</v>
       </c>
       <c r="B204" t="str">
-        <v>00100000111111000000000000001110</v>
+        <v>00000000000000000000000000000000</v>
       </c>
       <c r="C204" t="str">
         <v>00000000000000000000000000000000</v>
@@ -7496,7 +7496,7 @@
         <v>00000000000000000000000000000000</v>
       </c>
       <c r="E204" t="str">
-        <v>00100001011110100000000011001010</v>
+        <v>00000000000000000000000000000000</v>
       </c>
       <c r="F204" t="b">
         <v>0</v>
@@ -7519,10 +7519,10 @@
     </row>
     <row r="205">
       <c r="A205" t="str">
-        <v>00101110001110100000000000010101</v>
+        <v>00000000000000000000000010100101</v>
       </c>
       <c r="B205" t="str">
-        <v>00100000111111000000100011110101</v>
+        <v>00000000000000000000000000000000</v>
       </c>
       <c r="C205" t="str">
         <v>00000000000000000000000000000000</v>
@@ -7531,7 +7531,7 @@
         <v>00000000000000000000000000000000</v>
       </c>
       <c r="E205" t="str">
-        <v>00100001011110100000000011001011</v>
+        <v>00000000000000000000000000000000</v>
       </c>
       <c r="F205" t="b">
         <v>0</v>
@@ -7540,7 +7540,7 @@
         <v>0</v>
       </c>
       <c r="H205" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I205">
         <v>0</v>
@@ -7554,10 +7554,10 @@
     </row>
     <row r="206">
       <c r="A206" t="str">
-        <v>00101110001110100000000000010101</v>
+        <v>00000000000000000000000010101001</v>
       </c>
       <c r="B206" t="str">
-        <v>00100000111111000000101000101101</v>
+        <v>00000000000000000000000000000000</v>
       </c>
       <c r="C206" t="str">
         <v>00000000000000000000000000000000</v>
@@ -7566,7 +7566,7 @@
         <v>00000000000000000000000000000000</v>
       </c>
       <c r="E206" t="str">
-        <v>00100001011110100000000011001100</v>
+        <v>00000000000000000000000000000000</v>
       </c>
       <c r="F206" t="b">
         <v>0</v>
@@ -7575,7 +7575,7 @@
         <v>0</v>
       </c>
       <c r="H206" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I206">
         <v>0</v>
@@ -7589,10 +7589,10 @@
     </row>
     <row r="207">
       <c r="A207" t="str">
-        <v>00101110001110100000000000010101</v>
+        <v>00000000000000000000000010010110</v>
       </c>
       <c r="B207" t="str">
-        <v>00100000111111000000000010011101</v>
+        <v>00000000000000000000000000000000</v>
       </c>
       <c r="C207" t="str">
         <v>00000000000000000000000000000000</v>
@@ -7601,7 +7601,7 @@
         <v>00000000000000000000000000000000</v>
       </c>
       <c r="E207" t="str">
-        <v>00100001011110100000000011001101</v>
+        <v>00000000000000000000000000000000</v>
       </c>
       <c r="F207" t="b">
         <v>0</v>
@@ -7624,10 +7624,10 @@
     </row>
     <row r="208">
       <c r="A208" t="str">
-        <v>00101110001110100000000000010101</v>
+        <v>00000000000000000000000010001111</v>
       </c>
       <c r="B208" t="str">
-        <v>00100000111111000000000111111101</v>
+        <v>00000000000000000000000000000000</v>
       </c>
       <c r="C208" t="str">
         <v>00000000000000000000000000000000</v>
@@ -7636,7 +7636,7 @@
         <v>00000000000000000000000000000000</v>
       </c>
       <c r="E208" t="str">
-        <v>00100001011110100000000011001110</v>
+        <v>00000000000000000000000000000000</v>
       </c>
       <c r="F208" t="b">
         <v>0</v>
@@ -7659,10 +7659,10 @@
     </row>
     <row r="209">
       <c r="A209" t="str">
-        <v>00101110001110100000000000010101</v>
+        <v>00000000000000000000000010000100</v>
       </c>
       <c r="B209" t="str">
-        <v>00100000111111000000001101001010</v>
+        <v>00000000000000000000000000000000</v>
       </c>
       <c r="C209" t="str">
         <v>00000000000000000000000000000000</v>
@@ -7671,7 +7671,7 @@
         <v>00000000000000000000000000000000</v>
       </c>
       <c r="E209" t="str">
-        <v>00100001011110100000000011001111</v>
+        <v>00000000000000000000000000000000</v>
       </c>
       <c r="F209" t="b">
         <v>0</v>
@@ -7694,10 +7694,10 @@
     </row>
     <row r="210">
       <c r="A210" t="str">
-        <v>00101110001110100000000000010101</v>
+        <v>00000000000000000000000011100010</v>
       </c>
       <c r="B210" t="str">
-        <v>00100000111111000000001100011010</v>
+        <v>00000000000000000000000000000000</v>
       </c>
       <c r="C210" t="str">
         <v>00000000000000000000000000000000</v>
@@ -7706,7 +7706,7 @@
         <v>00000000000000000000000000000000</v>
       </c>
       <c r="E210" t="str">
-        <v>00100001011110100000000011010000</v>
+        <v>00000000000000000000000000000000</v>
       </c>
       <c r="F210" t="b">
         <v>0</v>
@@ -7729,10 +7729,10 @@
     </row>
     <row r="211">
       <c r="A211" t="str">
-        <v>00101110001110100000000000010101</v>
+        <v>00000000000000000000000001000001</v>
       </c>
       <c r="B211" t="str">
-        <v>00100000111111000000001001111110</v>
+        <v>00000000000000000000000000000000</v>
       </c>
       <c r="C211" t="str">
         <v>00000000000000000000000000000000</v>
@@ -7741,7 +7741,7 @@
         <v>00000000000000000000000000000000</v>
       </c>
       <c r="E211" t="str">
-        <v>00100001011110100000000011010001</v>
+        <v>00000000000000000000000000000000</v>
       </c>
       <c r="F211" t="b">
         <v>0</v>
@@ -7764,10 +7764,10 @@
     </row>
     <row r="212">
       <c r="A212" t="str">
-        <v>00101110001110100000000000010101</v>
+        <v>00000000000000000000000001011110</v>
       </c>
       <c r="B212" t="str">
-        <v>00100000111111000000000000001001</v>
+        <v>00000000000000000000000000000000</v>
       </c>
       <c r="C212" t="str">
         <v>00000000000000000000000000000000</v>
@@ -7776,7 +7776,7 @@
         <v>00000000000000000000000000000000</v>
       </c>
       <c r="E212" t="str">
-        <v>00100001011110100000000011010010</v>
+        <v>00000000000000000000000000000000</v>
       </c>
       <c r="F212" t="b">
         <v>0</v>
@@ -7799,7 +7799,7 @@
     </row>
     <row r="213">
       <c r="A213" t="str">
-        <v>00000000000000000000000010111111</v>
+        <v>00000000000000000000000010111100</v>
       </c>
       <c r="B213" t="str">
         <v>00000000000000000000000000000000</v>
@@ -7834,7 +7834,7 @@
     </row>
     <row r="214">
       <c r="A214" t="str">
-        <v>00000000000000000000000100101001</v>
+        <v>00000000000000000000000010011100</v>
       </c>
       <c r="B214" t="str">
         <v>00000000000000000000000000000000</v>
@@ -7855,7 +7855,7 @@
         <v>0</v>
       </c>
       <c r="H214" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I214">
         <v>0</v>
@@ -7869,10 +7869,10 @@
     </row>
     <row r="215">
       <c r="A215" t="str">
-        <v>00101110001110100000000000010110</v>
+        <v>00000000000000000000000010010101</v>
       </c>
       <c r="B215" t="str">
-        <v>00100000111111000000101011100110</v>
+        <v>00000000000000000000000000000000</v>
       </c>
       <c r="C215" t="str">
         <v>00000000000000000000000000000000</v>
@@ -7881,7 +7881,7 @@
         <v>00000000000000000000000000000000</v>
       </c>
       <c r="E215" t="str">
-        <v>00100001011110100000000011010101</v>
+        <v>00000000000000000000000000000000</v>
       </c>
       <c r="F215" t="b">
         <v>0</v>
@@ -7890,7 +7890,7 @@
         <v>0</v>
       </c>
       <c r="H215" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I215">
         <v>0</v>
@@ -7904,10 +7904,10 @@
     </row>
     <row r="216">
       <c r="A216" t="str">
-        <v>00101110001110100000000000010110</v>
+        <v>00000000000000000000000001100100</v>
       </c>
       <c r="B216" t="str">
-        <v>00100000111111000000010010011001</v>
+        <v>00000000000000000000000000000000</v>
       </c>
       <c r="C216" t="str">
         <v>00000000000000000000000000000000</v>
@@ -7916,7 +7916,7 @@
         <v>00000000000000000000000000000000</v>
       </c>
       <c r="E216" t="str">
-        <v>00100001011110100000000011010110</v>
+        <v>00000000000000000000000000000000</v>
       </c>
       <c r="F216" t="b">
         <v>0</v>
@@ -7939,7 +7939,7 @@
     </row>
     <row r="217">
       <c r="A217" t="str">
-        <v>00000000000000000000000011000011</v>
+        <v>00000000000000000000000000101111</v>
       </c>
       <c r="B217" t="str">
         <v>00000000000000000000000000000000</v>
@@ -7960,7 +7960,7 @@
         <v>0</v>
       </c>
       <c r="H217" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I217">
         <v>0</v>
@@ -7974,10 +7974,10 @@
     </row>
     <row r="218">
       <c r="A218" t="str">
-        <v>00101110001110100000000000010110</v>
+        <v>00000000000000000000000011011011</v>
       </c>
       <c r="B218" t="str">
-        <v>00100000111111000000001010010010</v>
+        <v>00000000000000000000000000000000</v>
       </c>
       <c r="C218" t="str">
         <v>00000000000000000000000000000000</v>
@@ -7986,7 +7986,7 @@
         <v>00000000000000000000000000000000</v>
       </c>
       <c r="E218" t="str">
-        <v>00100001011110100000000011011000</v>
+        <v>00000000000000000000000000000000</v>
       </c>
       <c r="F218" t="b">
         <v>0</v>
@@ -7995,7 +7995,7 @@
         <v>0</v>
       </c>
       <c r="H218" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I218">
         <v>0</v>
@@ -8009,7 +8009,7 @@
     </row>
     <row r="219">
       <c r="A219" t="str">
-        <v>00000000000000000000000011111100</v>
+        <v>00000000000000000000000001000110</v>
       </c>
       <c r="B219" t="str">
         <v>00000000000000000000000000000000</v>
@@ -8030,7 +8030,7 @@
         <v>0</v>
       </c>
       <c r="H219" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I219">
         <v>0</v>
@@ -8044,10 +8044,10 @@
     </row>
     <row r="220">
       <c r="A220" t="str">
-        <v>00101110001110100000000000010110</v>
+        <v>00000000000000000000000000011101</v>
       </c>
       <c r="B220" t="str">
-        <v>00100000111111000000101000101001</v>
+        <v>00000000000000000000000000000000</v>
       </c>
       <c r="C220" t="str">
         <v>00000000000000000000000000000000</v>
@@ -8056,7 +8056,7 @@
         <v>00000000000000000000000000000000</v>
       </c>
       <c r="E220" t="str">
-        <v>00100001011110100000000011011010</v>
+        <v>00000000000000000000000000000000</v>
       </c>
       <c r="F220" t="b">
         <v>0</v>
@@ -8079,10 +8079,10 @@
     </row>
     <row r="221">
       <c r="A221" t="str">
-        <v>00101110001110100000000000010110</v>
+        <v>00000000000000000000000011101110</v>
       </c>
       <c r="B221" t="str">
-        <v>00100000111111000000010010001001</v>
+        <v>00000000000000000000000000000000</v>
       </c>
       <c r="C221" t="str">
         <v>00000000000000000000000000000000</v>
@@ -8091,7 +8091,7 @@
         <v>00000000000000000000000000000000</v>
       </c>
       <c r="E221" t="str">
-        <v>00100001011110100000000011011011</v>
+        <v>00000000000000000000000000000000</v>
       </c>
       <c r="F221" t="b">
         <v>0</v>
@@ -8100,7 +8100,7 @@
         <v>0</v>
       </c>
       <c r="H221" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I221">
         <v>0</v>
@@ -8114,7 +8114,7 @@
     </row>
     <row r="222">
       <c r="A222" t="str">
-        <v>00000000000000000000000100011001</v>
+        <v>00000000000000000000000010111101</v>
       </c>
       <c r="B222" t="str">
         <v>00000000000000000000000000000000</v>
@@ -8149,7 +8149,7 @@
     </row>
     <row r="223">
       <c r="A223" t="str">
-        <v>00000000000000000000000011010011</v>
+        <v>00000000000000000000000011100101</v>
       </c>
       <c r="B223" t="str">
         <v>00000000000000000000000000000000</v>
@@ -8184,10 +8184,10 @@
     </row>
     <row r="224">
       <c r="A224" t="str">
-        <v>00101110001110100000000000010111</v>
+        <v>00000000000000000000000010011000</v>
       </c>
       <c r="B224" t="str">
-        <v>00100000111111000000101011111100</v>
+        <v>00000000000000000000000000000000</v>
       </c>
       <c r="C224" t="str">
         <v>00000000000000000000000000000000</v>
@@ -8196,7 +8196,7 @@
         <v>00000000000000000000000000000000</v>
       </c>
       <c r="E224" t="str">
-        <v>00100001011110100000000011011110</v>
+        <v>00000000000000000000000000000000</v>
       </c>
       <c r="F224" t="b">
         <v>0</v>
@@ -8219,10 +8219,10 @@
     </row>
     <row r="225">
       <c r="A225" t="str">
-        <v>00101110001110100000000000010111</v>
+        <v>00000000000000000000000000000001</v>
       </c>
       <c r="B225" t="str">
-        <v>00100000111111000000011010011110</v>
+        <v>00000000000000000000000000000000</v>
       </c>
       <c r="C225" t="str">
         <v>00000000000000000000000000000000</v>
@@ -8231,7 +8231,7 @@
         <v>00000000000000000000000000000000</v>
       </c>
       <c r="E225" t="str">
-        <v>00100001011110100000000011011111</v>
+        <v>00000000000000000000000000000000</v>
       </c>
       <c r="F225" t="b">
         <v>0</v>
@@ -8240,7 +8240,7 @@
         <v>0</v>
       </c>
       <c r="H225" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I225">
         <v>0</v>
@@ -8254,10 +8254,10 @@
     </row>
     <row r="226">
       <c r="A226" t="str">
-        <v>00101110001110100000000000010111</v>
+        <v>00000000000000000000000011000010</v>
       </c>
       <c r="B226" t="str">
-        <v>00100000111111000000100111011001</v>
+        <v>00000000000000000000000000000000</v>
       </c>
       <c r="C226" t="str">
         <v>00000000000000000000000000000000</v>
@@ -8266,7 +8266,7 @@
         <v>00000000000000000000000000000000</v>
       </c>
       <c r="E226" t="str">
-        <v>00100001011110100000000011100000</v>
+        <v>00000000000000000000000000000000</v>
       </c>
       <c r="F226" t="b">
         <v>0</v>
@@ -8289,7 +8289,7 @@
     </row>
     <row r="227">
       <c r="A227" t="str">
-        <v>00000000000000000000000011011001</v>
+        <v>00000000000000000000000011000110</v>
       </c>
       <c r="B227" t="str">
         <v>00000000000000000000000000000000</v>
@@ -8310,7 +8310,7 @@
         <v>0</v>
       </c>
       <c r="H227" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I227">
         <v>0</v>
@@ -8324,10 +8324,10 @@
     </row>
     <row r="228">
       <c r="A228" t="str">
-        <v>00101110001110100000000000011001</v>
+        <v>00000000000000000000000011001000</v>
       </c>
       <c r="B228" t="str">
-        <v>00100000111111000000011100101110</v>
+        <v>00000000000000000000000000000000</v>
       </c>
       <c r="C228" t="str">
         <v>00000000000000000000000000000000</v>
@@ -8336,7 +8336,7 @@
         <v>00000000000000000000000000000000</v>
       </c>
       <c r="E228" t="str">
-        <v>00100001011110100000000011100010</v>
+        <v>00000000000000000000000000000000</v>
       </c>
       <c r="F228" t="b">
         <v>0</v>
@@ -8359,10 +8359,10 @@
     </row>
     <row r="229">
       <c r="A229" t="str">
-        <v>00101110001110100000000000011001</v>
+        <v>00000000000000000000000010100010</v>
       </c>
       <c r="B229" t="str">
-        <v>00100000111111000000110110001101</v>
+        <v>00000000000000000000000000000000</v>
       </c>
       <c r="C229" t="str">
         <v>00000000000000000000000000000000</v>
@@ -8371,7 +8371,7 @@
         <v>00000000000000000000000000000000</v>
       </c>
       <c r="E229" t="str">
-        <v>00100001011110100000000011100011</v>
+        <v>00000000000000000000000000000000</v>
       </c>
       <c r="F229" t="b">
         <v>0</v>
@@ -8394,10 +8394,10 @@
     </row>
     <row r="230">
       <c r="A230" t="str">
-        <v>00101110001110100000000000011001</v>
+        <v>00000000000000000000000010110111</v>
       </c>
       <c r="B230" t="str">
-        <v>00100000111111000000100111110110</v>
+        <v>00000000000000000000000000000000</v>
       </c>
       <c r="C230" t="str">
         <v>00000000000000000000000000000000</v>
@@ -8406,7 +8406,7 @@
         <v>00000000000000000000000000000000</v>
       </c>
       <c r="E230" t="str">
-        <v>00100001011110100000000011100100</v>
+        <v>00000000000000000000000000000000</v>
       </c>
       <c r="F230" t="b">
         <v>0</v>
@@ -8415,7 +8415,7 @@
         <v>0</v>
       </c>
       <c r="H230" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I230">
         <v>0</v>
@@ -8429,10 +8429,10 @@
     </row>
     <row r="231">
       <c r="A231" t="str">
-        <v>00101110001110100000000000011001</v>
+        <v>00000000000000000000000011001100</v>
       </c>
       <c r="B231" t="str">
-        <v>00100000111111000000010101110011</v>
+        <v>00000000000000000000000000000000</v>
       </c>
       <c r="C231" t="str">
         <v>00000000000000000000000000000000</v>
@@ -8441,7 +8441,7 @@
         <v>00000000000000000000000000000000</v>
       </c>
       <c r="E231" t="str">
-        <v>00100001011110100000000011100101</v>
+        <v>00000000000000000000000000000000</v>
       </c>
       <c r="F231" t="b">
         <v>0</v>
@@ -8450,7 +8450,7 @@
         <v>0</v>
       </c>
       <c r="H231" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I231">
         <v>0</v>
@@ -8464,10 +8464,10 @@
     </row>
     <row r="232">
       <c r="A232" t="str">
-        <v>00101110001110100000000000011001</v>
+        <v>00000000000000000000000000000010</v>
       </c>
       <c r="B232" t="str">
-        <v>00100000111111000000000010010001</v>
+        <v>00000000000000000000000000000000</v>
       </c>
       <c r="C232" t="str">
         <v>00000000000000000000000000000000</v>
@@ -8476,7 +8476,7 @@
         <v>00000000000000000000000000000000</v>
       </c>
       <c r="E232" t="str">
-        <v>00100001011110100000000011100110</v>
+        <v>00000000000000000000000000000000</v>
       </c>
       <c r="F232" t="b">
         <v>0</v>
@@ -8499,10 +8499,10 @@
     </row>
     <row r="233">
       <c r="A233" t="str">
-        <v>00101110001110100000000000011001</v>
+        <v>00000000000000000000000000100111</v>
       </c>
       <c r="B233" t="str">
-        <v>00100000111111000000000101010100</v>
+        <v>00000000000000000000000000000000</v>
       </c>
       <c r="C233" t="str">
         <v>00000000000000000000000000000000</v>
@@ -8511,7 +8511,7 @@
         <v>00000000000000000000000000000000</v>
       </c>
       <c r="E233" t="str">
-        <v>00100001011110100000000011100111</v>
+        <v>00000000000000000000000000000000</v>
       </c>
       <c r="F233" t="b">
         <v>0</v>
@@ -8534,10 +8534,10 @@
     </row>
     <row r="234">
       <c r="A234" t="str">
-        <v>00101110001110100000000000011001</v>
+        <v>00000000000000000000000011001010</v>
       </c>
       <c r="B234" t="str">
-        <v>00100000111111000000101111110111</v>
+        <v>00000000000000000000000000000000</v>
       </c>
       <c r="C234" t="str">
         <v>00000000000000000000000000000000</v>
@@ -8546,7 +8546,7 @@
         <v>00000000000000000000000000000000</v>
       </c>
       <c r="E234" t="str">
-        <v>00100001011110100000000011101000</v>
+        <v>00000000000000000000000000000000</v>
       </c>
       <c r="F234" t="b">
         <v>0</v>
@@ -8569,10 +8569,10 @@
     </row>
     <row r="235">
       <c r="A235" t="str">
-        <v>00101110001110100000000000011001</v>
+        <v>00000000000000000000000011011111</v>
       </c>
       <c r="B235" t="str">
-        <v>00100000111111000000111001010110</v>
+        <v>00000000000000000000000000000000</v>
       </c>
       <c r="C235" t="str">
         <v>00000000000000000000000000000000</v>
@@ -8581,7 +8581,7 @@
         <v>00000000000000000000000000000000</v>
       </c>
       <c r="E235" t="str">
-        <v>00100001011110100000000011101001</v>
+        <v>00000000000000000000000000000000</v>
       </c>
       <c r="F235" t="b">
         <v>0</v>
@@ -8590,7 +8590,7 @@
         <v>0</v>
       </c>
       <c r="H235" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I235">
         <v>0</v>
@@ -8604,10 +8604,10 @@
     </row>
     <row r="236">
       <c r="A236" t="str">
-        <v>00101110001110100000000000011001</v>
+        <v>00000000000000000000000000001101</v>
       </c>
       <c r="B236" t="str">
-        <v>00100000111111000000100000001011</v>
+        <v>00000000000000000000000000000000</v>
       </c>
       <c r="C236" t="str">
         <v>00000000000000000000000000000000</v>
@@ -8616,7 +8616,7 @@
         <v>00000000000000000000000000000000</v>
       </c>
       <c r="E236" t="str">
-        <v>00100001011110100000000011101010</v>
+        <v>00000000000000000000000000000000</v>
       </c>
       <c r="F236" t="b">
         <v>0</v>
@@ -8639,10 +8639,10 @@
     </row>
     <row r="237">
       <c r="A237" t="str">
-        <v>00101110001110100000000000011001</v>
+        <v>00000000000000000000000011110001</v>
       </c>
       <c r="B237" t="str">
-        <v>00100000111111000000101010000001</v>
+        <v>00000000000000000000000000000000</v>
       </c>
       <c r="C237" t="str">
         <v>00000000000000000000000000000000</v>
@@ -8651,7 +8651,7 @@
         <v>00000000000000000000000000000000</v>
       </c>
       <c r="E237" t="str">
-        <v>00100001011110100000000011101011</v>
+        <v>00000000000000000000000000000000</v>
       </c>
       <c r="F237" t="b">
         <v>0</v>
@@ -8660,7 +8660,7 @@
         <v>0</v>
       </c>
       <c r="H237" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I237">
         <v>0</v>
@@ -8674,10 +8674,10 @@
     </row>
     <row r="238">
       <c r="A238" t="str">
-        <v>00101110001110100000000000011010</v>
+        <v>00000000000000000000000000011001</v>
       </c>
       <c r="B238" t="str">
-        <v>00100000111111000000011010111111</v>
+        <v>00000000000000000000000000000000</v>
       </c>
       <c r="C238" t="str">
         <v>00000000000000000000000000000000</v>
@@ -8686,7 +8686,7 @@
         <v>00000000000000000000000000000000</v>
       </c>
       <c r="E238" t="str">
-        <v>00100001011110100000000011101100</v>
+        <v>00000000000000000000000000000000</v>
       </c>
       <c r="F238" t="b">
         <v>0</v>
@@ -8709,10 +8709,10 @@
     </row>
     <row r="239">
       <c r="A239" t="str">
-        <v>00101110001110100000000000011010</v>
+        <v>00000000000000000000000001100000</v>
       </c>
       <c r="B239" t="str">
-        <v>00100000111111000000000010010000</v>
+        <v>00000000000000000000000000000000</v>
       </c>
       <c r="C239" t="str">
         <v>00000000000000000000000000000000</v>
@@ -8721,7 +8721,7 @@
         <v>00000000000000000000000000000000</v>
       </c>
       <c r="E239" t="str">
-        <v>00100001011110100000000011101101</v>
+        <v>00000000000000000000000000000000</v>
       </c>
       <c r="F239" t="b">
         <v>0</v>
@@ -8744,7 +8744,7 @@
     </row>
     <row r="240">
       <c r="A240" t="str">
-        <v>00000000000000000000000011000111</v>
+        <v>00000000000000000000000011011101</v>
       </c>
       <c r="B240" t="str">
         <v>00000000000000000000000000000000</v>
@@ -8779,10 +8779,10 @@
     </row>
     <row r="241">
       <c r="A241" t="str">
-        <v>00101110001110100000000000011010</v>
+        <v>00000000000000000000000001000100</v>
       </c>
       <c r="B241" t="str">
-        <v>00100000111111000000000000110111</v>
+        <v>00000000000000000000000000000000</v>
       </c>
       <c r="C241" t="str">
         <v>00000000000000000000000000000000</v>
@@ -8791,7 +8791,7 @@
         <v>00000000000000000000000000000000</v>
       </c>
       <c r="E241" t="str">
-        <v>00100001011110100000000011101111</v>
+        <v>00000000000000000000000000000000</v>
       </c>
       <c r="F241" t="b">
         <v>0</v>
@@ -8814,10 +8814,10 @@
     </row>
     <row r="242">
       <c r="A242" t="str">
-        <v>00101110001110100000000000011011</v>
+        <v>00000000000000000000000010110100</v>
       </c>
       <c r="B242" t="str">
-        <v>00100000111111000000010110110111</v>
+        <v>00000000000000000000000000000000</v>
       </c>
       <c r="C242" t="str">
         <v>00000000000000000000000000000000</v>
@@ -8826,7 +8826,7 @@
         <v>00000000000000000000000000000000</v>
       </c>
       <c r="E242" t="str">
-        <v>00100001011110100000000011110000</v>
+        <v>00000000000000000000000000000000</v>
       </c>
       <c r="F242" t="b">
         <v>0</v>
@@ -8835,7 +8835,7 @@
         <v>0</v>
       </c>
       <c r="H242" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I242">
         <v>0</v>
@@ -8849,10 +8849,10 @@
     </row>
     <row r="243">
       <c r="A243" t="str">
-        <v>00101110001110100000000000011011</v>
+        <v>00000000000000000000000011101001</v>
       </c>
       <c r="B243" t="str">
-        <v>00100000111111000000100100000110</v>
+        <v>00000000000000000000000000000000</v>
       </c>
       <c r="C243" t="str">
         <v>00000000000000000000000000000000</v>
@@ -8861,7 +8861,7 @@
         <v>00000000000000000000000000000000</v>
       </c>
       <c r="E243" t="str">
-        <v>00100001011110100000000011110001</v>
+        <v>00000000000000000000000000000000</v>
       </c>
       <c r="F243" t="b">
         <v>0</v>
@@ -8870,7 +8870,7 @@
         <v>0</v>
       </c>
       <c r="H243" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I243">
         <v>0</v>
@@ -8884,7 +8884,7 @@
     </row>
     <row r="244">
       <c r="A244" t="str">
-        <v>00000000000000000000000001010111</v>
+        <v>00000000000000000000000010001010</v>
       </c>
       <c r="B244" t="str">
         <v>00000000000000000000000000000000</v>
@@ -8905,7 +8905,7 @@
         <v>0</v>
       </c>
       <c r="H244" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I244">
         <v>0</v>
@@ -8919,10 +8919,10 @@
     </row>
     <row r="245">
       <c r="A245" t="str">
-        <v>00101110001110100000000000011011</v>
+        <v>00000000000000000000000011010000</v>
       </c>
       <c r="B245" t="str">
-        <v>00100000111111000000101000010010</v>
+        <v>00000000000000000000000000000000</v>
       </c>
       <c r="C245" t="str">
         <v>00000000000000000000000000000000</v>
@@ -8931,7 +8931,7 @@
         <v>00000000000000000000000000000000</v>
       </c>
       <c r="E245" t="str">
-        <v>00100001011110100000000011110011</v>
+        <v>00000000000000000000000000000000</v>
       </c>
       <c r="F245" t="b">
         <v>0</v>
@@ -8954,10 +8954,10 @@
     </row>
     <row r="246">
       <c r="A246" t="str">
-        <v>00101110001110100000000000011100</v>
+        <v>00000000000000000000000001011001</v>
       </c>
       <c r="B246" t="str">
-        <v>00100000111111000000001001010000</v>
+        <v>00000000000000000000000000000000</v>
       </c>
       <c r="C246" t="str">
         <v>00000000000000000000000000000000</v>
@@ -8966,7 +8966,7 @@
         <v>00000000000000000000000000000000</v>
       </c>
       <c r="E246" t="str">
-        <v>00100001011110100000000011110100</v>
+        <v>00000000000000000000000000000000</v>
       </c>
       <c r="F246" t="b">
         <v>0</v>
@@ -8989,10 +8989,10 @@
     </row>
     <row r="247">
       <c r="A247" t="str">
-        <v>00101110001110100000000000011100</v>
+        <v>00000000000000000000000010010000</v>
       </c>
       <c r="B247" t="str">
-        <v>00100000111111000000011000001000</v>
+        <v>00000000000000000000000000000000</v>
       </c>
       <c r="C247" t="str">
         <v>00000000000000000000000000000000</v>
@@ -9001,7 +9001,7 @@
         <v>00000000000000000000000000000000</v>
       </c>
       <c r="E247" t="str">
-        <v>00100001011110100000000011110101</v>
+        <v>00000000000000000000000000000000</v>
       </c>
       <c r="F247" t="b">
         <v>0</v>
@@ -9024,10 +9024,10 @@
     </row>
     <row r="248">
       <c r="A248" t="str">
-        <v>00101110001110100000000000011101</v>
+        <v>00000000000000000000000001011000</v>
       </c>
       <c r="B248" t="str">
-        <v>00100000111111000000000010111000</v>
+        <v>00000000000000000000000000000000</v>
       </c>
       <c r="C248" t="str">
         <v>00000000000000000000000000000000</v>
@@ -9036,7 +9036,7 @@
         <v>00000000000000000000000000000000</v>
       </c>
       <c r="E248" t="str">
-        <v>00100001011110100000000011110110</v>
+        <v>00000000000000000000000000000000</v>
       </c>
       <c r="F248" t="b">
         <v>0</v>
@@ -9059,10 +9059,10 @@
     </row>
     <row r="249">
       <c r="A249" t="str">
-        <v>00101110001110100000000000011101</v>
+        <v>00000000000000000000000001000101</v>
       </c>
       <c r="B249" t="str">
-        <v>00100000111111000000111000111111</v>
+        <v>00000000000000000000000000000000</v>
       </c>
       <c r="C249" t="str">
         <v>00000000000000000000000000000000</v>
@@ -9071,7 +9071,7 @@
         <v>00000000000000000000000000000000</v>
       </c>
       <c r="E249" t="str">
-        <v>00100001011110100000000011110111</v>
+        <v>00000000000000000000000000000000</v>
       </c>
       <c r="F249" t="b">
         <v>0</v>
@@ -9080,7 +9080,7 @@
         <v>0</v>
       </c>
       <c r="H249" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I249">
         <v>0</v>
@@ -9094,10 +9094,10 @@
     </row>
     <row r="250">
       <c r="A250" t="str">
-        <v>00101110001110100000000000011101</v>
+        <v>00000000000000000000000011110111</v>
       </c>
       <c r="B250" t="str">
-        <v>00100000111111000000100101010011</v>
+        <v>00000000000000000000000000000000</v>
       </c>
       <c r="C250" t="str">
         <v>00000000000000000000000000000000</v>
@@ -9106,7 +9106,7 @@
         <v>00000000000000000000000000000000</v>
       </c>
       <c r="E250" t="str">
-        <v>00100001011110100000000011111000</v>
+        <v>00000000000000000000000000000000</v>
       </c>
       <c r="F250" t="b">
         <v>0</v>
@@ -9115,7 +9115,7 @@
         <v>0</v>
       </c>
       <c r="H250" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I250">
         <v>0</v>
@@ -9129,10 +9129,10 @@
     </row>
     <row r="251">
       <c r="A251" t="str">
-        <v>00101110001110100000000000011101</v>
+        <v>00000000000000000000000011111000</v>
       </c>
       <c r="B251" t="str">
-        <v>00100000111111000000110000010100</v>
+        <v>00000000000000000000000000000000</v>
       </c>
       <c r="C251" t="str">
         <v>00000000000000000000000000000000</v>
@@ -9141,7 +9141,7 @@
         <v>00000000000000000000000000000000</v>
       </c>
       <c r="E251" t="str">
-        <v>00100001011110100000000011111001</v>
+        <v>00000000000000000000000000000000</v>
       </c>
       <c r="F251" t="b">
         <v>0</v>
@@ -9150,7 +9150,7 @@
         <v>0</v>
       </c>
       <c r="H251" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I251">
         <v>0</v>
@@ -9164,10 +9164,10 @@
     </row>
     <row r="252">
       <c r="A252" t="str">
-        <v>00101110001110100000000000011101</v>
+        <v>00000000000000000000000011111001</v>
       </c>
       <c r="B252" t="str">
-        <v>00100000111111000000100010001010</v>
+        <v>00000000000000000000000000000000</v>
       </c>
       <c r="C252" t="str">
         <v>00000000000000000000000000000000</v>
@@ -9176,7 +9176,7 @@
         <v>00000000000000000000000000000000</v>
       </c>
       <c r="E252" t="str">
-        <v>00100001011110100000000011111010</v>
+        <v>00000000000000000000000000000000</v>
       </c>
       <c r="F252" t="b">
         <v>0</v>
@@ -9185,7 +9185,7 @@
         <v>0</v>
       </c>
       <c r="H252" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I252">
         <v>0</v>
@@ -9199,10 +9199,10 @@
     </row>
     <row r="253">
       <c r="A253" t="str">
-        <v>00101110001110100000000000011101</v>
+        <v>00000000000000000000000011111010</v>
       </c>
       <c r="B253" t="str">
-        <v>00100000111111000000000010111101</v>
+        <v>00000000000000000000000000000000</v>
       </c>
       <c r="C253" t="str">
         <v>00000000000000000000000000000000</v>
@@ -9211,7 +9211,7 @@
         <v>00000000000000000000000000000000</v>
       </c>
       <c r="E253" t="str">
-        <v>00100001011110100000000011111011</v>
+        <v>00000000000000000000000000000000</v>
       </c>
       <c r="F253" t="b">
         <v>0</v>
@@ -9220,7 +9220,7 @@
         <v>0</v>
       </c>
       <c r="H253" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I253">
         <v>0</v>
@@ -9234,7 +9234,7 @@
     </row>
     <row r="254">
       <c r="A254" t="str">
-        <v>00000000000000000000000011101110</v>
+        <v>00000000000000000000000011111011</v>
       </c>
       <c r="B254" t="str">
         <v>00000000000000000000000000000000</v>
@@ -9269,10 +9269,10 @@
     </row>
     <row r="255">
       <c r="A255" t="str">
-        <v>00101110001110100000000000011110</v>
+        <v>00000000000000000000000011111100</v>
       </c>
       <c r="B255" t="str">
-        <v>00100000111111000000000001001111</v>
+        <v>00000000000000000000000000000000</v>
       </c>
       <c r="C255" t="str">
         <v>00000000000000000000000000000000</v>
@@ -9281,7 +9281,7 @@
         <v>00000000000000000000000000000000</v>
       </c>
       <c r="E255" t="str">
-        <v>00100001011110100000000011111101</v>
+        <v>00000000000000000000000000000000</v>
       </c>
       <c r="F255" t="b">
         <v>0</v>
@@ -9290,7 +9290,7 @@
         <v>0</v>
       </c>
       <c r="H255" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I255">
         <v>0</v>
@@ -9304,10 +9304,10 @@
     </row>
     <row r="256">
       <c r="A256" t="str">
-        <v>00101110001110100000000000011110</v>
+        <v>00000000000000000000000011111101</v>
       </c>
       <c r="B256" t="str">
-        <v>00100000111111000000101100000011</v>
+        <v>00000000000000000000000000000000</v>
       </c>
       <c r="C256" t="str">
         <v>00000000000000000000000000000000</v>
@@ -9316,7 +9316,7 @@
         <v>00000000000000000000000000000000</v>
       </c>
       <c r="E256" t="str">
-        <v>00100001011110100000000011111110</v>
+        <v>00000000000000000000000000000000</v>
       </c>
       <c r="F256" t="b">
         <v>0</v>
@@ -9325,7 +9325,7 @@
         <v>0</v>
       </c>
       <c r="H256" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I256">
         <v>0</v>
@@ -9339,7 +9339,7 @@
     </row>
     <row r="257">
       <c r="A257" t="str">
-        <v>00000000000000000000000011011101</v>
+        <v>00000000000000000000000011111110</v>
       </c>
       <c r="B257" t="str">
         <v>00000000000000000000000000000000</v>
@@ -9374,10 +9374,10 @@
     </row>
     <row r="258">
       <c r="A258" t="str">
-        <v>00101110001110100000000000011110</v>
+        <v>00000000000000000000000011111111</v>
       </c>
       <c r="B258" t="str">
-        <v>00100000111111000000000001010110</v>
+        <v>00000000000000000000000000000000</v>
       </c>
       <c r="C258" t="str">
         <v>00000000000000000000000000000000</v>
@@ -9386,7 +9386,7 @@
         <v>00000000000000000000000000000000</v>
       </c>
       <c r="E258" t="str">
-        <v>00100001011110100000000100000000</v>
+        <v>00000000000000000000000000000000</v>
       </c>
       <c r="F258" t="b">
         <v>0</v>
@@ -9395,7 +9395,7 @@
         <v>0</v>
       </c>
       <c r="H258" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I258">
         <v>0</v>
@@ -9409,7 +9409,7 @@
     </row>
     <row r="259">
       <c r="A259" t="str">
-        <v>00000000000000000000000100101000</v>
+        <v>00000000000000000000000100000000</v>
       </c>
       <c r="B259" t="str">
         <v>00000000000000000000000000000000</v>
@@ -9444,10 +9444,10 @@
     </row>
     <row r="260">
       <c r="A260" t="str">
-        <v>00101110001110100000000000011110</v>
+        <v>00000000000000000000000100000001</v>
       </c>
       <c r="B260" t="str">
-        <v>00100000111111000000101000000011</v>
+        <v>00000000000000000000000000000000</v>
       </c>
       <c r="C260" t="str">
         <v>00000000000000000000000000000000</v>
@@ -9456,7 +9456,7 @@
         <v>00000000000000000000000000000000</v>
       </c>
       <c r="E260" t="str">
-        <v>00100001011110100000000100000010</v>
+        <v>00000000000000000000000000000000</v>
       </c>
       <c r="F260" t="b">
         <v>0</v>
@@ -9465,7 +9465,7 @@
         <v>0</v>
       </c>
       <c r="H260" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I260">
         <v>0</v>
@@ -9479,10 +9479,10 @@
     </row>
     <row r="261">
       <c r="A261" t="str">
-        <v>00101110001110100000000000011110</v>
+        <v>00000000000000000000000100000010</v>
       </c>
       <c r="B261" t="str">
-        <v>00100000111111000000101110111000</v>
+        <v>00000000000000000000000000000000</v>
       </c>
       <c r="C261" t="str">
         <v>00000000000000000000000000000000</v>
@@ -9491,7 +9491,7 @@
         <v>00000000000000000000000000000000</v>
       </c>
       <c r="E261" t="str">
-        <v>00100001011110100000000100000011</v>
+        <v>00000000000000000000000000000000</v>
       </c>
       <c r="F261" t="b">
         <v>0</v>
@@ -9500,7 +9500,7 @@
         <v>0</v>
       </c>
       <c r="H261" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I261">
         <v>0</v>
@@ -9514,10 +9514,10 @@
     </row>
     <row r="262">
       <c r="A262" t="str">
-        <v>00101110001110100000000000011110</v>
+        <v>00000000000000000000000100000011</v>
       </c>
       <c r="B262" t="str">
-        <v>00100000111111000000000101100100</v>
+        <v>00000000000000000000000000000000</v>
       </c>
       <c r="C262" t="str">
         <v>00000000000000000000000000000000</v>
@@ -9526,7 +9526,7 @@
         <v>00000000000000000000000000000000</v>
       </c>
       <c r="E262" t="str">
-        <v>00100001011110100000000100000100</v>
+        <v>00000000000000000000000000000000</v>
       </c>
       <c r="F262" t="b">
         <v>0</v>
@@ -9535,7 +9535,7 @@
         <v>0</v>
       </c>
       <c r="H262" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I262">
         <v>0</v>
@@ -9549,10 +9549,10 @@
     </row>
     <row r="263">
       <c r="A263" t="str">
-        <v>00101110001110100000000000011110</v>
+        <v>00000000000000000000000100000100</v>
       </c>
       <c r="B263" t="str">
-        <v>00100000111111000000000001110111</v>
+        <v>00000000000000000000000000000000</v>
       </c>
       <c r="C263" t="str">
         <v>00000000000000000000000000000000</v>
@@ -9561,7 +9561,7 @@
         <v>00000000000000000000000000000000</v>
       </c>
       <c r="E263" t="str">
-        <v>00100001011110100000000100000101</v>
+        <v>00000000000000000000000000000000</v>
       </c>
       <c r="F263" t="b">
         <v>0</v>
@@ -9570,7 +9570,7 @@
         <v>0</v>
       </c>
       <c r="H263" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I263">
         <v>0</v>
@@ -9584,10 +9584,10 @@
     </row>
     <row r="264">
       <c r="A264" t="str">
-        <v>00101110001110100000000000011111</v>
+        <v>00000000000000000000000100000101</v>
       </c>
       <c r="B264" t="str">
-        <v>00100000111111000000000101001000</v>
+        <v>00000000000000000000000000000000</v>
       </c>
       <c r="C264" t="str">
         <v>00000000000000000000000000000000</v>
@@ -9596,7 +9596,7 @@
         <v>00000000000000000000000000000000</v>
       </c>
       <c r="E264" t="str">
-        <v>00100001011110100000000100000110</v>
+        <v>00000000000000000000000000000000</v>
       </c>
       <c r="F264" t="b">
         <v>0</v>
@@ -9605,7 +9605,7 @@
         <v>0</v>
       </c>
       <c r="H264" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I264">
         <v>0</v>
@@ -9619,10 +9619,10 @@
     </row>
     <row r="265">
       <c r="A265" t="str">
-        <v>00101110001110100000000000011111</v>
+        <v>00000000000000000000000100000110</v>
       </c>
       <c r="B265" t="str">
-        <v>00100000111111000000010011101100</v>
+        <v>00000000000000000000000000000000</v>
       </c>
       <c r="C265" t="str">
         <v>00000000000000000000000000000000</v>
@@ -9631,7 +9631,7 @@
         <v>00000000000000000000000000000000</v>
       </c>
       <c r="E265" t="str">
-        <v>00100001011110100000000100000111</v>
+        <v>00000000000000000000000000000000</v>
       </c>
       <c r="F265" t="b">
         <v>0</v>
@@ -9640,7 +9640,7 @@
         <v>0</v>
       </c>
       <c r="H265" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I265">
         <v>0</v>
@@ -9654,10 +9654,10 @@
     </row>
     <row r="266">
       <c r="A266" t="str">
-        <v>00101110001110100000000000100000</v>
+        <v>00000000000000000000000100000111</v>
       </c>
       <c r="B266" t="str">
-        <v>00100000111111000000101101001111</v>
+        <v>00000000000000000000000000000000</v>
       </c>
       <c r="C266" t="str">
         <v>00000000000000000000000000000000</v>
@@ -9666,7 +9666,7 @@
         <v>00000000000000000000000000000000</v>
       </c>
       <c r="E266" t="str">
-        <v>00100001011110100000000100001000</v>
+        <v>00000000000000000000000000000000</v>
       </c>
       <c r="F266" t="b">
         <v>0</v>
@@ -9675,7 +9675,7 @@
         <v>0</v>
       </c>
       <c r="H266" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I266">
         <v>0</v>
@@ -9689,10 +9689,10 @@
     </row>
     <row r="267">
       <c r="A267" t="str">
-        <v>00101110001110100000000000100000</v>
+        <v>00000000000000000000000010101101</v>
       </c>
       <c r="B267" t="str">
-        <v>00100000111111000000101101111100</v>
+        <v>00000000000000000000000000000000</v>
       </c>
       <c r="C267" t="str">
         <v>00000000000000000000000000000000</v>
@@ -9701,7 +9701,7 @@
         <v>00000000000000000000000000000000</v>
       </c>
       <c r="E267" t="str">
-        <v>00100001011110100000000100001001</v>
+        <v>00000000000000000000000000000000</v>
       </c>
       <c r="F267" t="b">
         <v>0</v>
@@ -9710,7 +9710,7 @@
         <v>0</v>
       </c>
       <c r="H267" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I267">
         <v>0</v>
@@ -9724,10 +9724,10 @@
     </row>
     <row r="268">
       <c r="A268" t="str">
-        <v>00101110001110100000000000100000</v>
+        <v>00000000000000000000000100001011</v>
       </c>
       <c r="B268" t="str">
-        <v>00100000111111000000011100110101</v>
+        <v>00000000000000000000000000000000</v>
       </c>
       <c r="C268" t="str">
         <v>00000000000000000000000000000000</v>
@@ -9736,7 +9736,7 @@
         <v>00000000000000000000000000000000</v>
       </c>
       <c r="E268" t="str">
-        <v>00100001011110100000000100001010</v>
+        <v>00000000000000000000000000000000</v>
       </c>
       <c r="F268" t="b">
         <v>0</v>
@@ -9745,7 +9745,7 @@
         <v>0</v>
       </c>
       <c r="H268" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I268">
         <v>0</v>
@@ -9759,10 +9759,10 @@
     </row>
     <row r="269">
       <c r="A269" t="str">
-        <v>00101110001110100000000000100000</v>
+        <v>00000000000000000000000100001100</v>
       </c>
       <c r="B269" t="str">
-        <v>00100000111111000000001010010000</v>
+        <v>00000000000000000000000000000000</v>
       </c>
       <c r="C269" t="str">
         <v>00000000000000000000000000000000</v>
@@ -9771,7 +9771,7 @@
         <v>00000000000000000000000000000000</v>
       </c>
       <c r="E269" t="str">
-        <v>00100001011110100000000100001011</v>
+        <v>00000000000000000000000000000000</v>
       </c>
       <c r="F269" t="b">
         <v>0</v>
@@ -9780,7 +9780,7 @@
         <v>0</v>
       </c>
       <c r="H269" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I269">
         <v>0</v>
@@ -9794,10 +9794,10 @@
     </row>
     <row r="270">
       <c r="A270" t="str">
-        <v>00101110001110100000000000100000</v>
+        <v>00000000000000000000000100001101</v>
       </c>
       <c r="B270" t="str">
-        <v>00100000111111000000000010011111</v>
+        <v>00000000000000000000000000000000</v>
       </c>
       <c r="C270" t="str">
         <v>00000000000000000000000000000000</v>
@@ -9806,7 +9806,7 @@
         <v>00000000000000000000000000000000</v>
       </c>
       <c r="E270" t="str">
-        <v>00100001011110100000000100001100</v>
+        <v>00000000000000000000000000000000</v>
       </c>
       <c r="F270" t="b">
         <v>0</v>
@@ -9815,7 +9815,7 @@
         <v>0</v>
       </c>
       <c r="H270" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I270">
         <v>0</v>
@@ -9829,10 +9829,10 @@
     </row>
     <row r="271">
       <c r="A271" t="str">
-        <v>00101110001110100000000000100000</v>
+        <v>00000000000000000000000100001110</v>
       </c>
       <c r="B271" t="str">
-        <v>00100000111111000000010111011011</v>
+        <v>00000000000000000000000000000000</v>
       </c>
       <c r="C271" t="str">
         <v>00000000000000000000000000000000</v>
@@ -9841,7 +9841,7 @@
         <v>00000000000000000000000000000000</v>
       </c>
       <c r="E271" t="str">
-        <v>00100001011110100000000100001101</v>
+        <v>00000000000000000000000000000000</v>
       </c>
       <c r="F271" t="b">
         <v>0</v>
@@ -9850,7 +9850,7 @@
         <v>0</v>
       </c>
       <c r="H271" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I271">
         <v>0</v>
@@ -9864,10 +9864,10 @@
     </row>
     <row r="272">
       <c r="A272" t="str">
-        <v>00101110001110100000000000100000</v>
+        <v>00000000000000000000000100001111</v>
       </c>
       <c r="B272" t="str">
-        <v>00100000111111000000101000010101</v>
+        <v>00000000000000000000000000000000</v>
       </c>
       <c r="C272" t="str">
         <v>00000000000000000000000000000000</v>
@@ -9876,7 +9876,7 @@
         <v>00000000000000000000000000000000</v>
       </c>
       <c r="E272" t="str">
-        <v>00100001011110100000000100001110</v>
+        <v>00000000000000000000000000000000</v>
       </c>
       <c r="F272" t="b">
         <v>0</v>
@@ -9885,7 +9885,7 @@
         <v>0</v>
       </c>
       <c r="H272" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I272">
         <v>0</v>
@@ -9899,10 +9899,10 @@
     </row>
     <row r="273">
       <c r="A273" t="str">
-        <v>00101110001110100000000000100000</v>
+        <v>00000000000000000000000100010000</v>
       </c>
       <c r="B273" t="str">
-        <v>00100000111111000000001111010101</v>
+        <v>00000000000000000000000000000000</v>
       </c>
       <c r="C273" t="str">
         <v>00000000000000000000000000000000</v>
@@ -9911,7 +9911,7 @@
         <v>00000000000000000000000000000000</v>
       </c>
       <c r="E273" t="str">
-        <v>00100001011110100000000100001111</v>
+        <v>00000000000000000000000000000000</v>
       </c>
       <c r="F273" t="b">
         <v>0</v>
@@ -9920,7 +9920,7 @@
         <v>0</v>
       </c>
       <c r="H273" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I273">
         <v>0</v>
@@ -9934,10 +9934,10 @@
     </row>
     <row r="274">
       <c r="A274" t="str">
-        <v>00101110001110100000000000100001</v>
+        <v>00000000000000000000000100010001</v>
       </c>
       <c r="B274" t="str">
-        <v>00100000111111000000001110000110</v>
+        <v>00000000000000000000000000000000</v>
       </c>
       <c r="C274" t="str">
         <v>00000000000000000000000000000000</v>
@@ -9946,7 +9946,7 @@
         <v>00000000000000000000000000000000</v>
       </c>
       <c r="E274" t="str">
-        <v>00100001011110100000000100010000</v>
+        <v>00000000000000000000000000000000</v>
       </c>
       <c r="F274" t="b">
         <v>0</v>
@@ -9955,7 +9955,7 @@
         <v>0</v>
       </c>
       <c r="H274" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I274">
         <v>0</v>
@@ -9969,10 +9969,10 @@
     </row>
     <row r="275">
       <c r="A275" t="str">
-        <v>00101110001110100000000000100001</v>
+        <v>00000000000000000000000100010010</v>
       </c>
       <c r="B275" t="str">
-        <v>00100000111111000000100101000111</v>
+        <v>00000000000000000000000000000000</v>
       </c>
       <c r="C275" t="str">
         <v>00000000000000000000000000000000</v>
@@ -9981,7 +9981,7 @@
         <v>00000000000000000000000000000000</v>
       </c>
       <c r="E275" t="str">
-        <v>00100001011110100000000100010001</v>
+        <v>00000000000000000000000000000000</v>
       </c>
       <c r="F275" t="b">
         <v>0</v>
@@ -9990,7 +9990,7 @@
         <v>0</v>
       </c>
       <c r="H275" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I275">
         <v>0</v>
@@ -10004,10 +10004,10 @@
     </row>
     <row r="276">
       <c r="A276" t="str">
-        <v>00101110001110100000000000100001</v>
+        <v>00000000000000000000000100010011</v>
       </c>
       <c r="B276" t="str">
-        <v>00100000111111000000000001011111</v>
+        <v>00000000000000000000000000000000</v>
       </c>
       <c r="C276" t="str">
         <v>00000000000000000000000000000000</v>
@@ -10016,7 +10016,7 @@
         <v>00000000000000000000000000000000</v>
       </c>
       <c r="E276" t="str">
-        <v>00100001011110100000000100010010</v>
+        <v>00000000000000000000000000000000</v>
       </c>
       <c r="F276" t="b">
         <v>0</v>
@@ -10025,7 +10025,7 @@
         <v>0</v>
       </c>
       <c r="H276" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I276">
         <v>0</v>
@@ -10039,10 +10039,10 @@
     </row>
     <row r="277">
       <c r="A277" t="str">
-        <v>00101110001110100000000000100011</v>
+        <v>00000000000000000000000100010100</v>
       </c>
       <c r="B277" t="str">
-        <v>00100000111111000000101100110101</v>
+        <v>00000000000000000000000000000000</v>
       </c>
       <c r="C277" t="str">
         <v>00000000000000000000000000000000</v>
@@ -10051,7 +10051,7 @@
         <v>00000000000000000000000000000000</v>
       </c>
       <c r="E277" t="str">
-        <v>00100001011110100000000100010011</v>
+        <v>00000000000000000000000000000000</v>
       </c>
       <c r="F277" t="b">
         <v>0</v>
@@ -10060,7 +10060,7 @@
         <v>0</v>
       </c>
       <c r="H277" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I277">
         <v>0</v>
@@ -10074,10 +10074,10 @@
     </row>
     <row r="278">
       <c r="A278" t="str">
-        <v>00101110001110100000000000100011</v>
+        <v>00000000000000000000000100010101</v>
       </c>
       <c r="B278" t="str">
-        <v>00100000111111000000101100111101</v>
+        <v>00000000000000000000000000000000</v>
       </c>
       <c r="C278" t="str">
         <v>00000000000000000000000000000000</v>
@@ -10086,7 +10086,7 @@
         <v>00000000000000000000000000000000</v>
       </c>
       <c r="E278" t="str">
-        <v>00100001011110100000000100010100</v>
+        <v>00000000000000000000000000000000</v>
       </c>
       <c r="F278" t="b">
         <v>0</v>
@@ -10095,7 +10095,7 @@
         <v>0</v>
       </c>
       <c r="H278" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I278">
         <v>0</v>
@@ -10109,10 +10109,10 @@
     </row>
     <row r="279">
       <c r="A279" t="str">
-        <v>00101110001110100000000000100011</v>
+        <v>00000000000000000000000100010110</v>
       </c>
       <c r="B279" t="str">
-        <v>00100000111111000000010000000000</v>
+        <v>00000000000000000000000000000000</v>
       </c>
       <c r="C279" t="str">
         <v>00000000000000000000000000000000</v>
@@ -10121,7 +10121,7 @@
         <v>00000000000000000000000000000000</v>
       </c>
       <c r="E279" t="str">
-        <v>00100001011110100000000100010101</v>
+        <v>00000000000000000000000000000000</v>
       </c>
       <c r="F279" t="b">
         <v>0</v>
@@ -10130,7 +10130,7 @@
         <v>0</v>
       </c>
       <c r="H279" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I279">
         <v>0</v>
@@ -10144,10 +10144,10 @@
     </row>
     <row r="280">
       <c r="A280" t="str">
-        <v>00101110001110100000000000100011</v>
+        <v>00000000000000000000000100010111</v>
       </c>
       <c r="B280" t="str">
-        <v>00100000111111000000001110101011</v>
+        <v>00000000000000000000000000000000</v>
       </c>
       <c r="C280" t="str">
         <v>00000000000000000000000000000000</v>
@@ -10156,7 +10156,7 @@
         <v>00000000000000000000000000000000</v>
       </c>
       <c r="E280" t="str">
-        <v>00100001011110100000000100010110</v>
+        <v>00000000000000000000000000000000</v>
       </c>
       <c r="F280" t="b">
         <v>0</v>
@@ -10165,7 +10165,7 @@
         <v>0</v>
       </c>
       <c r="H280" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I280">
         <v>0</v>
@@ -10179,10 +10179,10 @@
     </row>
     <row r="281">
       <c r="A281" t="str">
-        <v>00101110001110100000000000100011</v>
+        <v>00000000000000000000000100011000</v>
       </c>
       <c r="B281" t="str">
-        <v>00100000111111000000100000111111</v>
+        <v>00000000000000000000000000000000</v>
       </c>
       <c r="C281" t="str">
         <v>00000000000000000000000000000000</v>
@@ -10191,7 +10191,7 @@
         <v>00000000000000000000000000000000</v>
       </c>
       <c r="E281" t="str">
-        <v>00100001011110100000000100010111</v>
+        <v>00000000000000000000000000000000</v>
       </c>
       <c r="F281" t="b">
         <v>0</v>
@@ -10200,7 +10200,7 @@
         <v>0</v>
       </c>
       <c r="H281" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I281">
         <v>0</v>
@@ -10214,10 +10214,10 @@
     </row>
     <row r="282">
       <c r="A282" t="str">
-        <v>00101110001110100000000000100100</v>
+        <v>00000000000000000000000100011001</v>
       </c>
       <c r="B282" t="str">
-        <v>00100000111111000000011111011011</v>
+        <v>00000000000000000000000000000000</v>
       </c>
       <c r="C282" t="str">
         <v>00000000000000000000000000000000</v>
@@ -10226,7 +10226,7 @@
         <v>00000000000000000000000000000000</v>
       </c>
       <c r="E282" t="str">
-        <v>00100001011110100000000100011000</v>
+        <v>00000000000000000000000000000000</v>
       </c>
       <c r="F282" t="b">
         <v>0</v>
@@ -10235,7 +10235,7 @@
         <v>0</v>
       </c>
       <c r="H282" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I282">
         <v>0</v>
@@ -10249,7 +10249,7 @@
     </row>
     <row r="283">
       <c r="A283" t="str">
-        <v>00000000000000000000000000110111</v>
+        <v>00000000000000000000000100011010</v>
       </c>
       <c r="B283" t="str">
         <v>00000000000000000000000000000000</v>
@@ -10284,7 +10284,7 @@
     </row>
     <row r="284">
       <c r="A284" t="str">
-        <v>00000000000000000000000010110000</v>
+        <v>00000000000000000000000100011011</v>
       </c>
       <c r="B284" t="str">
         <v>00000000000000000000000000000000</v>
@@ -10319,10 +10319,10 @@
     </row>
     <row r="285">
       <c r="A285" t="str">
-        <v>00101110001110100000000000100100</v>
+        <v>00000000000000000000000100011100</v>
       </c>
       <c r="B285" t="str">
-        <v>00100000111111000000011001111011</v>
+        <v>00000000000000000000000000000000</v>
       </c>
       <c r="C285" t="str">
         <v>00000000000000000000000000000000</v>
@@ -10331,7 +10331,7 @@
         <v>00000000000000000000000000000000</v>
       </c>
       <c r="E285" t="str">
-        <v>00100001011110100000000100011011</v>
+        <v>00000000000000000000000000000000</v>
       </c>
       <c r="F285" t="b">
         <v>0</v>
@@ -10340,7 +10340,7 @@
         <v>0</v>
       </c>
       <c r="H285" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I285">
         <v>0</v>
@@ -10354,7 +10354,7 @@
     </row>
     <row r="286">
       <c r="A286" t="str">
-        <v>00000000000000000000000010100000</v>
+        <v>00000000000000000000000100011101</v>
       </c>
       <c r="B286" t="str">
         <v>00000000000000000000000000000000</v>
@@ -10389,10 +10389,10 @@
     </row>
     <row r="287">
       <c r="A287" t="str">
-        <v>00101110001110100000000000100100</v>
+        <v>00000000000000000000000100011110</v>
       </c>
       <c r="B287" t="str">
-        <v>00100000111111000000101011011111</v>
+        <v>00000000000000000000000000000000</v>
       </c>
       <c r="C287" t="str">
         <v>00000000000000000000000000000000</v>
@@ -10401,7 +10401,7 @@
         <v>00000000000000000000000000000000</v>
       </c>
       <c r="E287" t="str">
-        <v>00100001011110100000000100011101</v>
+        <v>00000000000000000000000000000000</v>
       </c>
       <c r="F287" t="b">
         <v>0</v>
@@ -10410,7 +10410,7 @@
         <v>0</v>
       </c>
       <c r="H287" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I287">
         <v>0</v>
@@ -10424,10 +10424,10 @@
     </row>
     <row r="288">
       <c r="A288" t="str">
-        <v>00101110001110100000000000100100</v>
+        <v>00000000000000000000000100011111</v>
       </c>
       <c r="B288" t="str">
-        <v>00100000111111000000110000111011</v>
+        <v>00000000000000000000000000000000</v>
       </c>
       <c r="C288" t="str">
         <v>00000000000000000000000000000000</v>
@@ -10436,7 +10436,7 @@
         <v>00000000000000000000000000000000</v>
       </c>
       <c r="E288" t="str">
-        <v>00100001011110100000000100011110</v>
+        <v>00000000000000000000000000000000</v>
       </c>
       <c r="F288" t="b">
         <v>0</v>
@@ -10445,7 +10445,7 @@
         <v>0</v>
       </c>
       <c r="H288" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I288">
         <v>0</v>
@@ -10459,10 +10459,10 @@
     </row>
     <row r="289">
       <c r="A289" t="str">
-        <v>00101110001110100000000000100100</v>
+        <v>00000000000000000000000100100000</v>
       </c>
       <c r="B289" t="str">
-        <v>00100000111111000000100100011010</v>
+        <v>00000000000000000000000000000000</v>
       </c>
       <c r="C289" t="str">
         <v>00000000000000000000000000000000</v>
@@ -10471,7 +10471,7 @@
         <v>00000000000000000000000000000000</v>
       </c>
       <c r="E289" t="str">
-        <v>00100001011110100000000100011111</v>
+        <v>00000000000000000000000000000000</v>
       </c>
       <c r="F289" t="b">
         <v>0</v>
@@ -10480,7 +10480,7 @@
         <v>0</v>
       </c>
       <c r="H289" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I289">
         <v>0</v>
@@ -10494,10 +10494,10 @@
     </row>
     <row r="290">
       <c r="A290" t="str">
-        <v>00101110001110100000000000100100</v>
+        <v>00000000000000000000000100100001</v>
       </c>
       <c r="B290" t="str">
-        <v>00100000111111000000110000011010</v>
+        <v>00000000000000000000000000000000</v>
       </c>
       <c r="C290" t="str">
         <v>00000000000000000000000000000000</v>
@@ -10506,7 +10506,7 @@
         <v>00000000000000000000000000000000</v>
       </c>
       <c r="E290" t="str">
-        <v>00100001011110100000000100100000</v>
+        <v>00000000000000000000000000000000</v>
       </c>
       <c r="F290" t="b">
         <v>0</v>
@@ -10515,7 +10515,7 @@
         <v>0</v>
       </c>
       <c r="H290" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I290">
         <v>0</v>
@@ -10529,10 +10529,10 @@
     </row>
     <row r="291">
       <c r="A291" t="str">
-        <v>00101110001110100000000000100100</v>
+        <v>00000000000000000000000100100010</v>
       </c>
       <c r="B291" t="str">
-        <v>00100000111111000000000110000110</v>
+        <v>00000000000000000000000000000000</v>
       </c>
       <c r="C291" t="str">
         <v>00000000000000000000000000000000</v>
@@ -10541,7 +10541,7 @@
         <v>00000000000000000000000000000000</v>
       </c>
       <c r="E291" t="str">
-        <v>00100001011110100000000100100001</v>
+        <v>00000000000000000000000000000000</v>
       </c>
       <c r="F291" t="b">
         <v>0</v>
@@ -10550,7 +10550,7 @@
         <v>0</v>
       </c>
       <c r="H291" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I291">
         <v>0</v>
@@ -10564,10 +10564,10 @@
     </row>
     <row r="292">
       <c r="A292" t="str">
-        <v>00101110001110100000000000100010</v>
+        <v>00000000000000000000000100100011</v>
       </c>
       <c r="B292" t="str">
-        <v>00100000111111000000001010110011</v>
+        <v>00000000000000000000000000000000</v>
       </c>
       <c r="C292" t="str">
         <v>00000000000000000000000000000000</v>
@@ -10576,7 +10576,7 @@
         <v>00000000000000000000000000000000</v>
       </c>
       <c r="E292" t="str">
-        <v>00100001011110100000000100100010</v>
+        <v>00000000000000000000000000000000</v>
       </c>
       <c r="F292" t="b">
         <v>0</v>
@@ -10585,7 +10585,7 @@
         <v>0</v>
       </c>
       <c r="H292" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I292">
         <v>0</v>
@@ -10599,10 +10599,10 @@
     </row>
     <row r="293">
       <c r="A293" t="str">
-        <v>00101110001110100000000000100010</v>
+        <v>00000000000000000000000100100100</v>
       </c>
       <c r="B293" t="str">
-        <v>00100000111111000000100110001010</v>
+        <v>00000000000000000000000000000000</v>
       </c>
       <c r="C293" t="str">
         <v>00000000000000000000000000000000</v>
@@ -10611,7 +10611,7 @@
         <v>00000000000000000000000000000000</v>
       </c>
       <c r="E293" t="str">
-        <v>00100001011110100000000100100011</v>
+        <v>00000000000000000000000000000000</v>
       </c>
       <c r="F293" t="b">
         <v>0</v>
@@ -10620,7 +10620,7 @@
         <v>0</v>
       </c>
       <c r="H293" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I293">
         <v>0</v>
@@ -10634,10 +10634,10 @@
     </row>
     <row r="294">
       <c r="A294" t="str">
-        <v>00101110001110100000000000100010</v>
+        <v>00000000000000000000000100100101</v>
       </c>
       <c r="B294" t="str">
-        <v>00100000111111000000001110010100</v>
+        <v>00000000000000000000000000000000</v>
       </c>
       <c r="C294" t="str">
         <v>00000000000000000000000000000000</v>
@@ -10646,7 +10646,7 @@
         <v>00000000000000000000000000000000</v>
       </c>
       <c r="E294" t="str">
-        <v>00100001011110100000000100100100</v>
+        <v>00000000000000000000000000000000</v>
       </c>
       <c r="F294" t="b">
         <v>0</v>
@@ -10655,7 +10655,7 @@
         <v>0</v>
       </c>
       <c r="H294" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I294">
         <v>0</v>
@@ -10669,10 +10669,10 @@
     </row>
     <row r="295">
       <c r="A295" t="str">
-        <v>00101110001110100000000000100010</v>
+        <v>00000000000000000000000100100110</v>
       </c>
       <c r="B295" t="str">
-        <v>00100000111111000000001000010111</v>
+        <v>00000000000000000000000000000000</v>
       </c>
       <c r="C295" t="str">
         <v>00000000000000000000000000000000</v>
@@ -10681,7 +10681,7 @@
         <v>00000000000000000000000000000000</v>
       </c>
       <c r="E295" t="str">
-        <v>00100001011110100000000100100101</v>
+        <v>00000000000000000000000000000000</v>
       </c>
       <c r="F295" t="b">
         <v>0</v>
@@ -10690,7 +10690,7 @@
         <v>0</v>
       </c>
       <c r="H295" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I295">
         <v>0</v>
@@ -10704,10 +10704,10 @@
     </row>
     <row r="296">
       <c r="A296" t="str">
-        <v>00101110001110100000000000100010</v>
+        <v>00000000000000000000000100100111</v>
       </c>
       <c r="B296" t="str">
-        <v>00100000111111000000100001110001</v>
+        <v>00000000000000000000000000000000</v>
       </c>
       <c r="C296" t="str">
         <v>00000000000000000000000000000000</v>
@@ -10716,7 +10716,7 @@
         <v>00000000000000000000000000000000</v>
       </c>
       <c r="E296" t="str">
-        <v>00100001011110100000000100100110</v>
+        <v>00000000000000000000000000000000</v>
       </c>
       <c r="F296" t="b">
         <v>0</v>
@@ -10725,7 +10725,7 @@
         <v>0</v>
       </c>
       <c r="H296" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I296">
         <v>0</v>
@@ -10739,10 +10739,10 @@
     </row>
     <row r="297">
       <c r="A297" t="str">
-        <v>00101110001110100000000000100010</v>
+        <v>00000000000000000000000100101000</v>
       </c>
       <c r="B297" t="str">
-        <v>00100000111111000000001110100011</v>
+        <v>00000000000000000000000000000000</v>
       </c>
       <c r="C297" t="str">
         <v>00000000000000000000000000000000</v>
@@ -10751,7 +10751,7 @@
         <v>00000000000000000000000000000000</v>
       </c>
       <c r="E297" t="str">
-        <v>00100001011110100000000100100111</v>
+        <v>00000000000000000000000000000000</v>
       </c>
       <c r="F297" t="b">
         <v>0</v>
@@ -10760,7 +10760,7 @@
         <v>0</v>
       </c>
       <c r="H297" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I297">
         <v>0</v>
@@ -10774,7 +10774,7 @@
     </row>
     <row r="298">
       <c r="A298" t="str">
-        <v>00000000000000000000000000110010</v>
+        <v>00000000000000000000000100101001</v>
       </c>
       <c r="B298" t="str">
         <v>00000000000000000000000000000000</v>
@@ -10809,7 +10809,7 @@
     </row>
     <row r="299">
       <c r="A299" t="str">
-        <v>00000000000000000000000011001000</v>
+        <v>00000000000000000000000100101010</v>
       </c>
       <c r="B299" t="str">
         <v>00000000000000000000000000000000</v>
@@ -10844,10 +10844,10 @@
     </row>
     <row r="300">
       <c r="A300" t="str">
-        <v>00101110001110100000000000011111</v>
+        <v>00000000000000000000000100101011</v>
       </c>
       <c r="B300" t="str">
-        <v>00100000111111000000101001100010</v>
+        <v>00000000000000000000000000000000</v>
       </c>
       <c r="C300" t="str">
         <v>00000000000000000000000000000000</v>
@@ -10856,7 +10856,7 @@
         <v>00000000000000000000000000000000</v>
       </c>
       <c r="E300" t="str">
-        <v>00100001011110100000000100101010</v>
+        <v>00000000000000000000000000000000</v>
       </c>
       <c r="F300" t="b">
         <v>0</v>
@@ -10865,7 +10865,7 @@
         <v>0</v>
       </c>
       <c r="H300" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I300">
         <v>0</v>
@@ -10879,10 +10879,10 @@
     </row>
     <row r="301">
       <c r="A301" t="str">
-        <v>00101110001110100000000000011111</v>
+        <v>00000000000000000000000100101100</v>
       </c>
       <c r="B301" t="str">
-        <v>00100000111111000000101011101010</v>
+        <v>00000000000000000000000000000000</v>
       </c>
       <c r="C301" t="str">
         <v>00000000000000000000000000000000</v>
@@ -10891,7 +10891,7 @@
         <v>00000000000000000000000000000000</v>
       </c>
       <c r="E301" t="str">
-        <v>00100001011110100000000100101011</v>
+        <v>00000000000000000000000000000000</v>
       </c>
       <c r="F301" t="b">
         <v>0</v>
@@ -10900,7 +10900,7 @@
         <v>0</v>
       </c>
       <c r="H301" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I301">
         <v>0</v>
